--- a/data/raw_data/feed_profiles_and_composition.xlsx
+++ b/data/raw_data/feed_profiles_and_composition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\climate_risks_to_fed_mariculture\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E6047F-E33A-4B4A-AF15-F3FC8510E6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303813B8-DDFC-4C34-8F6F-6B92AD618E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="feed_formulations" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="progress" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">feed_assignments!$A$1:$G$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">feed_assignments!$A$1:$F$300</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">feed_formulations!$A$1:$D$203</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1453" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="249">
   <si>
     <t>ingredient</t>
   </si>
@@ -573,9 +573,6 @@
     <t>feed_class</t>
   </si>
   <si>
-    <t>done</t>
-  </si>
-  <si>
     <t>notes</t>
   </si>
   <si>
@@ -729,15 +726,9 @@
     <t>Reunion</t>
   </si>
   <si>
-    <t>y</t>
-  </si>
-  <si>
     <t>Democratic People’s Republic of Korea</t>
   </si>
   <si>
-    <t>wip</t>
-  </si>
-  <si>
     <t>squid-oil</t>
   </si>
   <si>
@@ -811,6 +802,10 @@
   </si>
   <si>
     <t>grouper-world</t>
+  </si>
+  <si>
+    <t>Nankervis, L., Cobcroft, J. M., Nguyen, N. V., &amp; Rimmer, M. A. (2022). Advances in practical feed formulation and adoption for hybrid grouper (Epinephelus fuscoguttatus ♀ × E. lanceolatus ♂) aquaculture. Reviews in Aquaculture, 14(1), 288–307. https://doi.org/10.1111/raq.12598
+Sim, S.-Y., Rimmer, M. A., Williams, K., Toledo, J. D., Sugama, K., Rumengan, I., &amp; Phillips, M. J. (2005). A Practical Guide to Feeds and Feed Management for Cultured Groupers (Nos. 2005–02; p. 18). Asia-Pacific Marine Finfish Aquaculture Network. https://enaca.org/?id=301</t>
   </si>
 </sst>
 </file>
@@ -821,11 +816,18 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1077,64 +1079,67 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="4" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Good" xfId="3" builtinId="26"/>
@@ -1442,7 +1447,7 @@
         <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -1457,7 +1462,7 @@
     </row>
     <row r="2" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -1469,7 +1474,7 @@
     </row>
     <row r="3" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -1481,7 +1486,7 @@
     </row>
     <row r="4" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>24</v>
@@ -1493,7 +1498,7 @@
     </row>
     <row r="5" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>23</v>
@@ -1505,7 +1510,7 @@
     </row>
     <row r="6" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>25</v>
@@ -1517,7 +1522,7 @@
     </row>
     <row r="7" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
@@ -1628,7 +1633,7 @@
         <v>47</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2">
         <v>1.4999999999999999E-2</v>
@@ -2213,7 +2218,7 @@
     </row>
     <row r="65" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>10</v>
@@ -2225,7 +2230,7 @@
     </row>
     <row r="66" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>9</v>
@@ -2237,7 +2242,7 @@
     </row>
     <row r="67" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>1</v>
@@ -2249,7 +2254,7 @@
     </row>
     <row r="68" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>3</v>
@@ -2261,7 +2266,7 @@
     </row>
     <row r="69" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>2</v>
@@ -2273,7 +2278,7 @@
     </row>
     <row r="70" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>21</v>
@@ -2285,7 +2290,7 @@
     </row>
     <row r="71" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>6</v>
@@ -2297,7 +2302,7 @@
     </row>
     <row r="72" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>22</v>
@@ -2309,7 +2314,7 @@
     </row>
     <row r="73" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>23</v>
@@ -2321,7 +2326,7 @@
     </row>
     <row r="74" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>14</v>
@@ -2333,7 +2338,7 @@
     </row>
     <row r="75" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>5</v>
@@ -2345,7 +2350,7 @@
     </row>
     <row r="76" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -2357,10 +2362,10 @@
     </row>
     <row r="77" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C77" s="2">
         <v>3.7600000000000001E-2</v>
@@ -2369,7 +2374,7 @@
     </row>
     <row r="78" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>9</v>
@@ -2381,7 +2386,7 @@
     </row>
     <row r="79" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>1</v>
@@ -2393,7 +2398,7 @@
     </row>
     <row r="80" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>2</v>
@@ -2405,7 +2410,7 @@
     </row>
     <row r="81" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>33</v>
@@ -2417,7 +2422,7 @@
     </row>
     <row r="82" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>24</v>
@@ -2429,7 +2434,7 @@
     </row>
     <row r="83" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>22</v>
@@ -2441,7 +2446,7 @@
     </row>
     <row r="84" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>23</v>
@@ -2453,7 +2458,7 @@
     </row>
     <row r="85" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>12</v>
@@ -2465,7 +2470,7 @@
     </row>
     <row r="86" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>25</v>
@@ -2477,7 +2482,7 @@
     </row>
     <row r="87" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>5</v>
@@ -2489,7 +2494,7 @@
     </row>
     <row r="88" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>27</v>
@@ -2503,7 +2508,7 @@
     </row>
     <row r="89" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>1</v>
@@ -2516,7 +2521,7 @@
     </row>
     <row r="90" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>2</v>
@@ -2529,7 +2534,7 @@
     </row>
     <row r="91" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>26</v>
@@ -2542,7 +2547,7 @@
     </row>
     <row r="92" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>8</v>
@@ -2555,7 +2560,7 @@
     </row>
     <row r="93" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>33</v>
@@ -2568,7 +2573,7 @@
     </row>
     <row r="94" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B94" t="s">
         <v>21</v>
@@ -2593,10 +2598,10 @@
     </row>
     <row r="96" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C96" s="2">
         <v>1.4999999999999999E-2</v>
@@ -2605,10 +2610,10 @@
     </row>
     <row r="97" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C97" s="2">
         <v>0.13</v>
@@ -2617,7 +2622,7 @@
     </row>
     <row r="98" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>1</v>
@@ -2629,10 +2634,10 @@
     </row>
     <row r="99" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C99" s="2">
         <v>0.08</v>
@@ -2641,7 +2646,7 @@
     </row>
     <row r="100" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>28</v>
@@ -2653,7 +2658,7 @@
     </row>
     <row r="101" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>23</v>
@@ -2665,7 +2670,7 @@
     </row>
     <row r="102" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>12</v>
@@ -2677,10 +2682,10 @@
     </row>
     <row r="103" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C103" s="2">
         <v>0.15</v>
@@ -2689,7 +2694,7 @@
     </row>
     <row r="104" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>15</v>
@@ -2716,7 +2721,7 @@
     </row>
     <row r="108" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>44</v>
@@ -2728,7 +2733,7 @@
     </row>
     <row r="109" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>10</v>
@@ -2740,7 +2745,7 @@
     </row>
     <row r="110" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>9</v>
@@ -2752,7 +2757,7 @@
     </row>
     <row r="111" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>45</v>
@@ -2764,7 +2769,7 @@
     </row>
     <row r="112" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>1</v>
@@ -2774,12 +2779,12 @@
         <v>7.8947368421052627E-2</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>3</v>
@@ -2789,12 +2794,12 @@
         <v>7.1052631578947367E-2</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>2</v>
@@ -2804,12 +2809,12 @@
         <v>3.428571428571428E-2</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>4</v>
@@ -2819,12 +2824,12 @@
         <v>2.571428571428571E-2</v>
       </c>
       <c r="D115" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>33</v>
@@ -2836,10 +2841,10 @@
     </row>
     <row r="117" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C117" s="2">
         <v>0.03</v>
@@ -2848,7 +2853,7 @@
     </row>
     <row r="118" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>22</v>
@@ -2860,7 +2865,7 @@
     </row>
     <row r="119" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>14</v>
@@ -2872,7 +2877,7 @@
     </row>
     <row r="120" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>5</v>
@@ -2884,7 +2889,7 @@
     </row>
     <row r="121" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>15</v>
@@ -2896,7 +2901,7 @@
     </row>
     <row r="122" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>10</v>
@@ -2908,7 +2913,7 @@
     </row>
     <row r="123" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>13</v>
@@ -2920,7 +2925,7 @@
     </row>
     <row r="124" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>17</v>
@@ -2932,7 +2937,7 @@
     </row>
     <row r="125" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>1</v>
@@ -2944,7 +2949,7 @@
     </row>
     <row r="126" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>3</v>
@@ -2956,7 +2961,7 @@
     </row>
     <row r="127" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>2</v>
@@ -2968,7 +2973,7 @@
     </row>
     <row r="128" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>4</v>
@@ -2980,7 +2985,7 @@
     </row>
     <row r="129" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>16</v>
@@ -2992,7 +2997,7 @@
     </row>
     <row r="130" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>11</v>
@@ -3004,7 +3009,7 @@
     </row>
     <row r="131" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>20</v>
@@ -3016,7 +3021,7 @@
     </row>
     <row r="132" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>18</v>
@@ -3028,7 +3033,7 @@
     </row>
     <row r="133" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>12</v>
@@ -3040,7 +3045,7 @@
     </row>
     <row r="134" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>14</v>
@@ -3052,7 +3057,7 @@
     </row>
     <row r="135" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>19</v>
@@ -3064,7 +3069,7 @@
     </row>
     <row r="136" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>5</v>
@@ -3076,7 +3081,7 @@
     </row>
     <row r="137" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>15</v>
@@ -3088,7 +3093,7 @@
     </row>
     <row r="138" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>9</v>
@@ -3100,7 +3105,7 @@
     </row>
     <row r="139" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>45</v>
@@ -3112,7 +3117,7 @@
     </row>
     <row r="140" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>1</v>
@@ -3122,12 +3127,12 @@
         <v>0.15789473684210525</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>3</v>
@@ -3137,12 +3142,12 @@
         <v>0.14210526315789473</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>2</v>
@@ -3152,12 +3157,12 @@
         <v>5.1428571428571421E-2</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>4</v>
@@ -3167,12 +3172,12 @@
         <v>3.8571428571428562E-2</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>33</v>
@@ -3184,10 +3189,10 @@
     </row>
     <row r="145" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C145" s="2">
         <v>0.04</v>
@@ -3196,7 +3201,7 @@
     </row>
     <row r="146" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>22</v>
@@ -3208,7 +3213,7 @@
     </row>
     <row r="147" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>23</v>
@@ -3220,7 +3225,7 @@
     </row>
     <row r="148" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>12</v>
@@ -3232,7 +3237,7 @@
     </row>
     <row r="149" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>5</v>
@@ -3244,10 +3249,10 @@
     </row>
     <row r="150" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B150" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="C150" s="2">
         <v>7.1999999999999995E-2</v>
@@ -3256,7 +3261,7 @@
     </row>
     <row r="151" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>1</v>
@@ -3268,7 +3273,7 @@
     </row>
     <row r="152" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>2</v>
@@ -3280,7 +3285,7 @@
     </row>
     <row r="153" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>33</v>
@@ -3293,7 +3298,7 @@
     </row>
     <row r="154" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>23</v>
@@ -3305,7 +3310,7 @@
     </row>
     <row r="155" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>14</v>
@@ -3317,7 +3322,7 @@
     </row>
     <row r="156" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>5</v>
@@ -3329,7 +3334,7 @@
     </row>
     <row r="157" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>1</v>
@@ -3341,7 +3346,7 @@
     </row>
     <row r="158" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>2</v>
@@ -3353,7 +3358,7 @@
     </row>
     <row r="159" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>26</v>
@@ -3365,7 +3370,7 @@
     </row>
     <row r="160" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>8</v>
@@ -3377,7 +3382,7 @@
     </row>
     <row r="161" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>12</v>
@@ -3389,7 +3394,7 @@
     </row>
     <row r="162" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>14</v>
@@ -3401,7 +3406,7 @@
     </row>
     <row r="163" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>5</v>
@@ -3413,7 +3418,7 @@
     </row>
     <row r="164" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>15</v>
@@ -3425,7 +3430,7 @@
     </row>
     <row r="165" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B165" t="s">
         <v>1</v>
@@ -3436,7 +3441,7 @@
     </row>
     <row r="166" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>5</v>
@@ -3447,7 +3452,7 @@
     </row>
     <row r="167" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>23</v>
@@ -3458,10 +3463,10 @@
     </row>
     <row r="168" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B168" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C168">
         <v>4.0000000000000001E-3</v>
@@ -3469,7 +3474,7 @@
     </row>
     <row r="169" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B169" t="s">
         <v>25</v>
@@ -3480,10 +3485,10 @@
     </row>
     <row r="170" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B170" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C170">
         <v>8.0000000000000002E-3</v>
@@ -3491,10 +3496,10 @@
     </row>
     <row r="171" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B171" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C171">
         <v>3.5999999999999997E-2</v>
@@ -3502,7 +3507,7 @@
     </row>
     <row r="172" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B172" t="s">
         <v>12</v>
@@ -3513,7 +3518,7 @@
     </row>
     <row r="173" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B173" t="s">
         <v>2</v>
@@ -3524,7 +3529,7 @@
     </row>
     <row r="174" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B174" t="s">
         <v>19</v>
@@ -3535,7 +3540,7 @@
     </row>
     <row r="175" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B175" t="s">
         <v>15</v>
@@ -3546,7 +3551,7 @@
     </row>
     <row r="176" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B176" t="s">
         <v>33</v>
@@ -3562,10 +3567,10 @@
     </row>
     <row r="178" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B178" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C178" s="13">
         <v>0.05</v>
@@ -3573,7 +3578,7 @@
     </row>
     <row r="179" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B179" t="s">
         <v>1</v>
@@ -3584,7 +3589,7 @@
     </row>
     <row r="180" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B180" t="s">
         <v>3</v>
@@ -3595,7 +3600,7 @@
     </row>
     <row r="181" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B181" t="s">
         <v>33</v>
@@ -3606,7 +3611,7 @@
     </row>
     <row r="182" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B182" t="s">
         <v>23</v>
@@ -3617,7 +3622,7 @@
     </row>
     <row r="183" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B183" t="s">
         <v>12</v>
@@ -3628,7 +3633,7 @@
     </row>
     <row r="184" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B184" t="s">
         <v>5</v>
@@ -3639,7 +3644,7 @@
     </row>
     <row r="185" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B185" t="s">
         <v>1</v>
@@ -3650,7 +3655,7 @@
     </row>
     <row r="186" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B186" t="s">
         <v>2</v>
@@ -3661,7 +3666,7 @@
     </row>
     <row r="187" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B187" t="s">
         <v>33</v>
@@ -3672,7 +3677,7 @@
     </row>
     <row r="188" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B188" t="s">
         <v>23</v>
@@ -3683,7 +3688,7 @@
     </row>
     <row r="189" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B189" t="s">
         <v>5</v>
@@ -3694,10 +3699,10 @@
     </row>
     <row r="190" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B190" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="C190" s="13">
         <v>0.12</v>
@@ -3705,10 +3710,10 @@
     </row>
     <row r="191" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C191" s="13">
         <v>0.02</v>
@@ -3716,7 +3721,7 @@
     </row>
     <row r="192" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>9</v>
@@ -3727,7 +3732,7 @@
     </row>
     <row r="193" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>1</v>
@@ -3738,7 +3743,7 @@
     </row>
     <row r="194" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>33</v>
@@ -3749,10 +3754,10 @@
     </row>
     <row r="195" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C195" s="13">
         <v>1.15E-2</v>
@@ -3760,7 +3765,7 @@
     </row>
     <row r="196" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>23</v>
@@ -3771,7 +3776,7 @@
     </row>
     <row r="197" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>1</v>
@@ -3782,7 +3787,7 @@
     </row>
     <row r="198" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>2</v>
@@ -3793,7 +3798,7 @@
     </row>
     <row r="199" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>33</v>
@@ -3804,7 +3809,7 @@
     </row>
     <row r="200" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>22</v>
@@ -3815,7 +3820,7 @@
     </row>
     <row r="201" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>23</v>
@@ -3827,7 +3832,7 @@
     </row>
     <row r="202" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>25</v>
@@ -3838,7 +3843,7 @@
     </row>
     <row r="203" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>5</v>
@@ -4758,7 +4763,7 @@
       <sortCondition ref="A1:A203"/>
     </sortState>
   </autoFilter>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D88" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
   </hyperlinks>
@@ -4769,8 +4774,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A162FC-7907-44C7-A909-E8E1323EC5F6}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:G300"/>
+  <dimension ref="A1:F300"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5546875" style="6" bestFit="1" customWidth="1"/>
@@ -4778,12 +4782,11 @@
     <col min="3" max="3" width="11.109375" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.88671875" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="100.6640625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="97.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="6"/>
+    <col min="6" max="6" width="97.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>167</v>
       </c>
@@ -4797,18 +4800,15 @@
         <v>170</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>154</v>
@@ -4817,19 +4817,16 @@
         <v>223</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G2" s="7"/>
-    </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>92</v>
@@ -4838,17 +4835,14 @@
         <v>9</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E3" s="10"/>
-      <c r="F3" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G3" s="7"/>
-    </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>81</v>
@@ -4857,17 +4851,14 @@
         <v>2</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E4" s="10"/>
-      <c r="F4" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>55</v>
@@ -4876,15 +4867,12 @@
         <v>1</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E5" s="10"/>
-      <c r="F5" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G5" s="7"/>
-    </row>
-    <row r="6" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>126</v>
       </c>
@@ -4898,14 +4886,11 @@
         <v>151</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>126</v>
       </c>
@@ -4919,12 +4904,9 @@
         <v>151</v>
       </c>
       <c r="E7" s="10"/>
-      <c r="F7" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G7" s="7"/>
-    </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>126</v>
       </c>
@@ -4938,12 +4920,9 @@
         <v>151</v>
       </c>
       <c r="E8" s="10"/>
-      <c r="F8" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:6" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>126</v>
       </c>
@@ -4957,19 +4936,16 @@
         <v>166</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>126</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C10" s="7">
         <v>1</v>
@@ -4979,13 +4955,10 @@
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>126</v>
       </c>
@@ -4999,14 +4972,11 @@
         <v>140</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G11" s="7"/>
-    </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>126</v>
       </c>
@@ -5020,12 +4990,9 @@
         <v>140</v>
       </c>
       <c r="E12" s="10"/>
-      <c r="F12" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G12" s="7"/>
-    </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>126</v>
       </c>
@@ -5039,12 +5006,9 @@
         <v>140</v>
       </c>
       <c r="E13" s="10"/>
-      <c r="F13" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G13" s="7"/>
-    </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>126</v>
       </c>
@@ -5058,12 +5022,9 @@
         <v>140</v>
       </c>
       <c r="E14" s="10"/>
-      <c r="F14" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G14" s="7"/>
-    </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>126</v>
       </c>
@@ -5077,12 +5038,9 @@
         <v>140</v>
       </c>
       <c r="E15" s="10"/>
-      <c r="F15" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G15" s="7"/>
-    </row>
-    <row r="16" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>126</v>
       </c>
@@ -5096,14 +5054,11 @@
         <v>125</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G16" s="7"/>
-    </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>126</v>
       </c>
@@ -5117,12 +5072,9 @@
         <v>125</v>
       </c>
       <c r="E17" s="10"/>
-      <c r="F17" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G17" s="7"/>
-    </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>126</v>
       </c>
@@ -5136,12 +5088,9 @@
         <v>125</v>
       </c>
       <c r="E18" s="10"/>
-      <c r="F18" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G18" s="7"/>
-    </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>126</v>
       </c>
@@ -5155,12 +5104,9 @@
         <v>125</v>
       </c>
       <c r="E19" s="10"/>
-      <c r="F19" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G19" s="7"/>
-    </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>126</v>
       </c>
@@ -5174,12 +5120,9 @@
         <v>125</v>
       </c>
       <c r="E20" s="10"/>
-      <c r="F20" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G20" s="7"/>
-    </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>117</v>
       </c>
@@ -5192,9 +5135,8 @@
       <c r="D21" s="7"/>
       <c r="E21" s="8"/>
       <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-    </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>117</v>
       </c>
@@ -5207,9 +5149,8 @@
       <c r="D22" s="7"/>
       <c r="E22" s="8"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>117</v>
       </c>
@@ -5222,9 +5163,8 @@
       <c r="D23" s="7"/>
       <c r="E23" s="8"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-    </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>117</v>
       </c>
@@ -5237,9 +5177,8 @@
       <c r="D24" s="7"/>
       <c r="E24" s="8"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>117</v>
       </c>
@@ -5252,9 +5191,8 @@
       <c r="D25" s="7"/>
       <c r="E25" s="8"/>
       <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-    </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>117</v>
       </c>
@@ -5267,9 +5205,8 @@
       <c r="D26" s="7"/>
       <c r="E26" s="8"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-    </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>117</v>
       </c>
@@ -5282,9 +5219,8 @@
       <c r="D27" s="7"/>
       <c r="E27" s="8"/>
       <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-    </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>117</v>
       </c>
@@ -5297,9 +5233,8 @@
       <c r="D28" s="7"/>
       <c r="E28" s="8"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-    </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>117</v>
       </c>
@@ -5312,9 +5247,8 @@
       <c r="D29" s="7"/>
       <c r="E29" s="8"/>
       <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-    </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>117</v>
       </c>
@@ -5327,9 +5261,8 @@
       <c r="D30" s="7"/>
       <c r="E30" s="8"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-    </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>117</v>
       </c>
@@ -5342,9 +5275,8 @@
       <c r="D31" s="7"/>
       <c r="E31" s="8"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-    </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>117</v>
       </c>
@@ -5357,9 +5289,8 @@
       <c r="D32" s="7"/>
       <c r="E32" s="8"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-    </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>117</v>
       </c>
@@ -5372,9 +5303,8 @@
       <c r="D33" s="7"/>
       <c r="E33" s="8"/>
       <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-    </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>117</v>
       </c>
@@ -5387,9 +5317,8 @@
       <c r="D34" s="7"/>
       <c r="E34" s="8"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-    </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>117</v>
       </c>
@@ -5402,9 +5331,8 @@
       <c r="D35" s="7"/>
       <c r="E35" s="8"/>
       <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-    </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>117</v>
       </c>
@@ -5417,9 +5345,8 @@
       <c r="D36" s="7"/>
       <c r="E36" s="8"/>
       <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-    </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>117</v>
       </c>
@@ -5432,9 +5359,8 @@
       <c r="D37" s="7"/>
       <c r="E37" s="8"/>
       <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-    </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>117</v>
       </c>
@@ -5447,9 +5373,8 @@
       <c r="D38" s="7"/>
       <c r="E38" s="8"/>
       <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-    </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>117</v>
       </c>
@@ -5462,9 +5387,8 @@
       <c r="D39" s="7"/>
       <c r="E39" s="8"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-    </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>117</v>
       </c>
@@ -5477,9 +5401,8 @@
       <c r="D40" s="7"/>
       <c r="E40" s="8"/>
       <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-    </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>117</v>
       </c>
@@ -5492,9 +5415,8 @@
       <c r="D41" s="7"/>
       <c r="E41" s="8"/>
       <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-    </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>117</v>
       </c>
@@ -5507,9 +5429,8 @@
       <c r="D42" s="7"/>
       <c r="E42" s="8"/>
       <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-    </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>117</v>
       </c>
@@ -5522,9 +5443,8 @@
       <c r="D43" s="7"/>
       <c r="E43" s="8"/>
       <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-    </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>117</v>
       </c>
@@ -5537,9 +5457,8 @@
       <c r="D44" s="7"/>
       <c r="E44" s="8"/>
       <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-    </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>117</v>
       </c>
@@ -5552,9 +5471,8 @@
       <c r="D45" s="7"/>
       <c r="E45" s="8"/>
       <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-    </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>117</v>
       </c>
@@ -5567,9 +5485,8 @@
       <c r="D46" s="7"/>
       <c r="E46" s="8"/>
       <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-    </row>
-    <row r="47" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>116</v>
       </c>
@@ -5580,17 +5497,14 @@
         <v>259</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G47" s="7"/>
-    </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+      <c r="F47" s="7"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>116</v>
       </c>
@@ -5601,15 +5515,12 @@
         <v>60</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E48" s="10"/>
-      <c r="F48" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G48" s="7"/>
-    </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F48" s="7"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>116</v>
       </c>
@@ -5620,15 +5531,12 @@
         <v>34</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E49" s="10"/>
-      <c r="F49" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G49" s="7"/>
-    </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F49" s="7"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>116</v>
       </c>
@@ -5639,15 +5547,12 @@
         <v>28</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E50" s="10"/>
-      <c r="F50" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G50" s="7"/>
-    </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F50" s="7"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>116</v>
       </c>
@@ -5658,15 +5563,12 @@
         <v>22</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E51" s="10"/>
-      <c r="F51" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G51" s="7"/>
-    </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F51" s="7"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>116</v>
       </c>
@@ -5677,15 +5579,12 @@
         <v>19</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E52" s="10"/>
-      <c r="F52" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G52" s="7"/>
-    </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F52" s="7"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>116</v>
       </c>
@@ -5696,15 +5595,12 @@
         <v>16</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E53" s="10"/>
-      <c r="F53" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G53" s="7"/>
-    </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F53" s="7"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>116</v>
       </c>
@@ -5715,15 +5611,12 @@
         <v>9</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E54" s="10"/>
-      <c r="F54" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G54" s="7"/>
-    </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F54" s="7"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>116</v>
       </c>
@@ -5734,15 +5627,12 @@
         <v>4</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E55" s="10"/>
-      <c r="F55" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G55" s="7"/>
-    </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F55" s="7"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>116</v>
       </c>
@@ -5753,15 +5643,12 @@
         <v>3</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E56" s="10"/>
-      <c r="F56" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G56" s="7"/>
-    </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F56" s="7"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>116</v>
       </c>
@@ -5772,15 +5659,12 @@
         <v>2</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E57" s="10"/>
-      <c r="F57" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G57" s="7"/>
-    </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F57" s="7"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>116</v>
       </c>
@@ -5791,15 +5675,12 @@
         <v>2</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E58" s="10"/>
-      <c r="F58" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G58" s="7"/>
-    </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F58" s="7"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>116</v>
       </c>
@@ -5810,15 +5691,12 @@
         <v>2</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E59" s="10"/>
-      <c r="F59" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G59" s="7"/>
-    </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F59" s="7"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>116</v>
       </c>
@@ -5829,15 +5707,12 @@
         <v>2</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E60" s="10"/>
-      <c r="F60" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G60" s="7"/>
-    </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F60" s="7"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>116</v>
       </c>
@@ -5848,15 +5723,12 @@
         <v>1</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E61" s="10"/>
-      <c r="F61" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G61" s="7"/>
-    </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F61" s="7"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>116</v>
       </c>
@@ -5867,15 +5739,12 @@
         <v>1</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E62" s="10"/>
-      <c r="F62" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G62" s="7"/>
-    </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F62" s="7"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>116</v>
       </c>
@@ -5886,15 +5755,12 @@
         <v>1</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E63" s="10"/>
-      <c r="F63" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G63" s="7"/>
-    </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F63" s="7"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
         <v>116</v>
       </c>
@@ -5905,15 +5771,12 @@
         <v>1</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E64" s="10"/>
-      <c r="F64" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G64" s="7"/>
-    </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F64" s="7"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
         <v>116</v>
       </c>
@@ -5924,15 +5787,12 @@
         <v>1</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E65" s="10"/>
-      <c r="F65" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G65" s="7"/>
-    </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F65" s="7"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>116</v>
       </c>
@@ -5943,15 +5803,12 @@
         <v>1</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E66" s="10"/>
-      <c r="F66" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G66" s="7"/>
-    </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F66" s="7"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>116</v>
       </c>
@@ -5962,15 +5819,12 @@
         <v>1</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E67" s="10"/>
-      <c r="F67" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G67" s="7"/>
-    </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F67" s="7"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
         <v>116</v>
       </c>
@@ -5981,15 +5835,12 @@
         <v>1</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E68" s="10"/>
-      <c r="F68" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G68" s="7"/>
-    </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F68" s="7"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
         <v>116</v>
       </c>
@@ -6000,15 +5851,12 @@
         <v>1</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E69" s="10"/>
-      <c r="F69" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G69" s="7"/>
-    </row>
-    <row r="70" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F69" s="7"/>
+    </row>
+    <row r="70" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
         <v>115</v>
       </c>
@@ -6019,15 +5867,14 @@
         <v>239</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F70" s="7"/>
-      <c r="G70" s="7"/>
-    </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
         <v>115</v>
       </c>
@@ -6038,13 +5885,12 @@
         <v>4</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E71" s="10"/>
       <c r="F71" s="7"/>
-      <c r="G71" s="7"/>
-    </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
         <v>115</v>
       </c>
@@ -6055,13 +5901,12 @@
         <v>4</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E72" s="10"/>
       <c r="F72" s="7"/>
-      <c r="G72" s="7"/>
-    </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
         <v>115</v>
       </c>
@@ -6072,13 +5917,12 @@
         <v>2</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E73" s="10"/>
       <c r="F73" s="7"/>
-      <c r="G73" s="7"/>
-    </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
         <v>115</v>
       </c>
@@ -6089,13 +5933,12 @@
         <v>1</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E74" s="10"/>
       <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
-    </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
         <v>115</v>
       </c>
@@ -6106,13 +5949,12 @@
         <v>1</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E75" s="10"/>
       <c r="F75" s="7"/>
-      <c r="G75" s="7"/>
-    </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
         <v>115</v>
       </c>
@@ -6123,13 +5965,12 @@
         <v>1</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E76" s="10"/>
       <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-    </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
         <v>115</v>
       </c>
@@ -6140,13 +5981,12 @@
         <v>1</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E77" s="10"/>
       <c r="F77" s="7"/>
-      <c r="G77" s="7"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:6" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
         <v>111</v>
       </c>
@@ -6157,11 +5997,12 @@
         <v>214</v>
       </c>
       <c r="D78" s="7"/>
-      <c r="E78" s="8"/>
+      <c r="E78" s="8" t="s">
+        <v>248</v>
+      </c>
       <c r="F78" s="7"/>
-      <c r="G78" s="7"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
         <v>111</v>
       </c>
@@ -6172,11 +6013,10 @@
         <v>11</v>
       </c>
       <c r="D79" s="7"/>
-      <c r="E79" s="8"/>
+      <c r="E79" s="10"/>
       <c r="F79" s="7"/>
-      <c r="G79" s="7"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
         <v>111</v>
       </c>
@@ -6187,11 +6027,10 @@
         <v>8</v>
       </c>
       <c r="D80" s="7"/>
-      <c r="E80" s="8"/>
+      <c r="E80" s="10"/>
       <c r="F80" s="7"/>
-      <c r="G80" s="7"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
         <v>111</v>
       </c>
@@ -6202,11 +6041,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="7"/>
-      <c r="E81" s="8"/>
+      <c r="E81" s="10"/>
       <c r="F81" s="7"/>
-      <c r="G81" s="7"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
         <v>111</v>
       </c>
@@ -6217,11 +6055,10 @@
         <v>2</v>
       </c>
       <c r="D82" s="7"/>
-      <c r="E82" s="8"/>
+      <c r="E82" s="10"/>
       <c r="F82" s="7"/>
-      <c r="G82" s="7"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
         <v>111</v>
       </c>
@@ -6232,11 +6069,10 @@
         <v>2</v>
       </c>
       <c r="D83" s="7"/>
-      <c r="E83" s="8"/>
+      <c r="E83" s="10"/>
       <c r="F83" s="7"/>
-      <c r="G83" s="7"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
         <v>111</v>
       </c>
@@ -6247,11 +6083,10 @@
         <v>2</v>
       </c>
       <c r="D84" s="7"/>
-      <c r="E84" s="8"/>
+      <c r="E84" s="10"/>
       <c r="F84" s="7"/>
-      <c r="G84" s="7"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>111</v>
       </c>
@@ -6262,11 +6097,10 @@
         <v>1</v>
       </c>
       <c r="D85" s="7"/>
-      <c r="E85" s="8"/>
+      <c r="E85" s="10"/>
       <c r="F85" s="7"/>
-      <c r="G85" s="7"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
         <v>111</v>
       </c>
@@ -6277,11 +6111,10 @@
         <v>1</v>
       </c>
       <c r="D86" s="7"/>
-      <c r="E86" s="8"/>
+      <c r="E86" s="10"/>
       <c r="F86" s="7"/>
-      <c r="G86" s="7"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
         <v>111</v>
       </c>
@@ -6292,11 +6125,10 @@
         <v>1</v>
       </c>
       <c r="D87" s="7"/>
-      <c r="E87" s="8"/>
+      <c r="E87" s="10"/>
       <c r="F87" s="7"/>
-      <c r="G87" s="7"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
         <v>111</v>
       </c>
@@ -6307,11 +6139,10 @@
         <v>1</v>
       </c>
       <c r="D88" s="7"/>
-      <c r="E88" s="8"/>
+      <c r="E88" s="10"/>
       <c r="F88" s="7"/>
-      <c r="G88" s="7"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
         <v>111</v>
       </c>
@@ -6322,11 +6153,10 @@
         <v>1</v>
       </c>
       <c r="D89" s="7"/>
-      <c r="E89" s="8"/>
+      <c r="E89" s="10"/>
       <c r="F89" s="7"/>
-      <c r="G89" s="7"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
         <v>111</v>
       </c>
@@ -6337,11 +6167,10 @@
         <v>1</v>
       </c>
       <c r="D90" s="7"/>
-      <c r="E90" s="8"/>
+      <c r="E90" s="10"/>
       <c r="F90" s="7"/>
-      <c r="G90" s="7"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
         <v>111</v>
       </c>
@@ -6352,11 +6181,10 @@
         <v>1</v>
       </c>
       <c r="D91" s="7"/>
-      <c r="E91" s="8"/>
+      <c r="E91" s="10"/>
       <c r="F91" s="7"/>
-      <c r="G91" s="7"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
         <v>111</v>
       </c>
@@ -6367,11 +6195,10 @@
         <v>1</v>
       </c>
       <c r="D92" s="7"/>
-      <c r="E92" s="8"/>
+      <c r="E92" s="10"/>
       <c r="F92" s="7"/>
-      <c r="G92" s="7"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
         <v>111</v>
       </c>
@@ -6382,11 +6209,10 @@
         <v>1</v>
       </c>
       <c r="D93" s="7"/>
-      <c r="E93" s="8"/>
+      <c r="E93" s="10"/>
       <c r="F93" s="7"/>
-      <c r="G93" s="7"/>
-    </row>
-    <row r="94" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
         <v>32</v>
       </c>
@@ -6397,15 +6223,14 @@
         <v>150</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F94" s="7"/>
-      <c r="G94" s="7"/>
-    </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
         <v>32</v>
       </c>
@@ -6416,13 +6241,12 @@
         <v>29</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E95" s="10"/>
       <c r="F95" s="7"/>
-      <c r="G95" s="7"/>
-    </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
         <v>32</v>
       </c>
@@ -6433,13 +6257,12 @@
         <v>5</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E96" s="10"/>
       <c r="F96" s="7"/>
-      <c r="G96" s="7"/>
-    </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
         <v>32</v>
       </c>
@@ -6450,13 +6273,12 @@
         <v>2</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E97" s="10"/>
       <c r="F97" s="7"/>
-      <c r="G97" s="7"/>
-    </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
         <v>32</v>
       </c>
@@ -6467,13 +6289,12 @@
         <v>1</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E98" s="10"/>
       <c r="F98" s="7"/>
-      <c r="G98" s="7"/>
-    </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
         <v>32</v>
       </c>
@@ -6484,13 +6305,12 @@
         <v>1</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E99" s="10"/>
       <c r="F99" s="7"/>
-      <c r="G99" s="7"/>
-    </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
         <v>32</v>
       </c>
@@ -6501,13 +6321,12 @@
         <v>1</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E100" s="10"/>
       <c r="F100" s="7"/>
-      <c r="G100" s="7"/>
-    </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
         <v>32</v>
       </c>
@@ -6518,13 +6337,12 @@
         <v>1</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E101" s="10"/>
       <c r="F101" s="7"/>
-      <c r="G101" s="7"/>
-    </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
         <v>32</v>
       </c>
@@ -6535,13 +6353,12 @@
         <v>1</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E102" s="10"/>
       <c r="F102" s="7"/>
-      <c r="G102" s="7"/>
-    </row>
-    <row r="103" spans="1:7" ht="66" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:6" ht="66" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
         <v>34</v>
       </c>
@@ -6552,15 +6369,14 @@
         <v>433</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F103" s="7"/>
-      <c r="G103" s="7"/>
-    </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
         <v>34</v>
       </c>
@@ -6571,13 +6387,12 @@
         <v>214</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E104" s="10"/>
       <c r="F104" s="7"/>
-      <c r="G104" s="7"/>
-    </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
         <v>34</v>
       </c>
@@ -6588,13 +6403,12 @@
         <v>50</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E105" s="10"/>
       <c r="F105" s="7"/>
-      <c r="G105" s="7"/>
-    </row>
-    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
         <v>34</v>
       </c>
@@ -6605,13 +6419,12 @@
         <v>31</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E106" s="10"/>
       <c r="F106" s="7"/>
-      <c r="G106" s="7"/>
-    </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
         <v>34</v>
       </c>
@@ -6622,13 +6435,12 @@
         <v>6</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E107" s="10"/>
       <c r="F107" s="7"/>
-      <c r="G107" s="7"/>
-    </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
         <v>34</v>
       </c>
@@ -6639,13 +6451,12 @@
         <v>1</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E108" s="10"/>
       <c r="F108" s="7"/>
-      <c r="G108" s="7"/>
-    </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
         <v>34</v>
       </c>
@@ -6656,13 +6467,12 @@
         <v>1</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E109" s="10"/>
       <c r="F109" s="7"/>
-      <c r="G109" s="7"/>
-    </row>
-    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
         <v>34</v>
       </c>
@@ -6673,13 +6483,12 @@
         <v>1</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E110" s="10"/>
       <c r="F110" s="7"/>
-      <c r="G110" s="7"/>
-    </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
         <v>34</v>
       </c>
@@ -6690,13 +6499,12 @@
         <v>1</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E111" s="10"/>
       <c r="F111" s="7"/>
-      <c r="G111" s="7"/>
-    </row>
-    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
         <v>34</v>
       </c>
@@ -6707,13 +6515,12 @@
         <v>1</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E112" s="10"/>
       <c r="F112" s="7"/>
-      <c r="G112" s="7"/>
-    </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
         <v>34</v>
       </c>
@@ -6724,13 +6531,12 @@
         <v>1</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E113" s="10"/>
       <c r="F113" s="7"/>
-      <c r="G113" s="7"/>
-    </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
         <v>34</v>
       </c>
@@ -6741,13 +6547,12 @@
         <v>1</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E114" s="10"/>
       <c r="F114" s="7"/>
-      <c r="G114" s="7"/>
-    </row>
-    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
         <v>34</v>
       </c>
@@ -6758,13 +6563,12 @@
         <v>1</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E115" s="10"/>
       <c r="F115" s="7"/>
-      <c r="G115" s="7"/>
-    </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
         <v>34</v>
       </c>
@@ -6775,13 +6579,12 @@
         <v>1</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E116" s="10"/>
       <c r="F116" s="7"/>
-      <c r="G116" s="7"/>
-    </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
         <v>34</v>
       </c>
@@ -6792,13 +6595,12 @@
         <v>1</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E117" s="10"/>
       <c r="F117" s="7"/>
-      <c r="G117" s="7"/>
-    </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
         <v>34</v>
       </c>
@@ -6809,13 +6611,12 @@
         <v>1</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E118" s="10"/>
       <c r="F118" s="7"/>
-      <c r="G118" s="7"/>
-    </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
         <v>34</v>
       </c>
@@ -6826,13 +6627,12 @@
         <v>1</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E119" s="10"/>
       <c r="F119" s="7"/>
-      <c r="G119" s="7"/>
-    </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
         <v>38</v>
       </c>
@@ -6845,9 +6645,8 @@
       <c r="D120" s="7"/>
       <c r="E120" s="8"/>
       <c r="F120" s="7"/>
-      <c r="G120" s="7"/>
-    </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
         <v>38</v>
       </c>
@@ -6860,9 +6659,8 @@
       <c r="D121" s="7"/>
       <c r="E121" s="8"/>
       <c r="F121" s="7"/>
-      <c r="G121" s="7"/>
-    </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
         <v>38</v>
       </c>
@@ -6875,9 +6673,8 @@
       <c r="D122" s="7"/>
       <c r="E122" s="8"/>
       <c r="F122" s="7"/>
-      <c r="G122" s="7"/>
-    </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
         <v>38</v>
       </c>
@@ -6890,9 +6687,8 @@
       <c r="D123" s="7"/>
       <c r="E123" s="8"/>
       <c r="F123" s="7"/>
-      <c r="G123" s="7"/>
-    </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
         <v>38</v>
       </c>
@@ -6905,9 +6701,8 @@
       <c r="D124" s="7"/>
       <c r="E124" s="8"/>
       <c r="F124" s="7"/>
-      <c r="G124" s="7"/>
-    </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
         <v>38</v>
       </c>
@@ -6920,9 +6715,8 @@
       <c r="D125" s="7"/>
       <c r="E125" s="8"/>
       <c r="F125" s="7"/>
-      <c r="G125" s="7"/>
-    </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
         <v>38</v>
       </c>
@@ -6935,9 +6729,8 @@
       <c r="D126" s="7"/>
       <c r="E126" s="8"/>
       <c r="F126" s="7"/>
-      <c r="G126" s="7"/>
-    </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
         <v>38</v>
       </c>
@@ -6950,9 +6743,8 @@
       <c r="D127" s="7"/>
       <c r="E127" s="8"/>
       <c r="F127" s="7"/>
-      <c r="G127" s="7"/>
-    </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
         <v>38</v>
       </c>
@@ -6965,9 +6757,8 @@
       <c r="D128" s="7"/>
       <c r="E128" s="8"/>
       <c r="F128" s="7"/>
-      <c r="G128" s="7"/>
-    </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
         <v>38</v>
       </c>
@@ -6980,9 +6771,8 @@
       <c r="D129" s="7"/>
       <c r="E129" s="8"/>
       <c r="F129" s="7"/>
-      <c r="G129" s="7"/>
-    </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
         <v>38</v>
       </c>
@@ -6995,9 +6785,8 @@
       <c r="D130" s="7"/>
       <c r="E130" s="8"/>
       <c r="F130" s="7"/>
-      <c r="G130" s="7"/>
-    </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
         <v>38</v>
       </c>
@@ -7010,9 +6799,8 @@
       <c r="D131" s="7"/>
       <c r="E131" s="8"/>
       <c r="F131" s="7"/>
-      <c r="G131" s="7"/>
-    </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
         <v>38</v>
       </c>
@@ -7025,9 +6813,8 @@
       <c r="D132" s="7"/>
       <c r="E132" s="8"/>
       <c r="F132" s="7"/>
-      <c r="G132" s="7"/>
-    </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
         <v>38</v>
       </c>
@@ -7040,9 +6827,8 @@
       <c r="D133" s="7"/>
       <c r="E133" s="8"/>
       <c r="F133" s="7"/>
-      <c r="G133" s="7"/>
-    </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
         <v>38</v>
       </c>
@@ -7055,9 +6841,8 @@
       <c r="D134" s="7"/>
       <c r="E134" s="8"/>
       <c r="F134" s="7"/>
-      <c r="G134" s="7"/>
-    </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
         <v>38</v>
       </c>
@@ -7070,9 +6855,8 @@
       <c r="D135" s="7"/>
       <c r="E135" s="8"/>
       <c r="F135" s="7"/>
-      <c r="G135" s="7"/>
-    </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
         <v>38</v>
       </c>
@@ -7085,9 +6869,8 @@
       <c r="D136" s="7"/>
       <c r="E136" s="8"/>
       <c r="F136" s="7"/>
-      <c r="G136" s="7"/>
-    </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
         <v>38</v>
       </c>
@@ -7100,9 +6883,8 @@
       <c r="D137" s="7"/>
       <c r="E137" s="8"/>
       <c r="F137" s="7"/>
-      <c r="G137" s="7"/>
-    </row>
-    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
         <v>38</v>
       </c>
@@ -7115,9 +6897,8 @@
       <c r="D138" s="7"/>
       <c r="E138" s="8"/>
       <c r="F138" s="7"/>
-      <c r="G138" s="7"/>
-    </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
         <v>38</v>
       </c>
@@ -7130,9 +6911,8 @@
       <c r="D139" s="7"/>
       <c r="E139" s="8"/>
       <c r="F139" s="7"/>
-      <c r="G139" s="7"/>
-    </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
         <v>38</v>
       </c>
@@ -7145,9 +6925,8 @@
       <c r="D140" s="7"/>
       <c r="E140" s="8"/>
       <c r="F140" s="7"/>
-      <c r="G140" s="7"/>
-    </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
         <v>38</v>
       </c>
@@ -7160,9 +6939,8 @@
       <c r="D141" s="7"/>
       <c r="E141" s="8"/>
       <c r="F141" s="7"/>
-      <c r="G141" s="7"/>
-    </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
         <v>38</v>
       </c>
@@ -7175,9 +6953,8 @@
       <c r="D142" s="7"/>
       <c r="E142" s="8"/>
       <c r="F142" s="7"/>
-      <c r="G142" s="7"/>
-    </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
         <v>35</v>
       </c>
@@ -7190,9 +6967,8 @@
       <c r="D143" s="7"/>
       <c r="E143" s="8"/>
       <c r="F143" s="7"/>
-      <c r="G143" s="7"/>
-    </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
         <v>35</v>
       </c>
@@ -7205,9 +6981,8 @@
       <c r="D144" s="7"/>
       <c r="E144" s="8"/>
       <c r="F144" s="7"/>
-      <c r="G144" s="7"/>
-    </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
         <v>35</v>
       </c>
@@ -7220,9 +6995,8 @@
       <c r="D145" s="7"/>
       <c r="E145" s="8"/>
       <c r="F145" s="7"/>
-      <c r="G145" s="7"/>
-    </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
         <v>35</v>
       </c>
@@ -7235,9 +7009,8 @@
       <c r="D146" s="7"/>
       <c r="E146" s="8"/>
       <c r="F146" s="7"/>
-      <c r="G146" s="7"/>
-    </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
         <v>35</v>
       </c>
@@ -7250,9 +7023,8 @@
       <c r="D147" s="7"/>
       <c r="E147" s="8"/>
       <c r="F147" s="7"/>
-      <c r="G147" s="7"/>
-    </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
         <v>35</v>
       </c>
@@ -7265,9 +7037,8 @@
       <c r="D148" s="7"/>
       <c r="E148" s="8"/>
       <c r="F148" s="7"/>
-      <c r="G148" s="7"/>
-    </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
         <v>35</v>
       </c>
@@ -7280,9 +7051,8 @@
       <c r="D149" s="7"/>
       <c r="E149" s="8"/>
       <c r="F149" s="7"/>
-      <c r="G149" s="7"/>
-    </row>
-    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
         <v>35</v>
       </c>
@@ -7295,14 +7065,13 @@
       <c r="D150" s="7"/>
       <c r="E150" s="8"/>
       <c r="F150" s="7"/>
-      <c r="G150" s="7"/>
-    </row>
-    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C151" s="7">
         <v>1</v>
@@ -7310,9 +7079,8 @@
       <c r="D151" s="7"/>
       <c r="E151" s="8"/>
       <c r="F151" s="7"/>
-      <c r="G151" s="7"/>
-    </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
         <v>35</v>
       </c>
@@ -7325,9 +7093,8 @@
       <c r="D152" s="7"/>
       <c r="E152" s="8"/>
       <c r="F152" s="7"/>
-      <c r="G152" s="7"/>
-    </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
         <v>35</v>
       </c>
@@ -7340,9 +7107,8 @@
       <c r="D153" s="7"/>
       <c r="E153" s="8"/>
       <c r="F153" s="7"/>
-      <c r="G153" s="7"/>
-    </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
         <v>35</v>
       </c>
@@ -7355,9 +7121,8 @@
       <c r="D154" s="7"/>
       <c r="E154" s="8"/>
       <c r="F154" s="7"/>
-      <c r="G154" s="7"/>
-    </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
         <v>35</v>
       </c>
@@ -7370,9 +7135,8 @@
       <c r="D155" s="7"/>
       <c r="E155" s="8"/>
       <c r="F155" s="7"/>
-      <c r="G155" s="7"/>
-    </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
         <v>35</v>
       </c>
@@ -7385,9 +7149,8 @@
       <c r="D156" s="7"/>
       <c r="E156" s="8"/>
       <c r="F156" s="7"/>
-      <c r="G156" s="7"/>
-    </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
         <v>35</v>
       </c>
@@ -7400,9 +7163,8 @@
       <c r="D157" s="7"/>
       <c r="E157" s="8"/>
       <c r="F157" s="7"/>
-      <c r="G157" s="7"/>
-    </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
         <v>36</v>
       </c>
@@ -7415,9 +7177,8 @@
       <c r="D158" s="7"/>
       <c r="E158" s="8"/>
       <c r="F158" s="7"/>
-      <c r="G158" s="7"/>
-    </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
         <v>36</v>
       </c>
@@ -7430,9 +7191,8 @@
       <c r="D159" s="7"/>
       <c r="E159" s="8"/>
       <c r="F159" s="7"/>
-      <c r="G159" s="7"/>
-    </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
         <v>36</v>
       </c>
@@ -7445,9 +7205,8 @@
       <c r="D160" s="7"/>
       <c r="E160" s="8"/>
       <c r="F160" s="7"/>
-      <c r="G160" s="7"/>
-    </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
         <v>36</v>
       </c>
@@ -7460,9 +7219,8 @@
       <c r="D161" s="7"/>
       <c r="E161" s="8"/>
       <c r="F161" s="7"/>
-      <c r="G161" s="7"/>
-    </row>
-    <row r="162" spans="1:7" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="1:6" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
         <v>91</v>
       </c>
@@ -7476,14 +7234,11 @@
         <v>140</v>
       </c>
       <c r="E162" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="F162" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G162" s="7"/>
-    </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="F162" s="7"/>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
         <v>91</v>
       </c>
@@ -7497,11 +7252,8 @@
         <v>140</v>
       </c>
       <c r="E163" s="10"/>
-      <c r="F163" s="7" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
         <v>91</v>
       </c>
@@ -7515,12 +7267,9 @@
         <v>140</v>
       </c>
       <c r="E164" s="10"/>
-      <c r="F164" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G164" s="7"/>
-    </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F164" s="7"/>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
         <v>91</v>
       </c>
@@ -7534,12 +7283,9 @@
         <v>140</v>
       </c>
       <c r="E165" s="10"/>
-      <c r="F165" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G165" s="7"/>
-    </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F165" s="7"/>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
         <v>91</v>
       </c>
@@ -7553,12 +7299,9 @@
         <v>140</v>
       </c>
       <c r="E166" s="10"/>
-      <c r="F166" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G166" s="7"/>
-    </row>
-    <row r="167" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F166" s="7"/>
+    </row>
+    <row r="167" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
         <v>91</v>
       </c>
@@ -7569,17 +7312,14 @@
         <v>34</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E167" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F167" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G167" s="7"/>
-    </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="F167" s="7"/>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
         <v>91</v>
       </c>
@@ -7590,15 +7330,12 @@
         <v>23</v>
       </c>
       <c r="D168" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E168" s="10"/>
-      <c r="F168" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G168" s="7"/>
-    </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F168" s="7"/>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
         <v>91</v>
       </c>
@@ -7609,15 +7346,12 @@
         <v>23</v>
       </c>
       <c r="D169" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E169" s="10"/>
-      <c r="F169" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G169" s="7"/>
-    </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F169" s="7"/>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
         <v>91</v>
       </c>
@@ -7628,15 +7362,12 @@
         <v>19</v>
       </c>
       <c r="D170" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E170" s="10"/>
-      <c r="F170" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G170" s="7"/>
-    </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F170" s="7"/>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
         <v>91</v>
       </c>
@@ -7647,15 +7378,12 @@
         <v>4</v>
       </c>
       <c r="D171" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E171" s="10"/>
-      <c r="F171" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G171" s="7"/>
-    </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F171" s="7"/>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
         <v>91</v>
       </c>
@@ -7666,15 +7394,12 @@
         <v>1</v>
       </c>
       <c r="D172" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E172" s="10"/>
-      <c r="F172" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G172" s="7"/>
-    </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F172" s="7"/>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
         <v>91</v>
       </c>
@@ -7685,15 +7410,12 @@
         <v>1</v>
       </c>
       <c r="D173" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E173" s="10"/>
-      <c r="F173" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G173" s="7"/>
-    </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F173" s="7"/>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
         <v>91</v>
       </c>
@@ -7704,15 +7426,12 @@
         <v>1</v>
       </c>
       <c r="D174" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E174" s="10"/>
-      <c r="F174" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G174" s="7"/>
-    </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F174" s="7"/>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
         <v>91</v>
       </c>
@@ -7723,15 +7442,12 @@
         <v>1</v>
       </c>
       <c r="D175" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E175" s="10"/>
-      <c r="F175" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G175" s="7"/>
-    </row>
-    <row r="176" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F175" s="7"/>
+    </row>
+    <row r="176" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
         <v>91</v>
       </c>
@@ -7745,14 +7461,11 @@
         <v>166</v>
       </c>
       <c r="E176" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="F176" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G176" s="7"/>
-    </row>
-    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+      <c r="F176" s="7"/>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
         <v>91</v>
       </c>
@@ -7766,12 +7479,9 @@
         <v>166</v>
       </c>
       <c r="E177" s="10"/>
-      <c r="F177" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G177" s="7"/>
-    </row>
-    <row r="178" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F177" s="7"/>
+    </row>
+    <row r="178" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
         <v>80</v>
       </c>
@@ -7782,17 +7492,14 @@
         <v>134</v>
       </c>
       <c r="D178" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E178" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="E178" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="F178" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G178" s="7"/>
-    </row>
-    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F178" s="7"/>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
         <v>80</v>
       </c>
@@ -7803,15 +7510,12 @@
         <v>76</v>
       </c>
       <c r="D179" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E179" s="10"/>
-      <c r="F179" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G179" s="7"/>
-    </row>
-    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F179" s="7"/>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
         <v>80</v>
       </c>
@@ -7822,15 +7526,12 @@
         <v>17</v>
       </c>
       <c r="D180" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E180" s="10"/>
-      <c r="F180" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G180" s="7"/>
-    </row>
-    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F180" s="7"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
         <v>80</v>
       </c>
@@ -7841,15 +7542,12 @@
         <v>2</v>
       </c>
       <c r="D181" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E181" s="10"/>
-      <c r="F181" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G181" s="7"/>
-    </row>
-    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F181" s="7"/>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
         <v>80</v>
       </c>
@@ -7860,15 +7558,12 @@
         <v>1</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E182" s="10"/>
-      <c r="F182" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G182" s="7"/>
-    </row>
-    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F182" s="7"/>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
         <v>80</v>
       </c>
@@ -7879,15 +7574,12 @@
         <v>1</v>
       </c>
       <c r="D183" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E183" s="10"/>
-      <c r="F183" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G183" s="7"/>
-    </row>
-    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F183" s="7"/>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
         <v>80</v>
       </c>
@@ -7898,15 +7590,12 @@
         <v>1</v>
       </c>
       <c r="D184" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E184" s="10"/>
-      <c r="F184" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G184" s="7"/>
-    </row>
-    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F184" s="7"/>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
         <v>80</v>
       </c>
@@ -7917,15 +7606,12 @@
         <v>1</v>
       </c>
       <c r="D185" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E185" s="10"/>
-      <c r="F185" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G185" s="7"/>
-    </row>
-    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F185" s="7"/>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
         <v>80</v>
       </c>
@@ -7936,15 +7622,12 @@
         <v>1</v>
       </c>
       <c r="D186" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E186" s="10"/>
-      <c r="F186" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G186" s="7"/>
-    </row>
-    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F186" s="7"/>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
         <v>80</v>
       </c>
@@ -7955,15 +7638,12 @@
         <v>1</v>
       </c>
       <c r="D187" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E187" s="10"/>
-      <c r="F187" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G187" s="7"/>
-    </row>
-    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F187" s="7"/>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
         <v>80</v>
       </c>
@@ -7974,15 +7654,12 @@
         <v>1</v>
       </c>
       <c r="D188" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E188" s="10"/>
-      <c r="F188" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G188" s="7"/>
-    </row>
-    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F188" s="7"/>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
         <v>80</v>
       </c>
@@ -7993,15 +7670,12 @@
         <v>1</v>
       </c>
       <c r="D189" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E189" s="10"/>
-      <c r="F189" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G189" s="7"/>
-    </row>
-    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F189" s="7"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="7" t="s">
         <v>80</v>
       </c>
@@ -8012,15 +7686,12 @@
         <v>1</v>
       </c>
       <c r="D190" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E190" s="10"/>
-      <c r="F190" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G190" s="7"/>
-    </row>
-    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F190" s="7"/>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
         <v>80</v>
       </c>
@@ -8031,15 +7702,12 @@
         <v>1</v>
       </c>
       <c r="D191" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E191" s="10"/>
-      <c r="F191" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G191" s="7"/>
-    </row>
-    <row r="192" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F191" s="7"/>
+    </row>
+    <row r="192" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A192" s="7" t="s">
         <v>80</v>
       </c>
@@ -8050,15 +7718,14 @@
         <v>59</v>
       </c>
       <c r="D192" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E192" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F192" s="7"/>
-      <c r="G192" s="7"/>
-    </row>
-    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
         <v>80</v>
       </c>
@@ -8069,13 +7736,12 @@
         <v>40</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E193" s="10"/>
       <c r="F193" s="7"/>
-      <c r="G193" s="7"/>
-    </row>
-    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="7" t="s">
         <v>80</v>
       </c>
@@ -8086,13 +7752,12 @@
         <v>26</v>
       </c>
       <c r="D194" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E194" s="10"/>
       <c r="F194" s="7"/>
-      <c r="G194" s="7"/>
-    </row>
-    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
         <v>80</v>
       </c>
@@ -8103,13 +7768,12 @@
         <v>25</v>
       </c>
       <c r="D195" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E195" s="10"/>
       <c r="F195" s="7"/>
-      <c r="G195" s="7"/>
-    </row>
-    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="7" t="s">
         <v>80</v>
       </c>
@@ -8120,13 +7784,12 @@
         <v>23</v>
       </c>
       <c r="D196" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E196" s="10"/>
       <c r="F196" s="7"/>
-      <c r="G196" s="7"/>
-    </row>
-    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
         <v>80</v>
       </c>
@@ -8137,13 +7800,12 @@
         <v>18</v>
       </c>
       <c r="D197" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E197" s="10"/>
       <c r="F197" s="7"/>
-      <c r="G197" s="7"/>
-    </row>
-    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
         <v>80</v>
       </c>
@@ -8154,13 +7816,12 @@
         <v>14</v>
       </c>
       <c r="D198" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E198" s="10"/>
       <c r="F198" s="7"/>
-      <c r="G198" s="7"/>
-    </row>
-    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
         <v>80</v>
       </c>
@@ -8171,13 +7832,12 @@
         <v>14</v>
       </c>
       <c r="D199" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E199" s="10"/>
       <c r="F199" s="7"/>
-      <c r="G199" s="7"/>
-    </row>
-    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
         <v>80</v>
       </c>
@@ -8188,13 +7848,12 @@
         <v>10</v>
       </c>
       <c r="D200" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E200" s="10"/>
       <c r="F200" s="7"/>
-      <c r="G200" s="7"/>
-    </row>
-    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
         <v>80</v>
       </c>
@@ -8205,13 +7864,12 @@
         <v>9</v>
       </c>
       <c r="D201" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E201" s="10"/>
       <c r="F201" s="7"/>
-      <c r="G201" s="7"/>
-    </row>
-    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
         <v>80</v>
       </c>
@@ -8222,13 +7880,12 @@
         <v>3</v>
       </c>
       <c r="D202" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E202" s="10"/>
       <c r="F202" s="7"/>
-      <c r="G202" s="7"/>
-    </row>
-    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
         <v>80</v>
       </c>
@@ -8239,13 +7896,12 @@
         <v>3</v>
       </c>
       <c r="D203" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E203" s="10"/>
       <c r="F203" s="7"/>
-      <c r="G203" s="7"/>
-    </row>
-    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
         <v>80</v>
       </c>
@@ -8256,13 +7912,12 @@
         <v>2</v>
       </c>
       <c r="D204" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E204" s="10"/>
       <c r="F204" s="7"/>
-      <c r="G204" s="7"/>
-    </row>
-    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
         <v>80</v>
       </c>
@@ -8273,13 +7928,12 @@
         <v>2</v>
       </c>
       <c r="D205" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E205" s="10"/>
       <c r="F205" s="7"/>
-      <c r="G205" s="7"/>
-    </row>
-    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="7" t="s">
         <v>80</v>
       </c>
@@ -8290,13 +7944,12 @@
         <v>1</v>
       </c>
       <c r="D206" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E206" s="10"/>
       <c r="F206" s="7"/>
-      <c r="G206" s="7"/>
-    </row>
-    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
         <v>80</v>
       </c>
@@ -8307,13 +7960,12 @@
         <v>1</v>
       </c>
       <c r="D207" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E207" s="10"/>
       <c r="F207" s="7"/>
-      <c r="G207" s="7"/>
-    </row>
-    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="7" t="s">
         <v>80</v>
       </c>
@@ -8324,13 +7976,12 @@
         <v>1</v>
       </c>
       <c r="D208" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E208" s="10"/>
       <c r="F208" s="7"/>
-      <c r="G208" s="7"/>
-    </row>
-    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
         <v>80</v>
       </c>
@@ -8341,13 +7992,12 @@
         <v>1</v>
       </c>
       <c r="D209" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E209" s="10"/>
       <c r="F209" s="7"/>
-      <c r="G209" s="7"/>
-    </row>
-    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="7" t="s">
         <v>40</v>
       </c>
@@ -8358,15 +8008,14 @@
         <v>542</v>
       </c>
       <c r="D210" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E210" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F210" s="7"/>
-      <c r="G210" s="7"/>
-    </row>
-    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
         <v>40</v>
       </c>
@@ -8377,13 +8026,12 @@
         <v>418</v>
       </c>
       <c r="D211" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E211" s="10"/>
       <c r="F211" s="7"/>
-      <c r="G211" s="7"/>
-    </row>
-    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="7" t="s">
         <v>40</v>
       </c>
@@ -8394,13 +8042,12 @@
         <v>292</v>
       </c>
       <c r="D212" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E212" s="10"/>
       <c r="F212" s="7"/>
-      <c r="G212" s="7"/>
-    </row>
-    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
         <v>40</v>
       </c>
@@ -8411,13 +8058,12 @@
         <v>203</v>
       </c>
       <c r="D213" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E213" s="10"/>
       <c r="F213" s="7"/>
-      <c r="G213" s="7"/>
-    </row>
-    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="7" t="s">
         <v>40</v>
       </c>
@@ -8428,13 +8074,12 @@
         <v>151</v>
       </c>
       <c r="D214" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E214" s="10"/>
       <c r="F214" s="7"/>
-      <c r="G214" s="7"/>
-    </row>
-    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="7" t="s">
         <v>40</v>
       </c>
@@ -8445,13 +8090,12 @@
         <v>116</v>
       </c>
       <c r="D215" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E215" s="10"/>
       <c r="F215" s="7"/>
-      <c r="G215" s="7"/>
-    </row>
-    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="7" t="s">
         <v>40</v>
       </c>
@@ -8462,13 +8106,12 @@
         <v>96</v>
       </c>
       <c r="D216" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E216" s="10"/>
       <c r="F216" s="7"/>
-      <c r="G216" s="7"/>
-    </row>
-    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="7" t="s">
         <v>40</v>
       </c>
@@ -8479,13 +8122,12 @@
         <v>54</v>
       </c>
       <c r="D217" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E217" s="10"/>
       <c r="F217" s="7"/>
-      <c r="G217" s="7"/>
-    </row>
-    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="7" t="s">
         <v>40</v>
       </c>
@@ -8496,13 +8138,12 @@
         <v>51</v>
       </c>
       <c r="D218" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E218" s="10"/>
       <c r="F218" s="7"/>
-      <c r="G218" s="7"/>
-    </row>
-    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="7" t="s">
         <v>40</v>
       </c>
@@ -8513,13 +8154,12 @@
         <v>23</v>
       </c>
       <c r="D219" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E219" s="10"/>
       <c r="F219" s="7"/>
-      <c r="G219" s="7"/>
-    </row>
-    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="7" t="s">
         <v>40</v>
       </c>
@@ -8530,13 +8170,12 @@
         <v>6</v>
       </c>
       <c r="D220" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E220" s="10"/>
       <c r="F220" s="7"/>
-      <c r="G220" s="7"/>
-    </row>
-    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
         <v>40</v>
       </c>
@@ -8547,13 +8186,12 @@
         <v>2</v>
       </c>
       <c r="D221" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E221" s="10"/>
       <c r="F221" s="7"/>
-      <c r="G221" s="7"/>
-    </row>
-    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="7" t="s">
         <v>40</v>
       </c>
@@ -8564,13 +8202,12 @@
         <v>1</v>
       </c>
       <c r="D222" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E222" s="10"/>
       <c r="F222" s="7"/>
-      <c r="G222" s="7"/>
-    </row>
-    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="7" t="s">
         <v>40</v>
       </c>
@@ -8581,13 +8218,12 @@
         <v>1</v>
       </c>
       <c r="D223" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E223" s="10"/>
       <c r="F223" s="7"/>
-      <c r="G223" s="7"/>
-    </row>
-    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="7" t="s">
         <v>40</v>
       </c>
@@ -8598,13 +8234,12 @@
         <v>1</v>
       </c>
       <c r="D224" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E224" s="10"/>
       <c r="F224" s="7"/>
-      <c r="G224" s="7"/>
-    </row>
-    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
         <v>40</v>
       </c>
@@ -8615,13 +8250,12 @@
         <v>1</v>
       </c>
       <c r="D225" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E225" s="10"/>
       <c r="F225" s="7"/>
-      <c r="G225" s="7"/>
-    </row>
-    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="7" t="s">
         <v>40</v>
       </c>
@@ -8632,13 +8266,12 @@
         <v>1</v>
       </c>
       <c r="D226" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E226" s="10"/>
       <c r="F226" s="7"/>
-      <c r="G226" s="7"/>
-    </row>
-    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
         <v>40</v>
       </c>
@@ -8649,13 +8282,12 @@
         <v>1</v>
       </c>
       <c r="D227" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E227" s="10"/>
       <c r="F227" s="7"/>
-      <c r="G227" s="7"/>
-    </row>
-    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="7" t="s">
         <v>40</v>
       </c>
@@ -8666,13 +8298,12 @@
         <v>1</v>
       </c>
       <c r="D228" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E228" s="10"/>
       <c r="F228" s="7"/>
-      <c r="G228" s="7"/>
-    </row>
-    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
         <v>40</v>
       </c>
@@ -8683,13 +8314,12 @@
         <v>1</v>
       </c>
       <c r="D229" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E229" s="10"/>
       <c r="F229" s="7"/>
-      <c r="G229" s="7"/>
-    </row>
-    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="7" t="s">
         <v>37</v>
       </c>
@@ -8702,9 +8332,8 @@
       <c r="D230" s="7"/>
       <c r="E230" s="8"/>
       <c r="F230" s="7"/>
-      <c r="G230" s="7"/>
-    </row>
-    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
         <v>37</v>
       </c>
@@ -8717,9 +8346,8 @@
       <c r="D231" s="7"/>
       <c r="E231" s="8"/>
       <c r="F231" s="7"/>
-      <c r="G231" s="7"/>
-    </row>
-    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="7" t="s">
         <v>37</v>
       </c>
@@ -8732,9 +8360,8 @@
       <c r="D232" s="7"/>
       <c r="E232" s="8"/>
       <c r="F232" s="7"/>
-      <c r="G232" s="7"/>
-    </row>
-    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="7" t="s">
         <v>37</v>
       </c>
@@ -8747,9 +8374,8 @@
       <c r="D233" s="7"/>
       <c r="E233" s="8"/>
       <c r="F233" s="7"/>
-      <c r="G233" s="7"/>
-    </row>
-    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="7" t="s">
         <v>37</v>
       </c>
@@ -8762,9 +8388,8 @@
       <c r="D234" s="7"/>
       <c r="E234" s="8"/>
       <c r="F234" s="7"/>
-      <c r="G234" s="7"/>
-    </row>
-    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="7" t="s">
         <v>37</v>
       </c>
@@ -8777,9 +8402,8 @@
       <c r="D235" s="7"/>
       <c r="E235" s="8"/>
       <c r="F235" s="7"/>
-      <c r="G235" s="7"/>
-    </row>
-    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="7" t="s">
         <v>37</v>
       </c>
@@ -8792,9 +8416,8 @@
       <c r="D236" s="7"/>
       <c r="E236" s="8"/>
       <c r="F236" s="7"/>
-      <c r="G236" s="7"/>
-    </row>
-    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="7" t="s">
         <v>37</v>
       </c>
@@ -8807,9 +8430,8 @@
       <c r="D237" s="7"/>
       <c r="E237" s="8"/>
       <c r="F237" s="7"/>
-      <c r="G237" s="7"/>
-    </row>
-    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="7" t="s">
         <v>37</v>
       </c>
@@ -8822,9 +8444,8 @@
       <c r="D238" s="7"/>
       <c r="E238" s="8"/>
       <c r="F238" s="7"/>
-      <c r="G238" s="7"/>
-    </row>
-    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="7" t="s">
         <v>37</v>
       </c>
@@ -8837,9 +8458,8 @@
       <c r="D239" s="7"/>
       <c r="E239" s="8"/>
       <c r="F239" s="7"/>
-      <c r="G239" s="7"/>
-    </row>
-    <row r="240" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="240" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A240" s="7" t="s">
         <v>39</v>
       </c>
@@ -8850,15 +8470,14 @@
         <v>1183</v>
       </c>
       <c r="D240" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E240" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F240" s="7"/>
-      <c r="G240" s="7"/>
-    </row>
-    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="7" t="s">
         <v>39</v>
       </c>
@@ -8869,13 +8488,12 @@
         <v>14</v>
       </c>
       <c r="D241" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E241" s="10"/>
       <c r="F241" s="7"/>
-      <c r="G241" s="7"/>
-    </row>
-    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="7" t="s">
         <v>39</v>
       </c>
@@ -8886,13 +8504,12 @@
         <v>13</v>
       </c>
       <c r="D242" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E242" s="10"/>
       <c r="F242" s="7"/>
-      <c r="G242" s="7"/>
-    </row>
-    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="7" t="s">
         <v>39</v>
       </c>
@@ -8903,13 +8520,12 @@
         <v>13</v>
       </c>
       <c r="D243" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E243" s="10"/>
       <c r="F243" s="7"/>
-      <c r="G243" s="7"/>
-    </row>
-    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="7" t="s">
         <v>39</v>
       </c>
@@ -8920,13 +8536,12 @@
         <v>4</v>
       </c>
       <c r="D244" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E244" s="10"/>
       <c r="F244" s="7"/>
-      <c r="G244" s="7"/>
-    </row>
-    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="7" t="s">
         <v>39</v>
       </c>
@@ -8937,13 +8552,12 @@
         <v>3</v>
       </c>
       <c r="D245" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E245" s="10"/>
       <c r="F245" s="7"/>
-      <c r="G245" s="7"/>
-    </row>
-    <row r="246" spans="1:7" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="246" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A246" s="7" t="s">
         <v>39</v>
       </c>
@@ -8954,17 +8568,14 @@
         <v>1308</v>
       </c>
       <c r="D246" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E246" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="F246" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G246" s="7"/>
-    </row>
-    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+      <c r="F246" s="7"/>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="7" t="s">
         <v>39</v>
       </c>
@@ -8975,15 +8586,12 @@
         <v>260</v>
       </c>
       <c r="D247" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E247" s="10"/>
-      <c r="F247" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G247" s="7"/>
-    </row>
-    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F247" s="7"/>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="7" t="s">
         <v>39</v>
       </c>
@@ -8994,15 +8602,12 @@
         <v>179</v>
       </c>
       <c r="D248" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E248" s="10"/>
-      <c r="F248" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G248" s="7"/>
-    </row>
-    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F248" s="7"/>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
         <v>39</v>
       </c>
@@ -9013,15 +8618,12 @@
         <v>73</v>
       </c>
       <c r="D249" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E249" s="10"/>
-      <c r="F249" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G249" s="7"/>
-    </row>
-    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F249" s="7"/>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="7" t="s">
         <v>39</v>
       </c>
@@ -9032,15 +8634,12 @@
         <v>72</v>
       </c>
       <c r="D250" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E250" s="10"/>
-      <c r="F250" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G250" s="7"/>
-    </row>
-    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F250" s="7"/>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="7" t="s">
         <v>39</v>
       </c>
@@ -9051,15 +8650,12 @@
         <v>57</v>
       </c>
       <c r="D251" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E251" s="10"/>
-      <c r="F251" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G251" s="7"/>
-    </row>
-    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F251" s="7"/>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="7" t="s">
         <v>39</v>
       </c>
@@ -9070,15 +8666,12 @@
         <v>39</v>
       </c>
       <c r="D252" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E252" s="10"/>
-      <c r="F252" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G252" s="7"/>
-    </row>
-    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F252" s="7"/>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
         <v>39</v>
       </c>
@@ -9089,15 +8682,12 @@
         <v>37</v>
       </c>
       <c r="D253" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E253" s="10"/>
-      <c r="F253" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G253" s="7"/>
-    </row>
-    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F253" s="7"/>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="7" t="s">
         <v>39</v>
       </c>
@@ -9108,15 +8698,12 @@
         <v>36</v>
       </c>
       <c r="D254" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E254" s="10"/>
-      <c r="F254" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G254" s="7"/>
-    </row>
-    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F254" s="7"/>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
         <v>39</v>
       </c>
@@ -9127,15 +8714,12 @@
         <v>14</v>
       </c>
       <c r="D255" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E255" s="10"/>
-      <c r="F255" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G255" s="7"/>
-    </row>
-    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F255" s="7"/>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="7" t="s">
         <v>39</v>
       </c>
@@ -9146,15 +8730,12 @@
         <v>13</v>
       </c>
       <c r="D256" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E256" s="10"/>
-      <c r="F256" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G256" s="7"/>
-    </row>
-    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F256" s="7"/>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
         <v>39</v>
       </c>
@@ -9165,15 +8746,12 @@
         <v>12</v>
       </c>
       <c r="D257" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E257" s="10"/>
-      <c r="F257" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G257" s="7"/>
-    </row>
-    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F257" s="7"/>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="7" t="s">
         <v>39</v>
       </c>
@@ -9184,15 +8762,12 @@
         <v>11</v>
       </c>
       <c r="D258" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E258" s="10"/>
-      <c r="F258" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G258" s="7"/>
-    </row>
-    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F258" s="7"/>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
         <v>39</v>
       </c>
@@ -9203,15 +8778,12 @@
         <v>9</v>
       </c>
       <c r="D259" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E259" s="10"/>
-      <c r="F259" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G259" s="7"/>
-    </row>
-    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F259" s="7"/>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="7" t="s">
         <v>39</v>
       </c>
@@ -9222,15 +8794,12 @@
         <v>5</v>
       </c>
       <c r="D260" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E260" s="10"/>
-      <c r="F260" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G260" s="7"/>
-    </row>
-    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F260" s="7"/>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
         <v>39</v>
       </c>
@@ -9241,15 +8810,12 @@
         <v>3</v>
       </c>
       <c r="D261" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E261" s="10"/>
-      <c r="F261" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G261" s="7"/>
-    </row>
-    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F261" s="7"/>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="7" t="s">
         <v>39</v>
       </c>
@@ -9260,15 +8826,12 @@
         <v>2</v>
       </c>
       <c r="D262" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E262" s="10"/>
-      <c r="F262" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G262" s="7"/>
-    </row>
-    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F262" s="7"/>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
         <v>39</v>
       </c>
@@ -9279,15 +8842,12 @@
         <v>2</v>
       </c>
       <c r="D263" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E263" s="10"/>
-      <c r="F263" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G263" s="7"/>
-    </row>
-    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F263" s="7"/>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="7" t="s">
         <v>39</v>
       </c>
@@ -9298,15 +8858,12 @@
         <v>1</v>
       </c>
       <c r="D264" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E264" s="10"/>
-      <c r="F264" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G264" s="7"/>
-    </row>
-    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F264" s="7"/>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
         <v>39</v>
       </c>
@@ -9317,15 +8874,12 @@
         <v>1</v>
       </c>
       <c r="D265" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E265" s="10"/>
-      <c r="F265" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G265" s="7"/>
-    </row>
-    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F265" s="7"/>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="7" t="s">
         <v>39</v>
       </c>
@@ -9336,15 +8890,12 @@
         <v>1</v>
       </c>
       <c r="D266" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E266" s="10"/>
-      <c r="F266" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G266" s="7"/>
-    </row>
-    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F266" s="7"/>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
         <v>39</v>
       </c>
@@ -9355,15 +8906,12 @@
         <v>1</v>
       </c>
       <c r="D267" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E267" s="10"/>
-      <c r="F267" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G267" s="7"/>
-    </row>
-    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F267" s="7"/>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="7" t="s">
         <v>39</v>
       </c>
@@ -9374,15 +8922,12 @@
         <v>1</v>
       </c>
       <c r="D268" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E268" s="10"/>
-      <c r="F268" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G268" s="7"/>
-    </row>
-    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F268" s="7"/>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
         <v>39</v>
       </c>
@@ -9393,15 +8938,12 @@
         <v>1</v>
       </c>
       <c r="D269" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E269" s="10"/>
-      <c r="F269" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G269" s="7"/>
-    </row>
-    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F269" s="7"/>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="7" t="s">
         <v>39</v>
       </c>
@@ -9412,15 +8954,12 @@
         <v>1</v>
       </c>
       <c r="D270" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E270" s="10"/>
-      <c r="F270" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G270" s="7"/>
-    </row>
-    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F270" s="7"/>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
         <v>39</v>
       </c>
@@ -9431,15 +8970,12 @@
         <v>1</v>
       </c>
       <c r="D271" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E271" s="10"/>
-      <c r="F271" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G271" s="7"/>
-    </row>
-    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F271" s="7"/>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="7" t="s">
         <v>39</v>
       </c>
@@ -9450,15 +8986,12 @@
         <v>1</v>
       </c>
       <c r="D272" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E272" s="10"/>
-      <c r="F272" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G272" s="7"/>
-    </row>
-    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F272" s="7"/>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
         <v>39</v>
       </c>
@@ -9469,15 +9002,12 @@
         <v>1</v>
       </c>
       <c r="D273" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E273" s="10"/>
-      <c r="F273" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G273" s="7"/>
-    </row>
-    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F273" s="7"/>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="7" t="s">
         <v>39</v>
       </c>
@@ -9488,15 +9018,12 @@
         <v>1</v>
       </c>
       <c r="D274" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E274" s="10"/>
-      <c r="F274" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G274" s="7"/>
-    </row>
-    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F274" s="7"/>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="7" t="s">
         <v>39</v>
       </c>
@@ -9507,15 +9034,12 @@
         <v>1</v>
       </c>
       <c r="D275" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E275" s="10"/>
-      <c r="F275" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G275" s="7"/>
-    </row>
-    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F275" s="7"/>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="7" t="s">
         <v>39</v>
       </c>
@@ -9526,15 +9050,12 @@
         <v>1</v>
       </c>
       <c r="D276" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E276" s="10"/>
-      <c r="F276" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G276" s="7"/>
-    </row>
-    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F276" s="7"/>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="7" t="s">
         <v>39</v>
       </c>
@@ -9545,15 +9066,12 @@
         <v>1</v>
       </c>
       <c r="D277" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E277" s="10"/>
-      <c r="F277" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G277" s="7"/>
-    </row>
-    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F277" s="7"/>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="7" t="s">
         <v>39</v>
       </c>
@@ -9564,15 +9082,12 @@
         <v>1</v>
       </c>
       <c r="D278" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E278" s="10"/>
-      <c r="F278" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G278" s="7"/>
-    </row>
-    <row r="279" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F278" s="7"/>
+    </row>
+    <row r="279" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
         <v>39</v>
       </c>
@@ -9583,17 +9098,14 @@
         <v>795</v>
       </c>
       <c r="D279" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E279" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="F279" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G279" s="7"/>
-    </row>
-    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+      <c r="F279" s="7"/>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="7" t="s">
         <v>39</v>
       </c>
@@ -9604,15 +9116,12 @@
         <v>205</v>
       </c>
       <c r="D280" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E280" s="10"/>
-      <c r="F280" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G280" s="7"/>
-    </row>
-    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F280" s="7"/>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="7" t="s">
         <v>39</v>
       </c>
@@ -9623,15 +9132,12 @@
         <v>117</v>
       </c>
       <c r="D281" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E281" s="10"/>
-      <c r="F281" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G281" s="7"/>
-    </row>
-    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F281" s="7"/>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="7" t="s">
         <v>39</v>
       </c>
@@ -9642,15 +9148,12 @@
         <v>90</v>
       </c>
       <c r="D282" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E282" s="10"/>
-      <c r="F282" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G282" s="7"/>
-    </row>
-    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F282" s="7"/>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="7" t="s">
         <v>39</v>
       </c>
@@ -9661,15 +9164,12 @@
         <v>7</v>
       </c>
       <c r="D283" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E283" s="10"/>
-      <c r="F283" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G283" s="7"/>
-    </row>
-    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F283" s="7"/>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="7" t="s">
         <v>39</v>
       </c>
@@ -9680,15 +9180,12 @@
         <v>5</v>
       </c>
       <c r="D284" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E284" s="10"/>
-      <c r="F284" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G284" s="7"/>
-    </row>
-    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F284" s="7"/>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="7" t="s">
         <v>39</v>
       </c>
@@ -9699,15 +9196,12 @@
         <v>3</v>
       </c>
       <c r="D285" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E285" s="10"/>
-      <c r="F285" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G285" s="7"/>
-    </row>
-    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F285" s="7"/>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="7" t="s">
         <v>39</v>
       </c>
@@ -9718,15 +9212,12 @@
         <v>1</v>
       </c>
       <c r="D286" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E286" s="10"/>
-      <c r="F286" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G286" s="7"/>
-    </row>
-    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F286" s="7"/>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="7" t="s">
         <v>39</v>
       </c>
@@ -9737,15 +9228,12 @@
         <v>1</v>
       </c>
       <c r="D287" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E287" s="10"/>
-      <c r="F287" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G287" s="7"/>
-    </row>
-    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F287" s="7"/>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="7" t="s">
         <v>39</v>
       </c>
@@ -9756,15 +9244,12 @@
         <v>1</v>
       </c>
       <c r="D288" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E288" s="10"/>
-      <c r="F288" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G288" s="7"/>
-    </row>
-    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F288" s="7"/>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="7" t="s">
         <v>39</v>
       </c>
@@ -9775,15 +9260,12 @@
         <v>1</v>
       </c>
       <c r="D289" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E289" s="10"/>
-      <c r="F289" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="G289" s="7"/>
-    </row>
-    <row r="290" spans="1:7" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F289" s="7"/>
+    </row>
+    <row r="290" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A290" s="7" t="s">
         <v>39</v>
       </c>
@@ -9794,15 +9276,14 @@
         <v>520</v>
       </c>
       <c r="D290" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E290" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F290" s="7"/>
-      <c r="G290" s="7"/>
-    </row>
-    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="7" t="s">
         <v>39</v>
       </c>
@@ -9813,13 +9294,12 @@
         <v>455</v>
       </c>
       <c r="D291" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E291" s="10"/>
       <c r="F291" s="7"/>
-      <c r="G291" s="7"/>
-    </row>
-    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="7" t="s">
         <v>39</v>
       </c>
@@ -9830,13 +9310,12 @@
         <v>404</v>
       </c>
       <c r="D292" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E292" s="10"/>
       <c r="F292" s="7"/>
-      <c r="G292" s="7"/>
-    </row>
-    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="7" t="s">
         <v>39</v>
       </c>
@@ -9847,13 +9326,12 @@
         <v>94</v>
       </c>
       <c r="D293" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E293" s="10"/>
       <c r="F293" s="7"/>
-      <c r="G293" s="7"/>
-    </row>
-    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="7" t="s">
         <v>39</v>
       </c>
@@ -9864,13 +9342,12 @@
         <v>32</v>
       </c>
       <c r="D294" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E294" s="10"/>
       <c r="F294" s="7"/>
-      <c r="G294" s="7"/>
-    </row>
-    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="7" t="s">
         <v>39</v>
       </c>
@@ -9881,13 +9358,12 @@
         <v>9</v>
       </c>
       <c r="D295" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E295" s="10"/>
       <c r="F295" s="7"/>
-      <c r="G295" s="7"/>
-    </row>
-    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="7" t="s">
         <v>39</v>
       </c>
@@ -9898,13 +9374,12 @@
         <v>3</v>
       </c>
       <c r="D296" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E296" s="10"/>
       <c r="F296" s="7"/>
-      <c r="G296" s="7"/>
-    </row>
-    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="7" t="s">
         <v>39</v>
       </c>
@@ -9915,13 +9390,12 @@
         <v>1</v>
       </c>
       <c r="D297" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E297" s="10"/>
       <c r="F297" s="7"/>
-      <c r="G297" s="7"/>
-    </row>
-    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="7" t="s">
         <v>39</v>
       </c>
@@ -9932,13 +9406,12 @@
         <v>1</v>
       </c>
       <c r="D298" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E298" s="10"/>
       <c r="F298" s="7"/>
-      <c r="G298" s="7"/>
-    </row>
-    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="7" t="s">
         <v>39</v>
       </c>
@@ -9949,13 +9422,12 @@
         <v>1</v>
       </c>
       <c r="D299" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E299" s="10"/>
       <c r="F299" s="7"/>
-      <c r="G299" s="7"/>
-    </row>
-    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="7" t="s">
         <v>39</v>
       </c>
@@ -9966,24 +9438,18 @@
         <v>1</v>
       </c>
       <c r="D300" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E300" s="10"/>
       <c r="F300" s="7"/>
-      <c r="G300" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G300" xr:uid="{38A162FC-7907-44C7-A909-E8E1323EC5F6}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="grouper"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A240:G300">
+  <autoFilter ref="A1:F300" xr:uid="{38A162FC-7907-44C7-A909-E8E1323EC5F6}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A240:F300">
       <sortCondition ref="D1:D300"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="G2 F2:F300 F5:G5">
+  <conditionalFormatting sqref="F2 F5">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"Y"</formula>
     </cfRule>
@@ -9991,12 +9457,12 @@
       <formula>"WIP"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23">
+  <conditionalFormatting sqref="F23">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"Y"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G29">
+  <conditionalFormatting sqref="F29">
     <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"Y"</formula>
     </cfRule>
@@ -10019,7 +9485,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="24" x14ac:dyDescent="0.3">
       <c r="B1" s="33" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C1" s="32" t="s">
         <v>126</v>
@@ -10034,7 +9500,7 @@
         <v>116</v>
       </c>
       <c r="G1" s="32" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H1" s="32" t="s">
         <v>39</v>
@@ -10075,45 +9541,47 @@
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F2" s="30" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G2" s="30" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H2" s="30" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I2" s="30" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J2" s="30"/>
       <c r="K2" s="37" t="s">
-        <v>239</v>
-      </c>
-      <c r="L2" s="30"/>
+        <v>236</v>
+      </c>
+      <c r="L2" s="39" t="s">
+        <v>235</v>
+      </c>
       <c r="M2" s="30"/>
       <c r="N2" s="30"/>
       <c r="O2" s="30" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P2" s="30"/>
       <c r="Q2" s="38" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="R2" s="29" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="55.2" x14ac:dyDescent="0.25">
@@ -10121,37 +9589,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="K3" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
+      </c>
+      <c r="L3" s="40" t="s">
+        <v>235</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="R3" s="27" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="41.4" x14ac:dyDescent="0.25">
@@ -10159,37 +9630,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
+      </c>
+      <c r="L4" s="40" t="s">
+        <v>235</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="R4" s="27" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="96.6" x14ac:dyDescent="0.25">
@@ -10197,34 +9671,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
+      </c>
+      <c r="L5" s="40" t="s">
+        <v>235</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="R5" s="27" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -10232,41 +9709,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J6" s="36"/>
       <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
+      <c r="L6" s="41" t="s">
+        <v>235</v>
+      </c>
       <c r="M6" s="36"/>
       <c r="N6" s="36"/>
       <c r="O6" s="34" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P6" s="36"/>
       <c r="Q6" s="36"/>
       <c r="R6" s="35" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="27.6" x14ac:dyDescent="0.25">
@@ -10274,34 +9753,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="O7" s="16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="R7" s="16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="27.6" x14ac:dyDescent="0.25">
@@ -10309,7 +9788,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C8" s="28"/>
       <c r="R8" s="27"/>
@@ -10319,25 +9798,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="R9" s="27"/>
     </row>
@@ -10346,7 +9825,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C10" s="24"/>
       <c r="D10" s="23"/>
@@ -10370,7 +9849,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B12" s="17" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C12" s="21">
         <f>2918</f>
@@ -10437,7 +9916,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B13" s="17" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C13" s="20">
         <f t="shared" ref="C13:R13" si="0">C12/SUM($C12:$R12)</f>
@@ -10506,7 +9985,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B14" s="17" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C14" s="20">
         <f t="shared" ref="C14:R14" si="1">COUNTA(C2:C10)/9*C13</f>
@@ -10546,7 +10025,7 @@
       </c>
       <c r="L14" s="20">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8.761274468738655E-3</v>
       </c>
       <c r="M14" s="20">
         <f t="shared" si="1"/>
@@ -10575,11 +10054,11 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B15" s="19" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C15" s="18">
         <f>SUM(C14:R14)</f>
-        <v>0.66698081595040626</v>
+        <v>0.6757420904191449</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw_data/feed_profiles_and_composition.xlsx
+++ b/data/raw_data/feed_profiles_and_composition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\climate_risks_to_fed_mariculture\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A976A6-C1EF-4CBA-8CD8-258619C3DAB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A194B61-33BB-49CB-93C0-EFCA8165C51F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="408" yWindow="888" windowWidth="22728" windowHeight="13764" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="696" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="feed_formulations" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="268">
   <si>
     <t>ingredient</t>
   </si>
@@ -873,11 +873,18 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1143,71 +1150,73 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="4" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="4" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Good" xfId="3" builtinId="26"/>
@@ -5147,7 +5156,7 @@
       <sortCondition ref="A1:A229"/>
     </sortState>
   </autoFilter>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D95" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
   </hyperlinks>
@@ -10149,10 +10158,10 @@
         <v>234</v>
       </c>
       <c r="J2" s="30"/>
-      <c r="K2" s="37" t="s">
-        <v>235</v>
-      </c>
-      <c r="L2" s="39" t="s">
+      <c r="K2" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="L2" s="38" t="s">
         <v>234</v>
       </c>
       <c r="M2" s="30"/>
@@ -10161,7 +10170,7 @@
         <v>234</v>
       </c>
       <c r="P2" s="30"/>
-      <c r="Q2" s="38" t="s">
+      <c r="Q2" s="37" t="s">
         <v>235</v>
       </c>
       <c r="R2" s="29" t="s">
@@ -10196,28 +10205,28 @@
       <c r="I3" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="J3" s="42" t="s">
+      <c r="J3" s="41" t="s">
         <v>234</v>
       </c>
       <c r="K3" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="L3" s="40" t="s">
+      <c r="L3" s="39" t="s">
         <v>234</v>
       </c>
-      <c r="M3" s="42" t="s">
+      <c r="M3" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="N3" s="42" t="s">
+      <c r="N3" s="41" t="s">
         <v>234</v>
       </c>
       <c r="O3" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="P3" s="42" t="s">
+      <c r="P3" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="Q3" s="42" t="s">
+      <c r="Q3" s="41" t="s">
         <v>234</v>
       </c>
       <c r="R3" s="27" t="s">
@@ -10252,13 +10261,13 @@
       <c r="I4" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="J4" s="42" t="s">
+      <c r="J4" s="41" t="s">
         <v>234</v>
       </c>
       <c r="K4" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="L4" s="40" t="s">
+      <c r="L4" s="39" t="s">
         <v>234</v>
       </c>
       <c r="M4" s="16" t="s">
@@ -10308,28 +10317,28 @@
       <c r="I5" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="J5" s="42" t="s">
+      <c r="J5" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="K5" s="42" t="s">
+      <c r="K5" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="L5" s="40" t="s">
+      <c r="L5" s="39" t="s">
         <v>234</v>
       </c>
-      <c r="M5" s="42" t="s">
+      <c r="M5" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="N5" s="42" t="s">
+      <c r="N5" s="41" t="s">
         <v>234</v>
       </c>
       <c r="O5" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="P5" s="42" t="s">
+      <c r="P5" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="Q5" s="42" t="s">
+      <c r="Q5" s="41" t="s">
         <v>234</v>
       </c>
       <c r="R5" s="27" t="s">
@@ -10365,8 +10374,10 @@
         <v>234</v>
       </c>
       <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="41" t="s">
+      <c r="K6" s="44" t="s">
+        <v>234</v>
+      </c>
+      <c r="L6" s="40" t="s">
         <v>234</v>
       </c>
       <c r="M6" s="36"/>
@@ -10399,8 +10410,8 @@
       <c r="F7" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="G7" s="16" t="s">
-        <v>235</v>
+      <c r="G7" s="45" t="s">
+        <v>234</v>
       </c>
       <c r="H7" s="16" t="s">
         <v>235</v>
@@ -10408,7 +10419,7 @@
       <c r="I7" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="L7" s="42" t="s">
+      <c r="L7" s="41" t="s">
         <v>235</v>
       </c>
       <c r="O7" s="16" t="s">
@@ -10432,7 +10443,7 @@
       <c r="A9" s="23">
         <v>8</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="42" t="s">
         <v>236</v>
       </c>
       <c r="C9" s="24"/>
@@ -10531,7 +10542,7 @@
         <v>0.18333752199044986</v>
       </c>
       <c r="D12" s="20">
-        <f t="shared" ref="C12:R12" si="0">D11/SUM($C11:$R11)</f>
+        <f t="shared" ref="D12:R12" si="0">D11/SUM($C11:$R11)</f>
         <v>4.9258607690374469E-2</v>
       </c>
       <c r="E12" s="20">
@@ -10629,7 +10640,7 @@
       </c>
       <c r="K13" s="20">
         <f t="shared" si="1"/>
-        <v>7.9479768786127163E-3</v>
+        <v>9.9349710982658962E-3</v>
       </c>
       <c r="L13" s="20">
         <f t="shared" si="1"/>
@@ -10666,7 +10677,7 @@
       </c>
       <c r="C14" s="18">
         <f>SUM(C13:R13)</f>
-        <v>0.71270262628801229</v>
+        <v>0.71468962050766549</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw_data/feed_profiles_and_composition.xlsx
+++ b/data/raw_data/feed_profiles_and_composition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\climate_risks_to_fed_mariculture\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A194B61-33BB-49CB-93C0-EFCA8165C51F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFEB62F-F489-417E-A94F-7F502C113E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="696" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21744" yWindow="0" windowWidth="19632" windowHeight="16656" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="feed_formulations" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="268">
   <si>
     <t>ingredient</t>
   </si>
@@ -873,11 +873,18 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1150,72 +1157,73 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
@@ -5156,7 +5164,7 @@
       <sortCondition ref="A1:A229"/>
     </sortState>
   </autoFilter>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D95" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
   </hyperlinks>
@@ -10067,13 +10075,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4A353B5-0CCF-4CD3-981F-8A6F6874C0EC}">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:W29"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" style="16" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50.44140625" style="16" customWidth="1"/>
     <col min="3" max="18" width="8.6640625" style="16" customWidth="1"/>
-    <col min="19" max="16384" width="9.109375" style="16"/>
+    <col min="19" max="19" width="11.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.109375" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" x14ac:dyDescent="0.3">
@@ -10405,28 +10415,31 @@
         <v>234</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G7" s="45" t="s">
         <v>234</v>
       </c>
       <c r="H7" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="K7" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="I7" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="L7" s="41" t="s">
-        <v>235</v>
-      </c>
-      <c r="O7" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="R7" s="16" t="s">
-        <v>235</v>
+      <c r="L7" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="O7" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="R7" s="34" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="27.6" x14ac:dyDescent="0.25">
@@ -10640,7 +10653,7 @@
       </c>
       <c r="K13" s="20">
         <f t="shared" si="1"/>
-        <v>9.9349710982658962E-3</v>
+        <v>1.1921965317919074E-2</v>
       </c>
       <c r="L13" s="20">
         <f t="shared" si="1"/>
@@ -10677,8 +10690,61 @@
       </c>
       <c r="C14" s="18">
         <f>SUM(C13:R13)</f>
-        <v>0.71468962050766549</v>
-      </c>
+        <v>0.71667661472731869</v>
+      </c>
+    </row>
+    <row r="19" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="T19" s="46"/>
+    </row>
+    <row r="20" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="T20" s="46"/>
+    </row>
+    <row r="21" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S21" s="46"/>
+      <c r="T21" s="46"/>
+      <c r="U21" s="46"/>
+      <c r="V21" s="46"/>
+      <c r="W21" s="46"/>
+    </row>
+    <row r="22" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S22" s="46"/>
+      <c r="T22" s="46"/>
+      <c r="U22" s="46"/>
+    </row>
+    <row r="23" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S23" s="46"/>
+      <c r="T23" s="46"/>
+      <c r="U23" s="46"/>
+    </row>
+    <row r="24" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S24" s="46"/>
+      <c r="T24" s="46"/>
+      <c r="U24" s="46"/>
+    </row>
+    <row r="25" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S25" s="46"/>
+      <c r="T25" s="46"/>
+      <c r="U25" s="46"/>
+    </row>
+    <row r="26" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S26" s="46"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+    </row>
+    <row r="27" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S27" s="46"/>
+      <c r="T27" s="46"/>
+      <c r="U27" s="46"/>
+    </row>
+    <row r="28" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S28" s="46"/>
+      <c r="T28" s="46"/>
+      <c r="U28" s="46"/>
+    </row>
+    <row r="29" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S29" s="46"/>
+      <c r="T29" s="46"/>
+      <c r="U29" s="46"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:R10">

--- a/data/raw_data/feed_profiles_and_composition.xlsx
+++ b/data/raw_data/feed_profiles_and_composition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\climate_risks_to_fed_mariculture\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFEB62F-F489-417E-A94F-7F502C113E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D568A87B-F0F4-4A52-8323-5446FF3D895B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21744" yWindow="0" windowWidth="19632" windowHeight="16656" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="feed_formulations" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="270">
   <si>
     <t>ingredient</t>
   </si>
@@ -864,6 +864,12 @@
   <si>
     <t>Islam, M. R., Cho, S. H., &amp; Kim, T. (2024). Inclusion effect of jack mackerel meal in diets substituting fish meal with corn gluten meal on growth and feed utilization of olive flounder (Paralichthys olivaceus). Frontiers in Sustainable Food Systems, 8. https://doi.org/10.3389/fsufs.2024.1414574</t>
   </si>
+  <si>
+    <t>CODE PROGRESS</t>
+  </si>
+  <si>
+    <t>Code contribution</t>
+  </si>
 </sst>
 </file>
 
@@ -873,11 +879,18 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1157,74 +1170,80 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="4" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="8" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Good" xfId="3" builtinId="26"/>
@@ -5164,7 +5183,7 @@
       <sortCondition ref="A1:A229"/>
     </sortState>
   </autoFilter>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D95" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
   </hyperlinks>
@@ -5175,6 +5194,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A162FC-7907-44C7-A909-E8E1323EC5F6}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F300"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5207,7 +5227,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>195</v>
       </c>
@@ -5225,7 +5245,7 @@
       </c>
       <c r="F2" s="7"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>195</v>
       </c>
@@ -5241,7 +5261,7 @@
       <c r="E3" s="10"/>
       <c r="F3" s="7"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>195</v>
       </c>
@@ -5257,7 +5277,7 @@
       <c r="E4" s="10"/>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>195</v>
       </c>
@@ -5273,7 +5293,7 @@
       <c r="E5" s="10"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>125</v>
       </c>
@@ -5291,7 +5311,7 @@
       </c>
       <c r="F6" s="7"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>125</v>
       </c>
@@ -5307,7 +5327,7 @@
       <c r="E7" s="10"/>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>125</v>
       </c>
@@ -5323,7 +5343,7 @@
       <c r="E8" s="10"/>
       <c r="F8" s="7"/>
     </row>
-    <row r="9" spans="1:6" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>125</v>
       </c>
@@ -5341,7 +5361,7 @@
       </c>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>125</v>
       </c>
@@ -5359,7 +5379,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>125</v>
       </c>
@@ -5377,7 +5397,7 @@
       </c>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>125</v>
       </c>
@@ -5393,7 +5413,7 @@
       <c r="E12" s="10"/>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>125</v>
       </c>
@@ -5409,7 +5429,7 @@
       <c r="E13" s="10"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>125</v>
       </c>
@@ -5425,7 +5445,7 @@
       <c r="E14" s="10"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>125</v>
       </c>
@@ -5441,7 +5461,7 @@
       <c r="E15" s="10"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:6" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>125</v>
       </c>
@@ -5459,7 +5479,7 @@
       </c>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>125</v>
       </c>
@@ -5475,7 +5495,7 @@
       <c r="E17" s="10"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>125</v>
       </c>
@@ -5491,7 +5511,7 @@
       <c r="E18" s="10"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>125</v>
       </c>
@@ -5507,7 +5527,7 @@
       <c r="E19" s="10"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>125</v>
       </c>
@@ -5523,7 +5543,7 @@
       <c r="E20" s="10"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>116</v>
       </c>
@@ -5541,7 +5561,7 @@
       </c>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>116</v>
       </c>
@@ -5557,7 +5577,7 @@
       <c r="E22" s="10"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>116</v>
       </c>
@@ -5573,7 +5593,7 @@
       <c r="E23" s="10"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>116</v>
       </c>
@@ -5589,7 +5609,7 @@
       <c r="E24" s="10"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>116</v>
       </c>
@@ -5605,7 +5625,7 @@
       <c r="E25" s="10"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>116</v>
       </c>
@@ -5621,7 +5641,7 @@
       <c r="E26" s="10"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>116</v>
       </c>
@@ -5637,7 +5657,7 @@
       <c r="E27" s="10"/>
       <c r="F27" s="7"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>116</v>
       </c>
@@ -5653,7 +5673,7 @@
       <c r="E28" s="10"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>116</v>
       </c>
@@ -5669,7 +5689,7 @@
       <c r="E29" s="10"/>
       <c r="F29" s="7"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>116</v>
       </c>
@@ -5685,7 +5705,7 @@
       <c r="E30" s="10"/>
       <c r="F30" s="7"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>116</v>
       </c>
@@ -5701,7 +5721,7 @@
       <c r="E31" s="10"/>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>116</v>
       </c>
@@ -5717,7 +5737,7 @@
       <c r="E32" s="10"/>
       <c r="F32" s="7"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>116</v>
       </c>
@@ -5733,7 +5753,7 @@
       <c r="E33" s="10"/>
       <c r="F33" s="7"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>116</v>
       </c>
@@ -5749,7 +5769,7 @@
       <c r="E34" s="10"/>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>116</v>
       </c>
@@ -5765,7 +5785,7 @@
       <c r="E35" s="10"/>
       <c r="F35" s="7"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>116</v>
       </c>
@@ -5781,7 +5801,7 @@
       <c r="E36" s="10"/>
       <c r="F36" s="7"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>116</v>
       </c>
@@ -5797,7 +5817,7 @@
       <c r="E37" s="10"/>
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>116</v>
       </c>
@@ -5813,7 +5833,7 @@
       <c r="E38" s="10"/>
       <c r="F38" s="7"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>116</v>
       </c>
@@ -5829,7 +5849,7 @@
       <c r="E39" s="10"/>
       <c r="F39" s="7"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>116</v>
       </c>
@@ -5845,7 +5865,7 @@
       <c r="E40" s="10"/>
       <c r="F40" s="7"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>116</v>
       </c>
@@ -5861,7 +5881,7 @@
       <c r="E41" s="10"/>
       <c r="F41" s="7"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>116</v>
       </c>
@@ -5877,7 +5897,7 @@
       <c r="E42" s="10"/>
       <c r="F42" s="7"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>116</v>
       </c>
@@ -5893,7 +5913,7 @@
       <c r="E43" s="10"/>
       <c r="F43" s="7"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>116</v>
       </c>
@@ -5909,7 +5929,7 @@
       <c r="E44" s="10"/>
       <c r="F44" s="7"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>116</v>
       </c>
@@ -5925,7 +5945,7 @@
       <c r="E45" s="10"/>
       <c r="F45" s="7"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>116</v>
       </c>
@@ -5941,7 +5961,7 @@
       <c r="E46" s="10"/>
       <c r="F46" s="7"/>
     </row>
-    <row r="47" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>115</v>
       </c>
@@ -5959,7 +5979,7 @@
       </c>
       <c r="F47" s="7"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>115</v>
       </c>
@@ -5975,7 +5995,7 @@
       <c r="E48" s="10"/>
       <c r="F48" s="7"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>115</v>
       </c>
@@ -5991,7 +6011,7 @@
       <c r="E49" s="10"/>
       <c r="F49" s="7"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>115</v>
       </c>
@@ -6007,7 +6027,7 @@
       <c r="E50" s="10"/>
       <c r="F50" s="7"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>115</v>
       </c>
@@ -6023,7 +6043,7 @@
       <c r="E51" s="10"/>
       <c r="F51" s="7"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>115</v>
       </c>
@@ -6039,7 +6059,7 @@
       <c r="E52" s="10"/>
       <c r="F52" s="7"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>115</v>
       </c>
@@ -6055,7 +6075,7 @@
       <c r="E53" s="10"/>
       <c r="F53" s="7"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>115</v>
       </c>
@@ -6071,7 +6091,7 @@
       <c r="E54" s="10"/>
       <c r="F54" s="7"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>115</v>
       </c>
@@ -6087,7 +6107,7 @@
       <c r="E55" s="10"/>
       <c r="F55" s="7"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>115</v>
       </c>
@@ -6103,7 +6123,7 @@
       <c r="E56" s="10"/>
       <c r="F56" s="7"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>115</v>
       </c>
@@ -6119,7 +6139,7 @@
       <c r="E57" s="10"/>
       <c r="F57" s="7"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>115</v>
       </c>
@@ -6135,7 +6155,7 @@
       <c r="E58" s="10"/>
       <c r="F58" s="7"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>115</v>
       </c>
@@ -6151,7 +6171,7 @@
       <c r="E59" s="10"/>
       <c r="F59" s="7"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>115</v>
       </c>
@@ -6167,7 +6187,7 @@
       <c r="E60" s="10"/>
       <c r="F60" s="7"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>115</v>
       </c>
@@ -6183,7 +6203,7 @@
       <c r="E61" s="10"/>
       <c r="F61" s="7"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>115</v>
       </c>
@@ -6199,7 +6219,7 @@
       <c r="E62" s="10"/>
       <c r="F62" s="7"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>115</v>
       </c>
@@ -6215,7 +6235,7 @@
       <c r="E63" s="10"/>
       <c r="F63" s="7"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
         <v>115</v>
       </c>
@@ -6231,7 +6251,7 @@
       <c r="E64" s="10"/>
       <c r="F64" s="7"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
         <v>115</v>
       </c>
@@ -6247,7 +6267,7 @@
       <c r="E65" s="10"/>
       <c r="F65" s="7"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>115</v>
       </c>
@@ -6263,7 +6283,7 @@
       <c r="E66" s="10"/>
       <c r="F66" s="7"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>115</v>
       </c>
@@ -6279,7 +6299,7 @@
       <c r="E67" s="10"/>
       <c r="F67" s="7"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
         <v>115</v>
       </c>
@@ -6295,7 +6315,7 @@
       <c r="E68" s="10"/>
       <c r="F68" s="7"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
         <v>115</v>
       </c>
@@ -6311,7 +6331,7 @@
       <c r="E69" s="10"/>
       <c r="F69" s="7"/>
     </row>
-    <row r="70" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
         <v>114</v>
       </c>
@@ -6329,7 +6349,7 @@
       </c>
       <c r="F70" s="7"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
         <v>114</v>
       </c>
@@ -6345,7 +6365,7 @@
       <c r="E71" s="10"/>
       <c r="F71" s="7"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
         <v>114</v>
       </c>
@@ -6361,7 +6381,7 @@
       <c r="E72" s="10"/>
       <c r="F72" s="7"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
         <v>114</v>
       </c>
@@ -6377,7 +6397,7 @@
       <c r="E73" s="10"/>
       <c r="F73" s="7"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
         <v>114</v>
       </c>
@@ -6393,7 +6413,7 @@
       <c r="E74" s="10"/>
       <c r="F74" s="7"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
         <v>114</v>
       </c>
@@ -6409,7 +6429,7 @@
       <c r="E75" s="10"/>
       <c r="F75" s="7"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
         <v>114</v>
       </c>
@@ -6425,7 +6445,7 @@
       <c r="E76" s="10"/>
       <c r="F76" s="7"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
         <v>114</v>
       </c>
@@ -6441,7 +6461,7 @@
       <c r="E77" s="10"/>
       <c r="F77" s="7"/>
     </row>
-    <row r="78" spans="1:6" ht="79.2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="79.2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
         <v>110</v>
       </c>
@@ -6459,7 +6479,7 @@
       </c>
       <c r="F78" s="7"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
         <v>110</v>
       </c>
@@ -6475,7 +6495,7 @@
       <c r="E79" s="10"/>
       <c r="F79" s="7"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
         <v>110</v>
       </c>
@@ -6491,7 +6511,7 @@
       <c r="E80" s="10"/>
       <c r="F80" s="7"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
         <v>110</v>
       </c>
@@ -6507,7 +6527,7 @@
       <c r="E81" s="10"/>
       <c r="F81" s="7"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
         <v>110</v>
       </c>
@@ -6523,7 +6543,7 @@
       <c r="E82" s="10"/>
       <c r="F82" s="7"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
         <v>110</v>
       </c>
@@ -6539,7 +6559,7 @@
       <c r="E83" s="10"/>
       <c r="F83" s="7"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
         <v>110</v>
       </c>
@@ -6555,7 +6575,7 @@
       <c r="E84" s="10"/>
       <c r="F84" s="7"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>110</v>
       </c>
@@ -6571,7 +6591,7 @@
       <c r="E85" s="10"/>
       <c r="F85" s="7"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
         <v>110</v>
       </c>
@@ -6587,7 +6607,7 @@
       <c r="E86" s="10"/>
       <c r="F86" s="7"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
         <v>110</v>
       </c>
@@ -6603,7 +6623,7 @@
       <c r="E87" s="10"/>
       <c r="F87" s="7"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
         <v>110</v>
       </c>
@@ -6619,7 +6639,7 @@
       <c r="E88" s="10"/>
       <c r="F88" s="7"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
         <v>110</v>
       </c>
@@ -6635,7 +6655,7 @@
       <c r="E89" s="10"/>
       <c r="F89" s="7"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
         <v>110</v>
       </c>
@@ -6651,7 +6671,7 @@
       <c r="E90" s="10"/>
       <c r="F90" s="7"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
         <v>110</v>
       </c>
@@ -6667,7 +6687,7 @@
       <c r="E91" s="10"/>
       <c r="F91" s="7"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
         <v>110</v>
       </c>
@@ -6683,7 +6703,7 @@
       <c r="E92" s="10"/>
       <c r="F92" s="7"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
         <v>110</v>
       </c>
@@ -6699,7 +6719,7 @@
       <c r="E93" s="10"/>
       <c r="F93" s="7"/>
     </row>
-    <row r="94" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
         <v>31</v>
       </c>
@@ -6717,7 +6737,7 @@
       </c>
       <c r="F94" s="7"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
         <v>31</v>
       </c>
@@ -6733,7 +6753,7 @@
       <c r="E95" s="10"/>
       <c r="F95" s="7"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
         <v>31</v>
       </c>
@@ -6749,7 +6769,7 @@
       <c r="E96" s="10"/>
       <c r="F96" s="7"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
         <v>31</v>
       </c>
@@ -6765,7 +6785,7 @@
       <c r="E97" s="10"/>
       <c r="F97" s="7"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
         <v>31</v>
       </c>
@@ -6781,7 +6801,7 @@
       <c r="E98" s="10"/>
       <c r="F98" s="7"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
         <v>31</v>
       </c>
@@ -6797,7 +6817,7 @@
       <c r="E99" s="10"/>
       <c r="F99" s="7"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
         <v>31</v>
       </c>
@@ -6813,7 +6833,7 @@
       <c r="E100" s="10"/>
       <c r="F100" s="7"/>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
         <v>31</v>
       </c>
@@ -6829,7 +6849,7 @@
       <c r="E101" s="10"/>
       <c r="F101" s="7"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
         <v>31</v>
       </c>
@@ -6845,7 +6865,7 @@
       <c r="E102" s="10"/>
       <c r="F102" s="7"/>
     </row>
-    <row r="103" spans="1:6" ht="66" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" ht="66" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
         <v>33</v>
       </c>
@@ -6863,7 +6883,7 @@
       </c>
       <c r="F103" s="7"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
         <v>33</v>
       </c>
@@ -6879,7 +6899,7 @@
       <c r="E104" s="10"/>
       <c r="F104" s="7"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
         <v>33</v>
       </c>
@@ -6895,7 +6915,7 @@
       <c r="E105" s="10"/>
       <c r="F105" s="7"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
         <v>33</v>
       </c>
@@ -6911,7 +6931,7 @@
       <c r="E106" s="10"/>
       <c r="F106" s="7"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
         <v>33</v>
       </c>
@@ -6927,7 +6947,7 @@
       <c r="E107" s="10"/>
       <c r="F107" s="7"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
         <v>33</v>
       </c>
@@ -6943,7 +6963,7 @@
       <c r="E108" s="10"/>
       <c r="F108" s="7"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
         <v>33</v>
       </c>
@@ -6959,7 +6979,7 @@
       <c r="E109" s="10"/>
       <c r="F109" s="7"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
         <v>33</v>
       </c>
@@ -6975,7 +6995,7 @@
       <c r="E110" s="10"/>
       <c r="F110" s="7"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
         <v>33</v>
       </c>
@@ -6991,7 +7011,7 @@
       <c r="E111" s="10"/>
       <c r="F111" s="7"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
         <v>33</v>
       </c>
@@ -7007,7 +7027,7 @@
       <c r="E112" s="10"/>
       <c r="F112" s="7"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
         <v>33</v>
       </c>
@@ -7023,7 +7043,7 @@
       <c r="E113" s="10"/>
       <c r="F113" s="7"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
         <v>33</v>
       </c>
@@ -7039,7 +7059,7 @@
       <c r="E114" s="10"/>
       <c r="F114" s="7"/>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
         <v>33</v>
       </c>
@@ -7055,7 +7075,7 @@
       <c r="E115" s="10"/>
       <c r="F115" s="7"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
         <v>33</v>
       </c>
@@ -7071,7 +7091,7 @@
       <c r="E116" s="10"/>
       <c r="F116" s="7"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
         <v>33</v>
       </c>
@@ -7087,7 +7107,7 @@
       <c r="E117" s="10"/>
       <c r="F117" s="7"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
         <v>33</v>
       </c>
@@ -7103,7 +7123,7 @@
       <c r="E118" s="10"/>
       <c r="F118" s="7"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
         <v>33</v>
       </c>
@@ -7119,7 +7139,7 @@
       <c r="E119" s="10"/>
       <c r="F119" s="7"/>
     </row>
-    <row r="120" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
         <v>37</v>
       </c>
@@ -7137,7 +7157,7 @@
       </c>
       <c r="F120" s="7"/>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
         <v>37</v>
       </c>
@@ -7153,7 +7173,7 @@
       <c r="E121" s="10"/>
       <c r="F121" s="7"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
         <v>37</v>
       </c>
@@ -7169,7 +7189,7 @@
       <c r="E122" s="10"/>
       <c r="F122" s="7"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
         <v>37</v>
       </c>
@@ -7185,7 +7205,7 @@
       <c r="E123" s="10"/>
       <c r="F123" s="7"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
         <v>37</v>
       </c>
@@ -7201,7 +7221,7 @@
       <c r="E124" s="10"/>
       <c r="F124" s="7"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
         <v>37</v>
       </c>
@@ -7217,7 +7237,7 @@
       <c r="E125" s="10"/>
       <c r="F125" s="7"/>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
         <v>37</v>
       </c>
@@ -7233,7 +7253,7 @@
       <c r="E126" s="10"/>
       <c r="F126" s="7"/>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
         <v>37</v>
       </c>
@@ -7249,7 +7269,7 @@
       <c r="E127" s="10"/>
       <c r="F127" s="7"/>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
         <v>37</v>
       </c>
@@ -7265,7 +7285,7 @@
       <c r="E128" s="10"/>
       <c r="F128" s="7"/>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
         <v>37</v>
       </c>
@@ -7281,7 +7301,7 @@
       <c r="E129" s="10"/>
       <c r="F129" s="7"/>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
         <v>37</v>
       </c>
@@ -7297,7 +7317,7 @@
       <c r="E130" s="10"/>
       <c r="F130" s="7"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
         <v>37</v>
       </c>
@@ -7313,7 +7333,7 @@
       <c r="E131" s="10"/>
       <c r="F131" s="7"/>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
         <v>37</v>
       </c>
@@ -7329,7 +7349,7 @@
       <c r="E132" s="10"/>
       <c r="F132" s="7"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
         <v>37</v>
       </c>
@@ -7345,7 +7365,7 @@
       <c r="E133" s="10"/>
       <c r="F133" s="7"/>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
         <v>37</v>
       </c>
@@ -7361,7 +7381,7 @@
       <c r="E134" s="10"/>
       <c r="F134" s="7"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
         <v>37</v>
       </c>
@@ -7377,7 +7397,7 @@
       <c r="E135" s="10"/>
       <c r="F135" s="7"/>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
         <v>37</v>
       </c>
@@ -7393,7 +7413,7 @@
       <c r="E136" s="10"/>
       <c r="F136" s="7"/>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
         <v>37</v>
       </c>
@@ -7409,7 +7429,7 @@
       <c r="E137" s="10"/>
       <c r="F137" s="7"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
         <v>37</v>
       </c>
@@ -7425,7 +7445,7 @@
       <c r="E138" s="10"/>
       <c r="F138" s="7"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
         <v>37</v>
       </c>
@@ -7441,7 +7461,7 @@
       <c r="E139" s="10"/>
       <c r="F139" s="7"/>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
         <v>37</v>
       </c>
@@ -7457,7 +7477,7 @@
       <c r="E140" s="10"/>
       <c r="F140" s="7"/>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
         <v>37</v>
       </c>
@@ -7473,7 +7493,7 @@
       <c r="E141" s="10"/>
       <c r="F141" s="7"/>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
         <v>37</v>
       </c>
@@ -7731,7 +7751,7 @@
       <c r="E157" s="10"/>
       <c r="F157" s="7"/>
     </row>
-    <row r="158" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
         <v>35</v>
       </c>
@@ -7749,7 +7769,7 @@
       </c>
       <c r="F158" s="7"/>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
         <v>35</v>
       </c>
@@ -7765,7 +7785,7 @@
       <c r="E159" s="10"/>
       <c r="F159" s="7"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
         <v>35</v>
       </c>
@@ -7781,7 +7801,7 @@
       <c r="E160" s="10"/>
       <c r="F160" s="7"/>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
         <v>35</v>
       </c>
@@ -7797,7 +7817,7 @@
       <c r="E161" s="10"/>
       <c r="F161" s="7"/>
     </row>
-    <row r="162" spans="1:6" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
         <v>90</v>
       </c>
@@ -7815,7 +7835,7 @@
       </c>
       <c r="F162" s="7"/>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
         <v>90</v>
       </c>
@@ -7830,7 +7850,7 @@
       </c>
       <c r="E163" s="10"/>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
         <v>90</v>
       </c>
@@ -7846,7 +7866,7 @@
       <c r="E164" s="10"/>
       <c r="F164" s="7"/>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
         <v>90</v>
       </c>
@@ -7862,7 +7882,7 @@
       <c r="E165" s="10"/>
       <c r="F165" s="7"/>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
         <v>90</v>
       </c>
@@ -7878,7 +7898,7 @@
       <c r="E166" s="10"/>
       <c r="F166" s="7"/>
     </row>
-    <row r="167" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
         <v>90</v>
       </c>
@@ -7896,7 +7916,7 @@
       </c>
       <c r="F167" s="7"/>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
         <v>90</v>
       </c>
@@ -7912,7 +7932,7 @@
       <c r="E168" s="10"/>
       <c r="F168" s="7"/>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
         <v>90</v>
       </c>
@@ -7928,7 +7948,7 @@
       <c r="E169" s="10"/>
       <c r="F169" s="7"/>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
         <v>90</v>
       </c>
@@ -7944,7 +7964,7 @@
       <c r="E170" s="10"/>
       <c r="F170" s="7"/>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
         <v>90</v>
       </c>
@@ -7960,7 +7980,7 @@
       <c r="E171" s="10"/>
       <c r="F171" s="7"/>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
         <v>90</v>
       </c>
@@ -7976,7 +7996,7 @@
       <c r="E172" s="10"/>
       <c r="F172" s="7"/>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
         <v>90</v>
       </c>
@@ -7992,7 +8012,7 @@
       <c r="E173" s="10"/>
       <c r="F173" s="7"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
         <v>90</v>
       </c>
@@ -8008,7 +8028,7 @@
       <c r="E174" s="10"/>
       <c r="F174" s="7"/>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
         <v>90</v>
       </c>
@@ -8024,7 +8044,7 @@
       <c r="E175" s="10"/>
       <c r="F175" s="7"/>
     </row>
-    <row r="176" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
         <v>90</v>
       </c>
@@ -8042,7 +8062,7 @@
       </c>
       <c r="F176" s="7"/>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
         <v>90</v>
       </c>
@@ -8058,7 +8078,7 @@
       <c r="E177" s="10"/>
       <c r="F177" s="7"/>
     </row>
-    <row r="178" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
         <v>79</v>
       </c>
@@ -8076,7 +8096,7 @@
       </c>
       <c r="F178" s="7"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
         <v>79</v>
       </c>
@@ -8092,7 +8112,7 @@
       <c r="E179" s="10"/>
       <c r="F179" s="7"/>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
         <v>79</v>
       </c>
@@ -8108,7 +8128,7 @@
       <c r="E180" s="10"/>
       <c r="F180" s="7"/>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
         <v>79</v>
       </c>
@@ -8124,7 +8144,7 @@
       <c r="E181" s="10"/>
       <c r="F181" s="7"/>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
         <v>79</v>
       </c>
@@ -8140,7 +8160,7 @@
       <c r="E182" s="10"/>
       <c r="F182" s="7"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
         <v>79</v>
       </c>
@@ -8156,7 +8176,7 @@
       <c r="E183" s="10"/>
       <c r="F183" s="7"/>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
         <v>79</v>
       </c>
@@ -8172,7 +8192,7 @@
       <c r="E184" s="10"/>
       <c r="F184" s="7"/>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
         <v>79</v>
       </c>
@@ -8188,7 +8208,7 @@
       <c r="E185" s="10"/>
       <c r="F185" s="7"/>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
         <v>79</v>
       </c>
@@ -8204,7 +8224,7 @@
       <c r="E186" s="10"/>
       <c r="F186" s="7"/>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
         <v>79</v>
       </c>
@@ -8220,7 +8240,7 @@
       <c r="E187" s="10"/>
       <c r="F187" s="7"/>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
         <v>79</v>
       </c>
@@ -8236,7 +8256,7 @@
       <c r="E188" s="10"/>
       <c r="F188" s="7"/>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
         <v>79</v>
       </c>
@@ -8252,7 +8272,7 @@
       <c r="E189" s="10"/>
       <c r="F189" s="7"/>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="7" t="s">
         <v>79</v>
       </c>
@@ -8268,7 +8288,7 @@
       <c r="E190" s="10"/>
       <c r="F190" s="7"/>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
         <v>79</v>
       </c>
@@ -8284,7 +8304,7 @@
       <c r="E191" s="10"/>
       <c r="F191" s="7"/>
     </row>
-    <row r="192" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="7" t="s">
         <v>79</v>
       </c>
@@ -8302,7 +8322,7 @@
       </c>
       <c r="F192" s="7"/>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
         <v>79</v>
       </c>
@@ -8318,7 +8338,7 @@
       <c r="E193" s="10"/>
       <c r="F193" s="7"/>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="7" t="s">
         <v>79</v>
       </c>
@@ -8334,7 +8354,7 @@
       <c r="E194" s="10"/>
       <c r="F194" s="7"/>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
         <v>79</v>
       </c>
@@ -8350,7 +8370,7 @@
       <c r="E195" s="10"/>
       <c r="F195" s="7"/>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="7" t="s">
         <v>79</v>
       </c>
@@ -8366,7 +8386,7 @@
       <c r="E196" s="10"/>
       <c r="F196" s="7"/>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
         <v>79</v>
       </c>
@@ -8382,7 +8402,7 @@
       <c r="E197" s="10"/>
       <c r="F197" s="7"/>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
         <v>79</v>
       </c>
@@ -8398,7 +8418,7 @@
       <c r="E198" s="10"/>
       <c r="F198" s="7"/>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
         <v>79</v>
       </c>
@@ -8414,7 +8434,7 @@
       <c r="E199" s="10"/>
       <c r="F199" s="7"/>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
         <v>79</v>
       </c>
@@ -8430,7 +8450,7 @@
       <c r="E200" s="10"/>
       <c r="F200" s="7"/>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
         <v>79</v>
       </c>
@@ -8446,7 +8466,7 @@
       <c r="E201" s="10"/>
       <c r="F201" s="7"/>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
         <v>79</v>
       </c>
@@ -8462,7 +8482,7 @@
       <c r="E202" s="10"/>
       <c r="F202" s="7"/>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
         <v>79</v>
       </c>
@@ -8478,7 +8498,7 @@
       <c r="E203" s="10"/>
       <c r="F203" s="7"/>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
         <v>79</v>
       </c>
@@ -8494,7 +8514,7 @@
       <c r="E204" s="10"/>
       <c r="F204" s="7"/>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
         <v>79</v>
       </c>
@@ -8510,7 +8530,7 @@
       <c r="E205" s="10"/>
       <c r="F205" s="7"/>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="7" t="s">
         <v>79</v>
       </c>
@@ -8526,7 +8546,7 @@
       <c r="E206" s="10"/>
       <c r="F206" s="7"/>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
         <v>79</v>
       </c>
@@ -8542,7 +8562,7 @@
       <c r="E207" s="10"/>
       <c r="F207" s="7"/>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="7" t="s">
         <v>79</v>
       </c>
@@ -8558,7 +8578,7 @@
       <c r="E208" s="10"/>
       <c r="F208" s="7"/>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
         <v>79</v>
       </c>
@@ -8574,7 +8594,7 @@
       <c r="E209" s="10"/>
       <c r="F209" s="7"/>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="7" t="s">
         <v>39</v>
       </c>
@@ -8592,7 +8612,7 @@
       </c>
       <c r="F210" s="7"/>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
         <v>39</v>
       </c>
@@ -8608,7 +8628,7 @@
       <c r="E211" s="10"/>
       <c r="F211" s="7"/>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="7" t="s">
         <v>39</v>
       </c>
@@ -8624,7 +8644,7 @@
       <c r="E212" s="10"/>
       <c r="F212" s="7"/>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
         <v>39</v>
       </c>
@@ -8640,7 +8660,7 @@
       <c r="E213" s="10"/>
       <c r="F213" s="7"/>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="7" t="s">
         <v>39</v>
       </c>
@@ -8656,7 +8676,7 @@
       <c r="E214" s="10"/>
       <c r="F214" s="7"/>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="7" t="s">
         <v>39</v>
       </c>
@@ -8672,7 +8692,7 @@
       <c r="E215" s="10"/>
       <c r="F215" s="7"/>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="7" t="s">
         <v>39</v>
       </c>
@@ -8688,7 +8708,7 @@
       <c r="E216" s="10"/>
       <c r="F216" s="7"/>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="7" t="s">
         <v>39</v>
       </c>
@@ -8704,7 +8724,7 @@
       <c r="E217" s="10"/>
       <c r="F217" s="7"/>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="7" t="s">
         <v>39</v>
       </c>
@@ -8720,7 +8740,7 @@
       <c r="E218" s="10"/>
       <c r="F218" s="7"/>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="7" t="s">
         <v>39</v>
       </c>
@@ -8736,7 +8756,7 @@
       <c r="E219" s="10"/>
       <c r="F219" s="7"/>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="7" t="s">
         <v>39</v>
       </c>
@@ -8752,7 +8772,7 @@
       <c r="E220" s="10"/>
       <c r="F220" s="7"/>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
         <v>39</v>
       </c>
@@ -8768,7 +8788,7 @@
       <c r="E221" s="10"/>
       <c r="F221" s="7"/>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="7" t="s">
         <v>39</v>
       </c>
@@ -8784,7 +8804,7 @@
       <c r="E222" s="10"/>
       <c r="F222" s="7"/>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="7" t="s">
         <v>39</v>
       </c>
@@ -8800,7 +8820,7 @@
       <c r="E223" s="10"/>
       <c r="F223" s="7"/>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="7" t="s">
         <v>39</v>
       </c>
@@ -8816,7 +8836,7 @@
       <c r="E224" s="10"/>
       <c r="F224" s="7"/>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
         <v>39</v>
       </c>
@@ -8832,7 +8852,7 @@
       <c r="E225" s="10"/>
       <c r="F225" s="7"/>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="7" t="s">
         <v>39</v>
       </c>
@@ -8848,7 +8868,7 @@
       <c r="E226" s="10"/>
       <c r="F226" s="7"/>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
         <v>39</v>
       </c>
@@ -8864,7 +8884,7 @@
       <c r="E227" s="10"/>
       <c r="F227" s="7"/>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="7" t="s">
         <v>39</v>
       </c>
@@ -8880,7 +8900,7 @@
       <c r="E228" s="10"/>
       <c r="F228" s="7"/>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
         <v>39</v>
       </c>
@@ -8896,7 +8916,7 @@
       <c r="E229" s="10"/>
       <c r="F229" s="7"/>
     </row>
-    <row r="230" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="7" t="s">
         <v>36</v>
       </c>
@@ -8914,7 +8934,7 @@
       </c>
       <c r="F230" s="7"/>
     </row>
-    <row r="231" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
         <v>36</v>
       </c>
@@ -8932,7 +8952,7 @@
       </c>
       <c r="F231" s="7"/>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="7" t="s">
         <v>36</v>
       </c>
@@ -8948,7 +8968,7 @@
       <c r="E232" s="10"/>
       <c r="F232" s="7"/>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="7" t="s">
         <v>36</v>
       </c>
@@ -8964,7 +8984,7 @@
       <c r="E233" s="10"/>
       <c r="F233" s="7"/>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="7" t="s">
         <v>36</v>
       </c>
@@ -8980,7 +9000,7 @@
       <c r="E234" s="10"/>
       <c r="F234" s="7"/>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="7" t="s">
         <v>36</v>
       </c>
@@ -8996,7 +9016,7 @@
       <c r="E235" s="10"/>
       <c r="F235" s="7"/>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="7" t="s">
         <v>36</v>
       </c>
@@ -9012,7 +9032,7 @@
       <c r="E236" s="10"/>
       <c r="F236" s="7"/>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="7" t="s">
         <v>36</v>
       </c>
@@ -9028,7 +9048,7 @@
       <c r="E237" s="10"/>
       <c r="F237" s="7"/>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="7" t="s">
         <v>36</v>
       </c>
@@ -9044,7 +9064,7 @@
       <c r="E238" s="10"/>
       <c r="F238" s="7"/>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="7" t="s">
         <v>36</v>
       </c>
@@ -9060,7 +9080,7 @@
       <c r="E239" s="10"/>
       <c r="F239" s="7"/>
     </row>
-    <row r="240" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="7" t="s">
         <v>38</v>
       </c>
@@ -9078,7 +9098,7 @@
       </c>
       <c r="F240" s="7"/>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="7" t="s">
         <v>38</v>
       </c>
@@ -9094,7 +9114,7 @@
       <c r="E241" s="10"/>
       <c r="F241" s="7"/>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="7" t="s">
         <v>38</v>
       </c>
@@ -9110,7 +9130,7 @@
       <c r="E242" s="10"/>
       <c r="F242" s="7"/>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="7" t="s">
         <v>38</v>
       </c>
@@ -9126,7 +9146,7 @@
       <c r="E243" s="10"/>
       <c r="F243" s="7"/>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="7" t="s">
         <v>38</v>
       </c>
@@ -9142,7 +9162,7 @@
       <c r="E244" s="10"/>
       <c r="F244" s="7"/>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="7" t="s">
         <v>38</v>
       </c>
@@ -9158,7 +9178,7 @@
       <c r="E245" s="10"/>
       <c r="F245" s="7"/>
     </row>
-    <row r="246" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="7" t="s">
         <v>38</v>
       </c>
@@ -9176,7 +9196,7 @@
       </c>
       <c r="F246" s="7"/>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="7" t="s">
         <v>38</v>
       </c>
@@ -9192,7 +9212,7 @@
       <c r="E247" s="10"/>
       <c r="F247" s="7"/>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="7" t="s">
         <v>38</v>
       </c>
@@ -9208,7 +9228,7 @@
       <c r="E248" s="10"/>
       <c r="F248" s="7"/>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
         <v>38</v>
       </c>
@@ -9224,7 +9244,7 @@
       <c r="E249" s="10"/>
       <c r="F249" s="7"/>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="7" t="s">
         <v>38</v>
       </c>
@@ -9240,7 +9260,7 @@
       <c r="E250" s="10"/>
       <c r="F250" s="7"/>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="7" t="s">
         <v>38</v>
       </c>
@@ -9256,7 +9276,7 @@
       <c r="E251" s="10"/>
       <c r="F251" s="7"/>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="7" t="s">
         <v>38</v>
       </c>
@@ -9272,7 +9292,7 @@
       <c r="E252" s="10"/>
       <c r="F252" s="7"/>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
         <v>38</v>
       </c>
@@ -9288,7 +9308,7 @@
       <c r="E253" s="10"/>
       <c r="F253" s="7"/>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="7" t="s">
         <v>38</v>
       </c>
@@ -9304,7 +9324,7 @@
       <c r="E254" s="10"/>
       <c r="F254" s="7"/>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
         <v>38</v>
       </c>
@@ -9320,7 +9340,7 @@
       <c r="E255" s="10"/>
       <c r="F255" s="7"/>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="7" t="s">
         <v>38</v>
       </c>
@@ -9336,7 +9356,7 @@
       <c r="E256" s="10"/>
       <c r="F256" s="7"/>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
         <v>38</v>
       </c>
@@ -9352,7 +9372,7 @@
       <c r="E257" s="10"/>
       <c r="F257" s="7"/>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="7" t="s">
         <v>38</v>
       </c>
@@ -9368,7 +9388,7 @@
       <c r="E258" s="10"/>
       <c r="F258" s="7"/>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
         <v>38</v>
       </c>
@@ -9384,7 +9404,7 @@
       <c r="E259" s="10"/>
       <c r="F259" s="7"/>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="7" t="s">
         <v>38</v>
       </c>
@@ -9400,7 +9420,7 @@
       <c r="E260" s="10"/>
       <c r="F260" s="7"/>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
         <v>38</v>
       </c>
@@ -9416,7 +9436,7 @@
       <c r="E261" s="10"/>
       <c r="F261" s="7"/>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="7" t="s">
         <v>38</v>
       </c>
@@ -9432,7 +9452,7 @@
       <c r="E262" s="10"/>
       <c r="F262" s="7"/>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
         <v>38</v>
       </c>
@@ -9448,7 +9468,7 @@
       <c r="E263" s="10"/>
       <c r="F263" s="7"/>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="7" t="s">
         <v>38</v>
       </c>
@@ -9464,7 +9484,7 @@
       <c r="E264" s="10"/>
       <c r="F264" s="7"/>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
         <v>38</v>
       </c>
@@ -9480,7 +9500,7 @@
       <c r="E265" s="10"/>
       <c r="F265" s="7"/>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="7" t="s">
         <v>38</v>
       </c>
@@ -9496,7 +9516,7 @@
       <c r="E266" s="10"/>
       <c r="F266" s="7"/>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
         <v>38</v>
       </c>
@@ -9512,7 +9532,7 @@
       <c r="E267" s="10"/>
       <c r="F267" s="7"/>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="7" t="s">
         <v>38</v>
       </c>
@@ -9528,7 +9548,7 @@
       <c r="E268" s="10"/>
       <c r="F268" s="7"/>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
         <v>38</v>
       </c>
@@ -9544,7 +9564,7 @@
       <c r="E269" s="10"/>
       <c r="F269" s="7"/>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="7" t="s">
         <v>38</v>
       </c>
@@ -9560,7 +9580,7 @@
       <c r="E270" s="10"/>
       <c r="F270" s="7"/>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
         <v>38</v>
       </c>
@@ -9576,7 +9596,7 @@
       <c r="E271" s="10"/>
       <c r="F271" s="7"/>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="7" t="s">
         <v>38</v>
       </c>
@@ -9592,7 +9612,7 @@
       <c r="E272" s="10"/>
       <c r="F272" s="7"/>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
         <v>38</v>
       </c>
@@ -9608,7 +9628,7 @@
       <c r="E273" s="10"/>
       <c r="F273" s="7"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="7" t="s">
         <v>38</v>
       </c>
@@ -9624,7 +9644,7 @@
       <c r="E274" s="10"/>
       <c r="F274" s="7"/>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="7" t="s">
         <v>38</v>
       </c>
@@ -9640,7 +9660,7 @@
       <c r="E275" s="10"/>
       <c r="F275" s="7"/>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="7" t="s">
         <v>38</v>
       </c>
@@ -9656,7 +9676,7 @@
       <c r="E276" s="10"/>
       <c r="F276" s="7"/>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="7" t="s">
         <v>38</v>
       </c>
@@ -9672,7 +9692,7 @@
       <c r="E277" s="10"/>
       <c r="F277" s="7"/>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="7" t="s">
         <v>38</v>
       </c>
@@ -9688,7 +9708,7 @@
       <c r="E278" s="10"/>
       <c r="F278" s="7"/>
     </row>
-    <row r="279" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
         <v>38</v>
       </c>
@@ -9706,7 +9726,7 @@
       </c>
       <c r="F279" s="7"/>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="7" t="s">
         <v>38</v>
       </c>
@@ -9722,7 +9742,7 @@
       <c r="E280" s="10"/>
       <c r="F280" s="7"/>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="7" t="s">
         <v>38</v>
       </c>
@@ -9738,7 +9758,7 @@
       <c r="E281" s="10"/>
       <c r="F281" s="7"/>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="7" t="s">
         <v>38</v>
       </c>
@@ -9754,7 +9774,7 @@
       <c r="E282" s="10"/>
       <c r="F282" s="7"/>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="7" t="s">
         <v>38</v>
       </c>
@@ -9770,7 +9790,7 @@
       <c r="E283" s="10"/>
       <c r="F283" s="7"/>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="7" t="s">
         <v>38</v>
       </c>
@@ -9786,7 +9806,7 @@
       <c r="E284" s="10"/>
       <c r="F284" s="7"/>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="7" t="s">
         <v>38</v>
       </c>
@@ -9802,7 +9822,7 @@
       <c r="E285" s="10"/>
       <c r="F285" s="7"/>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="7" t="s">
         <v>38</v>
       </c>
@@ -9818,7 +9838,7 @@
       <c r="E286" s="10"/>
       <c r="F286" s="7"/>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="7" t="s">
         <v>38</v>
       </c>
@@ -9834,7 +9854,7 @@
       <c r="E287" s="10"/>
       <c r="F287" s="7"/>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="7" t="s">
         <v>38</v>
       </c>
@@ -9850,7 +9870,7 @@
       <c r="E288" s="10"/>
       <c r="F288" s="7"/>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="7" t="s">
         <v>38</v>
       </c>
@@ -9866,7 +9886,7 @@
       <c r="E289" s="10"/>
       <c r="F289" s="7"/>
     </row>
-    <row r="290" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="7" t="s">
         <v>38</v>
       </c>
@@ -9884,7 +9904,7 @@
       </c>
       <c r="F290" s="7"/>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="7" t="s">
         <v>38</v>
       </c>
@@ -9900,7 +9920,7 @@
       <c r="E291" s="10"/>
       <c r="F291" s="7"/>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="7" t="s">
         <v>38</v>
       </c>
@@ -9916,7 +9936,7 @@
       <c r="E292" s="10"/>
       <c r="F292" s="7"/>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="7" t="s">
         <v>38</v>
       </c>
@@ -9932,7 +9952,7 @@
       <c r="E293" s="10"/>
       <c r="F293" s="7"/>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="7" t="s">
         <v>38</v>
       </c>
@@ -9948,7 +9968,7 @@
       <c r="E294" s="10"/>
       <c r="F294" s="7"/>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="7" t="s">
         <v>38</v>
       </c>
@@ -9964,7 +9984,7 @@
       <c r="E295" s="10"/>
       <c r="F295" s="7"/>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="7" t="s">
         <v>38</v>
       </c>
@@ -9980,7 +10000,7 @@
       <c r="E296" s="10"/>
       <c r="F296" s="7"/>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="7" t="s">
         <v>38</v>
       </c>
@@ -9996,7 +10016,7 @@
       <c r="E297" s="10"/>
       <c r="F297" s="7"/>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="7" t="s">
         <v>38</v>
       </c>
@@ -10012,7 +10032,7 @@
       <c r="E298" s="10"/>
       <c r="F298" s="7"/>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="7" t="s">
         <v>38</v>
       </c>
@@ -10028,7 +10048,7 @@
       <c r="E299" s="10"/>
       <c r="F299" s="7"/>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="7" t="s">
         <v>38</v>
       </c>
@@ -10046,6 +10066,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F300" xr:uid="{38A162FC-7907-44C7-A909-E8E1323EC5F6}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="nile_tilapia"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A240:F300">
       <sortCondition ref="D1:D300"/>
     </sortState>
@@ -10075,7 +10100,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4A353B5-0CCF-4CD3-981F-8A6F6874C0EC}">
-  <dimension ref="A1:W29"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" style="16" bestFit="1" customWidth="1"/>
@@ -10179,7 +10204,9 @@
       <c r="O2" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="P2" s="30"/>
+      <c r="P2" s="47" t="s">
+        <v>234</v>
+      </c>
       <c r="Q2" s="37" t="s">
         <v>235</v>
       </c>
@@ -10395,7 +10422,9 @@
       <c r="O6" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="P6" s="36"/>
+      <c r="P6" s="50" t="s">
+        <v>234</v>
+      </c>
       <c r="Q6" s="36"/>
       <c r="R6" s="35" t="s">
         <v>234</v>
@@ -10429,8 +10458,8 @@
       <c r="I7" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="K7" s="16" t="s">
-        <v>235</v>
+      <c r="K7" s="48" t="s">
+        <v>234</v>
       </c>
       <c r="L7" s="16" t="s">
         <v>234</v>
@@ -10555,166 +10584,249 @@
         <v>0.18333752199044986</v>
       </c>
       <c r="D12" s="20">
-        <f t="shared" ref="D12:R12" si="0">D11/SUM($C11:$R11)</f>
+        <f>D11/SUM($C11:$R11)</f>
         <v>4.9258607690374469E-2</v>
       </c>
       <c r="E12" s="20">
+        <f>E11/SUM($C11:$R11)</f>
+        <v>3.0849459663231969E-2</v>
+      </c>
+      <c r="F12" s="20">
+        <f>F11/SUM($C11:$R11)</f>
+        <v>2.9592862528273436E-2</v>
+      </c>
+      <c r="G12" s="20">
+        <f>G11/SUM($C11:$R11)</f>
+        <v>1.4765016335762755E-2</v>
+      </c>
+      <c r="H12" s="20">
+        <f>H11/SUM($C11:$R11)</f>
+        <v>0.3847700427243026</v>
+      </c>
+      <c r="I12" s="20">
+        <f>I11/SUM($C11:$R11)</f>
+        <v>4.6871073133953257E-2</v>
+      </c>
+      <c r="J12" s="20">
+        <f>J11/SUM($C11:$R11)</f>
+        <v>4.4420708720784116E-2</v>
+      </c>
+      <c r="K12" s="20">
+        <f>K11/SUM($C11:$R11)</f>
+        <v>1.5895953757225433E-2</v>
+      </c>
+      <c r="L12" s="20">
+        <f>L11/SUM($C11:$R11)</f>
+        <v>1.577029404372958E-2</v>
+      </c>
+      <c r="M12" s="20">
+        <f>M11/SUM($C11:$R11)</f>
+        <v>1.46393566222669E-2</v>
+      </c>
+      <c r="N12" s="20">
+        <f>N11/SUM($C11:$R11)</f>
+        <v>1.4262377481779342E-2</v>
+      </c>
+      <c r="O12" s="20">
+        <f>O11/SUM($C11:$R11)</f>
+        <v>1.2000502638853983E-2</v>
+      </c>
+      <c r="P12" s="20">
+        <f>P11/SUM($C11:$R11)</f>
+        <v>6.0316662478009549E-3</v>
+      </c>
+      <c r="Q12" s="20">
+        <f>Q11/SUM($C11:$R11)</f>
+        <v>1.4262377481779342E-2</v>
+      </c>
+      <c r="R12" s="20">
+        <f>R11/SUM($C11:$R11)</f>
+        <v>0.12327217893943201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B13" s="49" t="s">
+        <v>269</v>
+      </c>
+      <c r="C13" s="20">
+        <f>COUNTA(C2:C7)/6*C12</f>
+        <v>0.18333752199044986</v>
+      </c>
+      <c r="D13" s="20">
+        <f t="shared" ref="D13:R13" si="0">COUNTA(D2:D7)/6*D12</f>
+        <v>4.9258607690374469E-2</v>
+      </c>
+      <c r="E13" s="20">
         <f t="shared" si="0"/>
         <v>3.0849459663231969E-2</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F13" s="20">
         <f t="shared" si="0"/>
         <v>2.9592862528273436E-2</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G13" s="20">
         <f t="shared" si="0"/>
         <v>1.4765016335762755E-2</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H13" s="20">
         <f t="shared" si="0"/>
         <v>0.3847700427243026</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I13" s="20">
         <f t="shared" si="0"/>
         <v>4.6871073133953257E-2</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J13" s="20">
         <f t="shared" si="0"/>
-        <v>4.4420708720784116E-2</v>
-      </c>
-      <c r="K12" s="20">
+        <v>2.2210354360392058E-2</v>
+      </c>
+      <c r="K13" s="20">
         <f t="shared" si="0"/>
         <v>1.5895953757225433E-2</v>
       </c>
-      <c r="L12" s="20">
+      <c r="L13" s="20">
         <f t="shared" si="0"/>
         <v>1.577029404372958E-2</v>
       </c>
-      <c r="M12" s="20">
+      <c r="M13" s="20">
         <f t="shared" si="0"/>
-        <v>1.46393566222669E-2</v>
-      </c>
-      <c r="N12" s="20">
+        <v>7.3196783111334502E-3</v>
+      </c>
+      <c r="N13" s="20">
         <f t="shared" si="0"/>
-        <v>1.4262377481779342E-2</v>
-      </c>
-      <c r="O12" s="20">
+        <v>7.1311887408896709E-3</v>
+      </c>
+      <c r="O13" s="20">
         <f t="shared" si="0"/>
         <v>1.2000502638853983E-2</v>
       </c>
-      <c r="P12" s="20">
+      <c r="P13" s="20">
         <f t="shared" si="0"/>
-        <v>6.0316662478009549E-3</v>
-      </c>
-      <c r="Q12" s="20">
+        <v>5.0263885398341293E-3</v>
+      </c>
+      <c r="Q13" s="20">
         <f t="shared" si="0"/>
-        <v>1.4262377481779342E-2</v>
-      </c>
-      <c r="R12" s="20">
+        <v>9.5082516545195606E-3</v>
+      </c>
+      <c r="R13" s="20">
         <f t="shared" si="0"/>
         <v>0.12327217893943201</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="17" t="s">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B14" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C14" s="20">
         <f>COUNTA(C2:C9)/8*C12</f>
         <v>0.13750314149283741</v>
       </c>
-      <c r="D13" s="20">
-        <f t="shared" ref="D13:R13" si="1">COUNTA(D2:D9)/8*D12</f>
+      <c r="D14" s="20">
+        <f>COUNTA(D2:D9)/8*D12</f>
         <v>3.6943955767780853E-2</v>
       </c>
-      <c r="E13" s="20">
-        <f t="shared" si="1"/>
+      <c r="E14" s="20">
+        <f>COUNTA(E2:E9)/8*E12</f>
         <v>2.3137094747423977E-2</v>
       </c>
-      <c r="F13" s="20">
-        <f t="shared" si="1"/>
+      <c r="F14" s="20">
+        <f>COUNTA(F2:F9)/8*F12</f>
         <v>2.2194646896205077E-2</v>
       </c>
-      <c r="G13" s="20">
-        <f t="shared" si="1"/>
+      <c r="G14" s="20">
+        <f>COUNTA(G2:G9)/8*G12</f>
         <v>1.1073762251822066E-2</v>
       </c>
-      <c r="H13" s="20">
-        <f t="shared" si="1"/>
+      <c r="H14" s="20">
+        <f>COUNTA(H2:H9)/8*H12</f>
         <v>0.28857753204322695</v>
       </c>
-      <c r="I13" s="20">
-        <f t="shared" si="1"/>
+      <c r="I14" s="20">
+        <f>COUNTA(I2:I9)/8*I12</f>
         <v>3.5153304850464945E-2</v>
       </c>
-      <c r="J13" s="20">
-        <f t="shared" si="1"/>
+      <c r="J14" s="20">
+        <f>COUNTA(J2:J9)/8*J12</f>
         <v>1.6657765770294042E-2</v>
       </c>
-      <c r="K13" s="20">
-        <f t="shared" si="1"/>
+      <c r="K14" s="20">
+        <f>COUNTA(K2:K9)/8*K12</f>
         <v>1.1921965317919074E-2</v>
       </c>
-      <c r="L13" s="20">
-        <f t="shared" si="1"/>
+      <c r="L14" s="20">
+        <f>COUNTA(L2:L9)/8*L12</f>
         <v>1.1827720532797185E-2</v>
       </c>
-      <c r="M13" s="20">
-        <f t="shared" si="1"/>
+      <c r="M14" s="20">
+        <f>COUNTA(M2:M9)/8*M12</f>
         <v>5.4897587333500881E-3</v>
       </c>
-      <c r="N13" s="20">
-        <f t="shared" si="1"/>
+      <c r="N14" s="20">
+        <f>COUNTA(N2:N9)/8*N12</f>
         <v>5.3483915556672527E-3</v>
       </c>
-      <c r="O13" s="20">
-        <f t="shared" si="1"/>
+      <c r="O14" s="20">
+        <f>COUNTA(O2:O9)/8*O12</f>
         <v>9.0003769791404883E-3</v>
       </c>
-      <c r="P13" s="20">
-        <f t="shared" si="1"/>
-        <v>2.2618748429253581E-3</v>
-      </c>
-      <c r="Q13" s="20">
-        <f t="shared" si="1"/>
+      <c r="P14" s="20">
+        <f>COUNTA(P2:P9)/8*P12</f>
+        <v>3.7697914048755968E-3</v>
+      </c>
+      <c r="Q14" s="20">
+        <f>COUNTA(Q2:Q9)/8*Q12</f>
         <v>7.1311887408896709E-3</v>
       </c>
-      <c r="R13" s="20">
-        <f t="shared" si="1"/>
+      <c r="R14" s="20">
+        <f>COUNTA(R2:R9)/8*R12</f>
         <v>9.2454134204574018E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="19" t="s">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B15" s="49" t="s">
+        <v>268</v>
+      </c>
+      <c r="C15" s="18">
+        <f>SUM(C13:R13)</f>
+        <v>0.95757937505235824</v>
+      </c>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B16" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="C14" s="18">
-        <f>SUM(C13:R13)</f>
-        <v>0.71667661472731869</v>
-      </c>
-    </row>
-    <row r="19" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="T19" s="46"/>
-    </row>
-    <row r="20" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="T20" s="46"/>
+      <c r="C16" s="18">
+        <f>SUM(C14:R14)</f>
+        <v>0.71818453128926885</v>
+      </c>
     </row>
     <row r="21" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S21" s="46"/>
       <c r="T21" s="46"/>
-      <c r="U21" s="46"/>
-      <c r="V21" s="46"/>
-      <c r="W21" s="46"/>
     </row>
     <row r="22" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S22" s="46"/>
       <c r="T22" s="46"/>
-      <c r="U22" s="46"/>
     </row>
     <row r="23" spans="19:23" x14ac:dyDescent="0.25">
       <c r="S23" s="46"/>
       <c r="T23" s="46"/>
       <c r="U23" s="46"/>
+      <c r="V23" s="46"/>
+      <c r="W23" s="46"/>
     </row>
     <row r="24" spans="19:23" x14ac:dyDescent="0.25">
       <c r="S24" s="46"/>
@@ -10745,6 +10857,16 @@
       <c r="S29" s="46"/>
       <c r="T29" s="46"/>
       <c r="U29" s="46"/>
+    </row>
+    <row r="30" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S30" s="46"/>
+      <c r="T30" s="46"/>
+      <c r="U30" s="46"/>
+    </row>
+    <row r="31" spans="19:23" x14ac:dyDescent="0.25">
+      <c r="S31" s="46"/>
+      <c r="T31" s="46"/>
+      <c r="U31" s="46"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:R10">

--- a/data/raw_data/feed_profiles_and_composition.xlsx
+++ b/data/raw_data/feed_profiles_and_composition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\climate_risks_to_fed_mariculture\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D568A87B-F0F4-4A52-8323-5446FF3D895B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C4D544-BF4A-4F7D-A2FE-1BB52A9F7EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="270">
   <si>
     <t>ingredient</t>
   </si>
@@ -879,11 +879,18 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1170,79 +1177,82 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="4" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
@@ -5183,7 +5193,7 @@
       <sortCondition ref="A1:A229"/>
     </sortState>
   </autoFilter>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D95" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
   </hyperlinks>
@@ -10192,7 +10202,9 @@
       <c r="I2" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="J2" s="30"/>
+      <c r="J2" s="52" t="s">
+        <v>234</v>
+      </c>
       <c r="K2" s="43" t="s">
         <v>234</v>
       </c>
@@ -10207,9 +10219,7 @@
       <c r="P2" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="Q2" s="37" t="s">
-        <v>235</v>
-      </c>
+      <c r="Q2" s="37"/>
       <c r="R2" s="29" t="s">
         <v>234</v>
       </c>
@@ -10410,7 +10420,9 @@
       <c r="I6" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="J6" s="36"/>
+      <c r="J6" s="53" t="s">
+        <v>234</v>
+      </c>
       <c r="K6" s="44" t="s">
         <v>234</v>
       </c>
@@ -10458,6 +10470,9 @@
       <c r="I7" s="16" t="s">
         <v>234</v>
       </c>
+      <c r="J7" s="51" t="s">
+        <v>235</v>
+      </c>
       <c r="K7" s="48" t="s">
         <v>234</v>
       </c>
@@ -10465,6 +10480,9 @@
         <v>234</v>
       </c>
       <c r="O7" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="P7" s="51" t="s">
         <v>234</v>
       </c>
       <c r="R7" s="34" t="s">
@@ -10580,67 +10598,67 @@
         <v>232</v>
       </c>
       <c r="C12" s="20">
-        <f>C11/SUM($C11:$R11)</f>
+        <f t="shared" ref="C12:R12" si="0">C11/SUM($C11:$R11)</f>
         <v>0.18333752199044986</v>
       </c>
       <c r="D12" s="20">
-        <f>D11/SUM($C11:$R11)</f>
+        <f t="shared" si="0"/>
         <v>4.9258607690374469E-2</v>
       </c>
       <c r="E12" s="20">
-        <f>E11/SUM($C11:$R11)</f>
+        <f t="shared" si="0"/>
         <v>3.0849459663231969E-2</v>
       </c>
       <c r="F12" s="20">
-        <f>F11/SUM($C11:$R11)</f>
+        <f t="shared" si="0"/>
         <v>2.9592862528273436E-2</v>
       </c>
       <c r="G12" s="20">
-        <f>G11/SUM($C11:$R11)</f>
+        <f t="shared" si="0"/>
         <v>1.4765016335762755E-2</v>
       </c>
       <c r="H12" s="20">
-        <f>H11/SUM($C11:$R11)</f>
+        <f t="shared" si="0"/>
         <v>0.3847700427243026</v>
       </c>
       <c r="I12" s="20">
-        <f>I11/SUM($C11:$R11)</f>
+        <f t="shared" si="0"/>
         <v>4.6871073133953257E-2</v>
       </c>
       <c r="J12" s="20">
-        <f>J11/SUM($C11:$R11)</f>
+        <f t="shared" si="0"/>
         <v>4.4420708720784116E-2</v>
       </c>
       <c r="K12" s="20">
-        <f>K11/SUM($C11:$R11)</f>
+        <f t="shared" si="0"/>
         <v>1.5895953757225433E-2</v>
       </c>
       <c r="L12" s="20">
-        <f>L11/SUM($C11:$R11)</f>
+        <f t="shared" si="0"/>
         <v>1.577029404372958E-2</v>
       </c>
       <c r="M12" s="20">
-        <f>M11/SUM($C11:$R11)</f>
+        <f t="shared" si="0"/>
         <v>1.46393566222669E-2</v>
       </c>
       <c r="N12" s="20">
-        <f>N11/SUM($C11:$R11)</f>
+        <f t="shared" si="0"/>
         <v>1.4262377481779342E-2</v>
       </c>
       <c r="O12" s="20">
-        <f>O11/SUM($C11:$R11)</f>
+        <f t="shared" si="0"/>
         <v>1.2000502638853983E-2</v>
       </c>
       <c r="P12" s="20">
-        <f>P11/SUM($C11:$R11)</f>
+        <f t="shared" si="0"/>
         <v>6.0316662478009549E-3</v>
       </c>
       <c r="Q12" s="20">
-        <f>Q11/SUM($C11:$R11)</f>
+        <f t="shared" si="0"/>
         <v>1.4262377481779342E-2</v>
       </c>
       <c r="R12" s="20">
-        <f>R11/SUM($C11:$R11)</f>
+        <f t="shared" si="0"/>
         <v>0.12327217893943201</v>
       </c>
     </row>
@@ -10653,63 +10671,63 @@
         <v>0.18333752199044986</v>
       </c>
       <c r="D13" s="20">
-        <f t="shared" ref="D13:R13" si="0">COUNTA(D2:D7)/6*D12</f>
+        <f t="shared" ref="D13:R13" si="1">COUNTA(D2:D7)/6*D12</f>
         <v>4.9258607690374469E-2</v>
       </c>
       <c r="E13" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.0849459663231969E-2</v>
       </c>
       <c r="F13" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.9592862528273436E-2</v>
       </c>
       <c r="G13" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.4765016335762755E-2</v>
       </c>
       <c r="H13" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.3847700427243026</v>
       </c>
       <c r="I13" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.6871073133953257E-2</v>
       </c>
       <c r="J13" s="20">
-        <f t="shared" si="0"/>
-        <v>2.2210354360392058E-2</v>
+        <f t="shared" si="1"/>
+        <v>4.4420708720784116E-2</v>
       </c>
       <c r="K13" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.5895953757225433E-2</v>
       </c>
       <c r="L13" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.577029404372958E-2</v>
       </c>
       <c r="M13" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.3196783111334502E-3</v>
       </c>
       <c r="N13" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.1311887408896709E-3</v>
       </c>
       <c r="O13" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2000502638853983E-2</v>
       </c>
       <c r="P13" s="20">
-        <f t="shared" si="0"/>
-        <v>5.0263885398341293E-3</v>
+        <f t="shared" si="1"/>
+        <v>6.0316662478009549E-3</v>
       </c>
       <c r="Q13" s="20">
-        <f t="shared" si="0"/>
-        <v>9.5082516545195606E-3</v>
+        <f t="shared" si="1"/>
+        <v>7.1311887408896709E-3</v>
       </c>
       <c r="R13" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.12327217893943201</v>
       </c>
     </row>
@@ -10718,67 +10736,67 @@
         <v>231</v>
       </c>
       <c r="C14" s="20">
-        <f>COUNTA(C2:C9)/8*C12</f>
+        <f t="shared" ref="C14:R14" si="2">COUNTA(C2:C9)/8*C12</f>
         <v>0.13750314149283741</v>
       </c>
       <c r="D14" s="20">
-        <f>COUNTA(D2:D9)/8*D12</f>
+        <f t="shared" si="2"/>
         <v>3.6943955767780853E-2</v>
       </c>
       <c r="E14" s="20">
-        <f>COUNTA(E2:E9)/8*E12</f>
+        <f t="shared" si="2"/>
         <v>2.3137094747423977E-2</v>
       </c>
       <c r="F14" s="20">
-        <f>COUNTA(F2:F9)/8*F12</f>
+        <f t="shared" si="2"/>
         <v>2.2194646896205077E-2</v>
       </c>
       <c r="G14" s="20">
-        <f>COUNTA(G2:G9)/8*G12</f>
+        <f t="shared" si="2"/>
         <v>1.1073762251822066E-2</v>
       </c>
       <c r="H14" s="20">
-        <f>COUNTA(H2:H9)/8*H12</f>
+        <f t="shared" si="2"/>
         <v>0.28857753204322695</v>
       </c>
       <c r="I14" s="20">
-        <f>COUNTA(I2:I9)/8*I12</f>
+        <f t="shared" si="2"/>
         <v>3.5153304850464945E-2</v>
       </c>
       <c r="J14" s="20">
-        <f>COUNTA(J2:J9)/8*J12</f>
-        <v>1.6657765770294042E-2</v>
+        <f t="shared" si="2"/>
+        <v>3.3315531540588084E-2</v>
       </c>
       <c r="K14" s="20">
-        <f>COUNTA(K2:K9)/8*K12</f>
+        <f t="shared" si="2"/>
         <v>1.1921965317919074E-2</v>
       </c>
       <c r="L14" s="20">
-        <f>COUNTA(L2:L9)/8*L12</f>
+        <f t="shared" si="2"/>
         <v>1.1827720532797185E-2</v>
       </c>
       <c r="M14" s="20">
-        <f>COUNTA(M2:M9)/8*M12</f>
+        <f t="shared" si="2"/>
         <v>5.4897587333500881E-3</v>
       </c>
       <c r="N14" s="20">
-        <f>COUNTA(N2:N9)/8*N12</f>
+        <f t="shared" si="2"/>
         <v>5.3483915556672527E-3</v>
       </c>
       <c r="O14" s="20">
-        <f>COUNTA(O2:O9)/8*O12</f>
+        <f t="shared" si="2"/>
         <v>9.0003769791404883E-3</v>
       </c>
       <c r="P14" s="20">
-        <f>COUNTA(P2:P9)/8*P12</f>
-        <v>3.7697914048755968E-3</v>
+        <f t="shared" si="2"/>
+        <v>4.5237496858507161E-3</v>
       </c>
       <c r="Q14" s="20">
-        <f>COUNTA(Q2:Q9)/8*Q12</f>
-        <v>7.1311887408896709E-3</v>
+        <f t="shared" si="2"/>
+        <v>5.3483915556672527E-3</v>
       </c>
       <c r="R14" s="20">
-        <f>COUNTA(R2:R9)/8*R12</f>
+        <f t="shared" si="2"/>
         <v>9.2454134204574018E-2</v>
       </c>
     </row>
@@ -10788,7 +10806,7 @@
       </c>
       <c r="C15" s="18">
         <f>SUM(C13:R13)</f>
-        <v>0.95757937505235824</v>
+        <v>0.97841794420708716</v>
       </c>
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
@@ -10812,7 +10830,7 @@
       </c>
       <c r="C16" s="18">
         <f>SUM(C14:R14)</f>
-        <v>0.71818453128926885</v>
+        <v>0.73381345815531551</v>
       </c>
     </row>
     <row r="21" spans="19:23" x14ac:dyDescent="0.25">

--- a/data/raw_data/feed_profiles_and_composition.xlsx
+++ b/data/raw_data/feed_profiles_and_composition.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C4D544-BF4A-4F7D-A2FE-1BB52A9F7EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="feed_formulations" sheetId="1" r:id="rId1"/>

--- a/data/raw_data/feed_profiles_and_composition.xlsx
+++ b/data/raw_data/feed_profiles_and_composition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\treimer\Documents\R-temp-files\climate_risks_to_fed_mariculture\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C4D544-BF4A-4F7D-A2FE-1BB52A9F7EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FE671A-7020-428A-9874-7740CD564589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="feed_formulations" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1517" uniqueCount="272">
   <si>
     <t>ingredient</t>
   </si>
@@ -829,9 +829,6 @@
     <t>Zhan, Q., Han, T., Li, X., Wang, J., Yang, Y., Yu, X., Zheng, P., Liu, T., Xu, H., &amp; Wang, C. (2020). Effects of dietary carbohydrate levels on growth, body composition, and gene expression of key enzymes involved in hepatopancreas metabolism in mud crab Scylla paramamosain. Aquaculture, 529, 735638. https://doi.org/10.1016/j.aquaculture.2020.735638</t>
   </si>
   <si>
-    <t>tuna-japan</t>
-  </si>
-  <si>
     <t>fish-protein-concentrate</t>
   </si>
   <si>
@@ -844,9 +841,6 @@
     <t>starch</t>
   </si>
   <si>
-    <t>tuna-ranch</t>
-  </si>
-  <si>
     <t>Betancor, M. B., Ortega, A., de la Gándara, F., Tocher, D. R., &amp; Mourente, G. (2019). Performance, feed utilization, and hepatic metabolic response of weaned juvenile Atlantic bluefin tuna (Thunnus thynnus L.): Effects of dietary lipid level and source. Fish Physiology and Biochemistry, 45(2), 697–718. https://doi.org/10.1007/s10695-018-0587-9</t>
   </si>
   <si>
@@ -869,6 +863,18 @@
   </si>
   <si>
     <t>Code contribution</t>
+  </si>
+  <si>
+    <t>tuna_full-japan</t>
+  </si>
+  <si>
+    <t>tuna_ranch-ranch</t>
+  </si>
+  <si>
+    <t>tuna_full</t>
+  </si>
+  <si>
+    <t>tuna_ranch</t>
   </si>
 </sst>
 </file>
@@ -2980,7 +2986,7 @@
     </row>
     <row r="119" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B119" t="s">
         <v>1</v>
@@ -2991,7 +2997,7 @@
     </row>
     <row r="120" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B120" t="s">
         <v>23</v>
@@ -3002,7 +3008,7 @@
     </row>
     <row r="121" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B121" t="s">
         <v>5</v>
@@ -3013,7 +3019,7 @@
     </row>
     <row r="122" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B122" t="s">
         <v>2</v>
@@ -3024,7 +3030,7 @@
     </row>
     <row r="123" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B123" t="s">
         <v>12</v>
@@ -3035,7 +3041,7 @@
     </row>
     <row r="124" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B124" t="s">
         <v>32</v>
@@ -3887,7 +3893,7 @@
     </row>
     <row r="194" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B194" t="s">
         <v>1</v>
@@ -3898,7 +3904,7 @@
     </row>
     <row r="195" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B195" t="s">
         <v>25</v>
@@ -3909,10 +3915,10 @@
     </row>
     <row r="196" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B196" t="s">
         <v>256</v>
-      </c>
-      <c r="B196" t="s">
-        <v>257</v>
       </c>
       <c r="C196">
         <v>0.3</v>
@@ -3920,10 +3926,10 @@
     </row>
     <row r="197" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B197" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C197">
         <v>4.7E-2</v>
@@ -3931,10 +3937,10 @@
     </row>
     <row r="198" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B198" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C198">
         <v>0.02</v>
@@ -3942,10 +3948,10 @@
     </row>
     <row r="199" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B199" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C199">
         <v>9.8000000000000004E-2</v>
@@ -3953,7 +3959,7 @@
     </row>
     <row r="200" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B200" t="s">
         <v>192</v>
@@ -3964,7 +3970,7 @@
     </row>
     <row r="201" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B201" t="s">
         <v>32</v>
@@ -3975,7 +3981,7 @@
     </row>
     <row r="202" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B202" t="s">
         <v>1</v>
@@ -3986,7 +3992,7 @@
     </row>
     <row r="203" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B203" t="s">
         <v>25</v>
@@ -5204,7 +5210,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A162FC-7907-44C7-A909-E8E1323EC5F6}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:F300"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5237,7 +5242,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>195</v>
       </c>
@@ -5255,7 +5260,7 @@
       </c>
       <c r="F2" s="7"/>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>195</v>
       </c>
@@ -5271,7 +5276,7 @@
       <c r="E3" s="10"/>
       <c r="F3" s="7"/>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>195</v>
       </c>
@@ -5287,7 +5292,7 @@
       <c r="E4" s="10"/>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>195</v>
       </c>
@@ -5303,7 +5308,7 @@
       <c r="E5" s="10"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>125</v>
       </c>
@@ -5321,7 +5326,7 @@
       </c>
       <c r="F6" s="7"/>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>125</v>
       </c>
@@ -5337,7 +5342,7 @@
       <c r="E7" s="10"/>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>125</v>
       </c>
@@ -5353,7 +5358,7 @@
       <c r="E8" s="10"/>
       <c r="F8" s="7"/>
     </row>
-    <row r="9" spans="1:6" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>125</v>
       </c>
@@ -5371,7 +5376,7 @@
       </c>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>125</v>
       </c>
@@ -5389,7 +5394,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>125</v>
       </c>
@@ -5407,7 +5412,7 @@
       </c>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>125</v>
       </c>
@@ -5423,7 +5428,7 @@
       <c r="E12" s="10"/>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>125</v>
       </c>
@@ -5439,7 +5444,7 @@
       <c r="E13" s="10"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>125</v>
       </c>
@@ -5455,7 +5460,7 @@
       <c r="E14" s="10"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>125</v>
       </c>
@@ -5471,7 +5476,7 @@
       <c r="E15" s="10"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:6" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>125</v>
       </c>
@@ -5489,7 +5494,7 @@
       </c>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>125</v>
       </c>
@@ -5505,7 +5510,7 @@
       <c r="E17" s="10"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>125</v>
       </c>
@@ -5521,7 +5526,7 @@
       <c r="E18" s="10"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>125</v>
       </c>
@@ -5537,7 +5542,7 @@
       <c r="E19" s="10"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>125</v>
       </c>
@@ -5553,7 +5558,7 @@
       <c r="E20" s="10"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>116</v>
       </c>
@@ -5571,7 +5576,7 @@
       </c>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>116</v>
       </c>
@@ -5587,7 +5592,7 @@
       <c r="E22" s="10"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>116</v>
       </c>
@@ -5603,7 +5608,7 @@
       <c r="E23" s="10"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>116</v>
       </c>
@@ -5619,7 +5624,7 @@
       <c r="E24" s="10"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>116</v>
       </c>
@@ -5635,7 +5640,7 @@
       <c r="E25" s="10"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>116</v>
       </c>
@@ -5651,7 +5656,7 @@
       <c r="E26" s="10"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>116</v>
       </c>
@@ -5667,7 +5672,7 @@
       <c r="E27" s="10"/>
       <c r="F27" s="7"/>
     </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>116</v>
       </c>
@@ -5683,7 +5688,7 @@
       <c r="E28" s="10"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>116</v>
       </c>
@@ -5699,7 +5704,7 @@
       <c r="E29" s="10"/>
       <c r="F29" s="7"/>
     </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>116</v>
       </c>
@@ -5715,7 +5720,7 @@
       <c r="E30" s="10"/>
       <c r="F30" s="7"/>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>116</v>
       </c>
@@ -5731,7 +5736,7 @@
       <c r="E31" s="10"/>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>116</v>
       </c>
@@ -5747,7 +5752,7 @@
       <c r="E32" s="10"/>
       <c r="F32" s="7"/>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>116</v>
       </c>
@@ -5763,7 +5768,7 @@
       <c r="E33" s="10"/>
       <c r="F33" s="7"/>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>116</v>
       </c>
@@ -5779,7 +5784,7 @@
       <c r="E34" s="10"/>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>116</v>
       </c>
@@ -5795,7 +5800,7 @@
       <c r="E35" s="10"/>
       <c r="F35" s="7"/>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>116</v>
       </c>
@@ -5811,7 +5816,7 @@
       <c r="E36" s="10"/>
       <c r="F36" s="7"/>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>116</v>
       </c>
@@ -5827,7 +5832,7 @@
       <c r="E37" s="10"/>
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>116</v>
       </c>
@@ -5843,7 +5848,7 @@
       <c r="E38" s="10"/>
       <c r="F38" s="7"/>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>116</v>
       </c>
@@ -5859,7 +5864,7 @@
       <c r="E39" s="10"/>
       <c r="F39" s="7"/>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>116</v>
       </c>
@@ -5875,7 +5880,7 @@
       <c r="E40" s="10"/>
       <c r="F40" s="7"/>
     </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>116</v>
       </c>
@@ -5891,7 +5896,7 @@
       <c r="E41" s="10"/>
       <c r="F41" s="7"/>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>116</v>
       </c>
@@ -5907,7 +5912,7 @@
       <c r="E42" s="10"/>
       <c r="F42" s="7"/>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>116</v>
       </c>
@@ -5923,7 +5928,7 @@
       <c r="E43" s="10"/>
       <c r="F43" s="7"/>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>116</v>
       </c>
@@ -5939,7 +5944,7 @@
       <c r="E44" s="10"/>
       <c r="F44" s="7"/>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>116</v>
       </c>
@@ -5955,7 +5960,7 @@
       <c r="E45" s="10"/>
       <c r="F45" s="7"/>
     </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>116</v>
       </c>
@@ -5971,7 +5976,7 @@
       <c r="E46" s="10"/>
       <c r="F46" s="7"/>
     </row>
-    <row r="47" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>115</v>
       </c>
@@ -5989,7 +5994,7 @@
       </c>
       <c r="F47" s="7"/>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>115</v>
       </c>
@@ -6005,7 +6010,7 @@
       <c r="E48" s="10"/>
       <c r="F48" s="7"/>
     </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>115</v>
       </c>
@@ -6021,7 +6026,7 @@
       <c r="E49" s="10"/>
       <c r="F49" s="7"/>
     </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>115</v>
       </c>
@@ -6037,7 +6042,7 @@
       <c r="E50" s="10"/>
       <c r="F50" s="7"/>
     </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>115</v>
       </c>
@@ -6053,7 +6058,7 @@
       <c r="E51" s="10"/>
       <c r="F51" s="7"/>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>115</v>
       </c>
@@ -6069,7 +6074,7 @@
       <c r="E52" s="10"/>
       <c r="F52" s="7"/>
     </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>115</v>
       </c>
@@ -6085,7 +6090,7 @@
       <c r="E53" s="10"/>
       <c r="F53" s="7"/>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>115</v>
       </c>
@@ -6101,7 +6106,7 @@
       <c r="E54" s="10"/>
       <c r="F54" s="7"/>
     </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>115</v>
       </c>
@@ -6117,7 +6122,7 @@
       <c r="E55" s="10"/>
       <c r="F55" s="7"/>
     </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>115</v>
       </c>
@@ -6133,7 +6138,7 @@
       <c r="E56" s="10"/>
       <c r="F56" s="7"/>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>115</v>
       </c>
@@ -6149,7 +6154,7 @@
       <c r="E57" s="10"/>
       <c r="F57" s="7"/>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>115</v>
       </c>
@@ -6165,7 +6170,7 @@
       <c r="E58" s="10"/>
       <c r="F58" s="7"/>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>115</v>
       </c>
@@ -6181,7 +6186,7 @@
       <c r="E59" s="10"/>
       <c r="F59" s="7"/>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>115</v>
       </c>
@@ -6197,7 +6202,7 @@
       <c r="E60" s="10"/>
       <c r="F60" s="7"/>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>115</v>
       </c>
@@ -6213,7 +6218,7 @@
       <c r="E61" s="10"/>
       <c r="F61" s="7"/>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>115</v>
       </c>
@@ -6229,7 +6234,7 @@
       <c r="E62" s="10"/>
       <c r="F62" s="7"/>
     </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>115</v>
       </c>
@@ -6245,7 +6250,7 @@
       <c r="E63" s="10"/>
       <c r="F63" s="7"/>
     </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
         <v>115</v>
       </c>
@@ -6261,7 +6266,7 @@
       <c r="E64" s="10"/>
       <c r="F64" s="7"/>
     </row>
-    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
         <v>115</v>
       </c>
@@ -6277,7 +6282,7 @@
       <c r="E65" s="10"/>
       <c r="F65" s="7"/>
     </row>
-    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>115</v>
       </c>
@@ -6293,7 +6298,7 @@
       <c r="E66" s="10"/>
       <c r="F66" s="7"/>
     </row>
-    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>115</v>
       </c>
@@ -6309,7 +6314,7 @@
       <c r="E67" s="10"/>
       <c r="F67" s="7"/>
     </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
         <v>115</v>
       </c>
@@ -6325,7 +6330,7 @@
       <c r="E68" s="10"/>
       <c r="F68" s="7"/>
     </row>
-    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
         <v>115</v>
       </c>
@@ -6341,7 +6346,7 @@
       <c r="E69" s="10"/>
       <c r="F69" s="7"/>
     </row>
-    <row r="70" spans="1:6" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
         <v>114</v>
       </c>
@@ -6359,7 +6364,7 @@
       </c>
       <c r="F70" s="7"/>
     </row>
-    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
         <v>114</v>
       </c>
@@ -6375,7 +6380,7 @@
       <c r="E71" s="10"/>
       <c r="F71" s="7"/>
     </row>
-    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
         <v>114</v>
       </c>
@@ -6391,7 +6396,7 @@
       <c r="E72" s="10"/>
       <c r="F72" s="7"/>
     </row>
-    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
         <v>114</v>
       </c>
@@ -6407,7 +6412,7 @@
       <c r="E73" s="10"/>
       <c r="F73" s="7"/>
     </row>
-    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
         <v>114</v>
       </c>
@@ -6423,7 +6428,7 @@
       <c r="E74" s="10"/>
       <c r="F74" s="7"/>
     </row>
-    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
         <v>114</v>
       </c>
@@ -6439,7 +6444,7 @@
       <c r="E75" s="10"/>
       <c r="F75" s="7"/>
     </row>
-    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
         <v>114</v>
       </c>
@@ -6455,7 +6460,7 @@
       <c r="E76" s="10"/>
       <c r="F76" s="7"/>
     </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
         <v>114</v>
       </c>
@@ -6471,7 +6476,7 @@
       <c r="E77" s="10"/>
       <c r="F77" s="7"/>
     </row>
-    <row r="78" spans="1:6" ht="79.2" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
         <v>110</v>
       </c>
@@ -6489,7 +6494,7 @@
       </c>
       <c r="F78" s="7"/>
     </row>
-    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
         <v>110</v>
       </c>
@@ -6505,7 +6510,7 @@
       <c r="E79" s="10"/>
       <c r="F79" s="7"/>
     </row>
-    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
         <v>110</v>
       </c>
@@ -6521,7 +6526,7 @@
       <c r="E80" s="10"/>
       <c r="F80" s="7"/>
     </row>
-    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
         <v>110</v>
       </c>
@@ -6537,7 +6542,7 @@
       <c r="E81" s="10"/>
       <c r="F81" s="7"/>
     </row>
-    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
         <v>110</v>
       </c>
@@ -6553,7 +6558,7 @@
       <c r="E82" s="10"/>
       <c r="F82" s="7"/>
     </row>
-    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
         <v>110</v>
       </c>
@@ -6569,7 +6574,7 @@
       <c r="E83" s="10"/>
       <c r="F83" s="7"/>
     </row>
-    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
         <v>110</v>
       </c>
@@ -6585,7 +6590,7 @@
       <c r="E84" s="10"/>
       <c r="F84" s="7"/>
     </row>
-    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>110</v>
       </c>
@@ -6601,7 +6606,7 @@
       <c r="E85" s="10"/>
       <c r="F85" s="7"/>
     </row>
-    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
         <v>110</v>
       </c>
@@ -6617,7 +6622,7 @@
       <c r="E86" s="10"/>
       <c r="F86" s="7"/>
     </row>
-    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
         <v>110</v>
       </c>
@@ -6633,7 +6638,7 @@
       <c r="E87" s="10"/>
       <c r="F87" s="7"/>
     </row>
-    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
         <v>110</v>
       </c>
@@ -6649,7 +6654,7 @@
       <c r="E88" s="10"/>
       <c r="F88" s="7"/>
     </row>
-    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
         <v>110</v>
       </c>
@@ -6665,7 +6670,7 @@
       <c r="E89" s="10"/>
       <c r="F89" s="7"/>
     </row>
-    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
         <v>110</v>
       </c>
@@ -6681,7 +6686,7 @@
       <c r="E90" s="10"/>
       <c r="F90" s="7"/>
     </row>
-    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
         <v>110</v>
       </c>
@@ -6697,7 +6702,7 @@
       <c r="E91" s="10"/>
       <c r="F91" s="7"/>
     </row>
-    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
         <v>110</v>
       </c>
@@ -6713,7 +6718,7 @@
       <c r="E92" s="10"/>
       <c r="F92" s="7"/>
     </row>
-    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
         <v>110</v>
       </c>
@@ -6729,7 +6734,7 @@
       <c r="E93" s="10"/>
       <c r="F93" s="7"/>
     </row>
-    <row r="94" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
         <v>31</v>
       </c>
@@ -6747,7 +6752,7 @@
       </c>
       <c r="F94" s="7"/>
     </row>
-    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
         <v>31</v>
       </c>
@@ -6763,7 +6768,7 @@
       <c r="E95" s="10"/>
       <c r="F95" s="7"/>
     </row>
-    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
         <v>31</v>
       </c>
@@ -6779,7 +6784,7 @@
       <c r="E96" s="10"/>
       <c r="F96" s="7"/>
     </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
         <v>31</v>
       </c>
@@ -6795,7 +6800,7 @@
       <c r="E97" s="10"/>
       <c r="F97" s="7"/>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
         <v>31</v>
       </c>
@@ -6811,7 +6816,7 @@
       <c r="E98" s="10"/>
       <c r="F98" s="7"/>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
         <v>31</v>
       </c>
@@ -6827,7 +6832,7 @@
       <c r="E99" s="10"/>
       <c r="F99" s="7"/>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
         <v>31</v>
       </c>
@@ -6843,7 +6848,7 @@
       <c r="E100" s="10"/>
       <c r="F100" s="7"/>
     </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
         <v>31</v>
       </c>
@@ -6859,7 +6864,7 @@
       <c r="E101" s="10"/>
       <c r="F101" s="7"/>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
         <v>31</v>
       </c>
@@ -6875,7 +6880,7 @@
       <c r="E102" s="10"/>
       <c r="F102" s="7"/>
     </row>
-    <row r="103" spans="1:6" ht="66" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" ht="66" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
         <v>33</v>
       </c>
@@ -6893,7 +6898,7 @@
       </c>
       <c r="F103" s="7"/>
     </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
         <v>33</v>
       </c>
@@ -6909,7 +6914,7 @@
       <c r="E104" s="10"/>
       <c r="F104" s="7"/>
     </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
         <v>33</v>
       </c>
@@ -6925,7 +6930,7 @@
       <c r="E105" s="10"/>
       <c r="F105" s="7"/>
     </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
         <v>33</v>
       </c>
@@ -6941,7 +6946,7 @@
       <c r="E106" s="10"/>
       <c r="F106" s="7"/>
     </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
         <v>33</v>
       </c>
@@ -6957,7 +6962,7 @@
       <c r="E107" s="10"/>
       <c r="F107" s="7"/>
     </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
         <v>33</v>
       </c>
@@ -6973,7 +6978,7 @@
       <c r="E108" s="10"/>
       <c r="F108" s="7"/>
     </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
         <v>33</v>
       </c>
@@ -6989,7 +6994,7 @@
       <c r="E109" s="10"/>
       <c r="F109" s="7"/>
     </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
         <v>33</v>
       </c>
@@ -7005,7 +7010,7 @@
       <c r="E110" s="10"/>
       <c r="F110" s="7"/>
     </row>
-    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
         <v>33</v>
       </c>
@@ -7021,7 +7026,7 @@
       <c r="E111" s="10"/>
       <c r="F111" s="7"/>
     </row>
-    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
         <v>33</v>
       </c>
@@ -7037,7 +7042,7 @@
       <c r="E112" s="10"/>
       <c r="F112" s="7"/>
     </row>
-    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
         <v>33</v>
       </c>
@@ -7053,7 +7058,7 @@
       <c r="E113" s="10"/>
       <c r="F113" s="7"/>
     </row>
-    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
         <v>33</v>
       </c>
@@ -7069,7 +7074,7 @@
       <c r="E114" s="10"/>
       <c r="F114" s="7"/>
     </row>
-    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
         <v>33</v>
       </c>
@@ -7085,7 +7090,7 @@
       <c r="E115" s="10"/>
       <c r="F115" s="7"/>
     </row>
-    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
         <v>33</v>
       </c>
@@ -7101,7 +7106,7 @@
       <c r="E116" s="10"/>
       <c r="F116" s="7"/>
     </row>
-    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
         <v>33</v>
       </c>
@@ -7117,7 +7122,7 @@
       <c r="E117" s="10"/>
       <c r="F117" s="7"/>
     </row>
-    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
         <v>33</v>
       </c>
@@ -7133,7 +7138,7 @@
       <c r="E118" s="10"/>
       <c r="F118" s="7"/>
     </row>
-    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
         <v>33</v>
       </c>
@@ -7149,7 +7154,7 @@
       <c r="E119" s="10"/>
       <c r="F119" s="7"/>
     </row>
-    <row r="120" spans="1:6" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
         <v>37</v>
       </c>
@@ -7167,7 +7172,7 @@
       </c>
       <c r="F120" s="7"/>
     </row>
-    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
         <v>37</v>
       </c>
@@ -7183,7 +7188,7 @@
       <c r="E121" s="10"/>
       <c r="F121" s="7"/>
     </row>
-    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
         <v>37</v>
       </c>
@@ -7199,7 +7204,7 @@
       <c r="E122" s="10"/>
       <c r="F122" s="7"/>
     </row>
-    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
         <v>37</v>
       </c>
@@ -7215,7 +7220,7 @@
       <c r="E123" s="10"/>
       <c r="F123" s="7"/>
     </row>
-    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
         <v>37</v>
       </c>
@@ -7231,7 +7236,7 @@
       <c r="E124" s="10"/>
       <c r="F124" s="7"/>
     </row>
-    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
         <v>37</v>
       </c>
@@ -7247,7 +7252,7 @@
       <c r="E125" s="10"/>
       <c r="F125" s="7"/>
     </row>
-    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
         <v>37</v>
       </c>
@@ -7263,7 +7268,7 @@
       <c r="E126" s="10"/>
       <c r="F126" s="7"/>
     </row>
-    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
         <v>37</v>
       </c>
@@ -7279,7 +7284,7 @@
       <c r="E127" s="10"/>
       <c r="F127" s="7"/>
     </row>
-    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
         <v>37</v>
       </c>
@@ -7295,7 +7300,7 @@
       <c r="E128" s="10"/>
       <c r="F128" s="7"/>
     </row>
-    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
         <v>37</v>
       </c>
@@ -7311,7 +7316,7 @@
       <c r="E129" s="10"/>
       <c r="F129" s="7"/>
     </row>
-    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
         <v>37</v>
       </c>
@@ -7327,7 +7332,7 @@
       <c r="E130" s="10"/>
       <c r="F130" s="7"/>
     </row>
-    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
         <v>37</v>
       </c>
@@ -7343,7 +7348,7 @@
       <c r="E131" s="10"/>
       <c r="F131" s="7"/>
     </row>
-    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
         <v>37</v>
       </c>
@@ -7359,7 +7364,7 @@
       <c r="E132" s="10"/>
       <c r="F132" s="7"/>
     </row>
-    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
         <v>37</v>
       </c>
@@ -7375,7 +7380,7 @@
       <c r="E133" s="10"/>
       <c r="F133" s="7"/>
     </row>
-    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
         <v>37</v>
       </c>
@@ -7391,7 +7396,7 @@
       <c r="E134" s="10"/>
       <c r="F134" s="7"/>
     </row>
-    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
         <v>37</v>
       </c>
@@ -7407,7 +7412,7 @@
       <c r="E135" s="10"/>
       <c r="F135" s="7"/>
     </row>
-    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
         <v>37</v>
       </c>
@@ -7423,7 +7428,7 @@
       <c r="E136" s="10"/>
       <c r="F136" s="7"/>
     </row>
-    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
         <v>37</v>
       </c>
@@ -7439,7 +7444,7 @@
       <c r="E137" s="10"/>
       <c r="F137" s="7"/>
     </row>
-    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
         <v>37</v>
       </c>
@@ -7455,7 +7460,7 @@
       <c r="E138" s="10"/>
       <c r="F138" s="7"/>
     </row>
-    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
         <v>37</v>
       </c>
@@ -7471,7 +7476,7 @@
       <c r="E139" s="10"/>
       <c r="F139" s="7"/>
     </row>
-    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
         <v>37</v>
       </c>
@@ -7487,7 +7492,7 @@
       <c r="E140" s="10"/>
       <c r="F140" s="7"/>
     </row>
-    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
         <v>37</v>
       </c>
@@ -7503,7 +7508,7 @@
       <c r="E141" s="10"/>
       <c r="F141" s="7"/>
     </row>
-    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
         <v>37</v>
       </c>
@@ -7761,7 +7766,7 @@
       <c r="E157" s="10"/>
       <c r="F157" s="7"/>
     </row>
-    <row r="158" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
         <v>35</v>
       </c>
@@ -7772,14 +7777,14 @@
         <v>184</v>
       </c>
       <c r="D158" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E158" s="8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F158" s="7"/>
     </row>
-    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
         <v>35</v>
       </c>
@@ -7790,12 +7795,12 @@
         <v>39</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E159" s="10"/>
       <c r="F159" s="7"/>
     </row>
-    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
         <v>35</v>
       </c>
@@ -7806,12 +7811,12 @@
         <v>3</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E160" s="10"/>
       <c r="F160" s="7"/>
     </row>
-    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
         <v>35</v>
       </c>
@@ -7822,12 +7827,12 @@
         <v>1</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E161" s="10"/>
       <c r="F161" s="7"/>
     </row>
-    <row r="162" spans="1:6" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
         <v>90</v>
       </c>
@@ -7845,7 +7850,7 @@
       </c>
       <c r="F162" s="7"/>
     </row>
-    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
         <v>90</v>
       </c>
@@ -7860,7 +7865,7 @@
       </c>
       <c r="E163" s="10"/>
     </row>
-    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
         <v>90</v>
       </c>
@@ -7876,7 +7881,7 @@
       <c r="E164" s="10"/>
       <c r="F164" s="7"/>
     </row>
-    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
         <v>90</v>
       </c>
@@ -7892,7 +7897,7 @@
       <c r="E165" s="10"/>
       <c r="F165" s="7"/>
     </row>
-    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
         <v>90</v>
       </c>
@@ -7908,7 +7913,7 @@
       <c r="E166" s="10"/>
       <c r="F166" s="7"/>
     </row>
-    <row r="167" spans="1:6" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
         <v>90</v>
       </c>
@@ -7926,7 +7931,7 @@
       </c>
       <c r="F167" s="7"/>
     </row>
-    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
         <v>90</v>
       </c>
@@ -7942,7 +7947,7 @@
       <c r="E168" s="10"/>
       <c r="F168" s="7"/>
     </row>
-    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
         <v>90</v>
       </c>
@@ -7958,7 +7963,7 @@
       <c r="E169" s="10"/>
       <c r="F169" s="7"/>
     </row>
-    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
         <v>90</v>
       </c>
@@ -7974,7 +7979,7 @@
       <c r="E170" s="10"/>
       <c r="F170" s="7"/>
     </row>
-    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
         <v>90</v>
       </c>
@@ -7990,7 +7995,7 @@
       <c r="E171" s="10"/>
       <c r="F171" s="7"/>
     </row>
-    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
         <v>90</v>
       </c>
@@ -8006,7 +8011,7 @@
       <c r="E172" s="10"/>
       <c r="F172" s="7"/>
     </row>
-    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
         <v>90</v>
       </c>
@@ -8022,7 +8027,7 @@
       <c r="E173" s="10"/>
       <c r="F173" s="7"/>
     </row>
-    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
         <v>90</v>
       </c>
@@ -8038,7 +8043,7 @@
       <c r="E174" s="10"/>
       <c r="F174" s="7"/>
     </row>
-    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
         <v>90</v>
       </c>
@@ -8054,7 +8059,7 @@
       <c r="E175" s="10"/>
       <c r="F175" s="7"/>
     </row>
-    <row r="176" spans="1:6" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
         <v>90</v>
       </c>
@@ -8072,7 +8077,7 @@
       </c>
       <c r="F176" s="7"/>
     </row>
-    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
         <v>90</v>
       </c>
@@ -8088,7 +8093,7 @@
       <c r="E177" s="10"/>
       <c r="F177" s="7"/>
     </row>
-    <row r="178" spans="1:6" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
         <v>79</v>
       </c>
@@ -8106,7 +8111,7 @@
       </c>
       <c r="F178" s="7"/>
     </row>
-    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
         <v>79</v>
       </c>
@@ -8122,7 +8127,7 @@
       <c r="E179" s="10"/>
       <c r="F179" s="7"/>
     </row>
-    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
         <v>79</v>
       </c>
@@ -8138,7 +8143,7 @@
       <c r="E180" s="10"/>
       <c r="F180" s="7"/>
     </row>
-    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
         <v>79</v>
       </c>
@@ -8154,7 +8159,7 @@
       <c r="E181" s="10"/>
       <c r="F181" s="7"/>
     </row>
-    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
         <v>79</v>
       </c>
@@ -8170,7 +8175,7 @@
       <c r="E182" s="10"/>
       <c r="F182" s="7"/>
     </row>
-    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
         <v>79</v>
       </c>
@@ -8186,7 +8191,7 @@
       <c r="E183" s="10"/>
       <c r="F183" s="7"/>
     </row>
-    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
         <v>79</v>
       </c>
@@ -8202,7 +8207,7 @@
       <c r="E184" s="10"/>
       <c r="F184" s="7"/>
     </row>
-    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
         <v>79</v>
       </c>
@@ -8218,7 +8223,7 @@
       <c r="E185" s="10"/>
       <c r="F185" s="7"/>
     </row>
-    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
         <v>79</v>
       </c>
@@ -8234,7 +8239,7 @@
       <c r="E186" s="10"/>
       <c r="F186" s="7"/>
     </row>
-    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
         <v>79</v>
       </c>
@@ -8250,7 +8255,7 @@
       <c r="E187" s="10"/>
       <c r="F187" s="7"/>
     </row>
-    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
         <v>79</v>
       </c>
@@ -8266,7 +8271,7 @@
       <c r="E188" s="10"/>
       <c r="F188" s="7"/>
     </row>
-    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
         <v>79</v>
       </c>
@@ -8282,7 +8287,7 @@
       <c r="E189" s="10"/>
       <c r="F189" s="7"/>
     </row>
-    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="7" t="s">
         <v>79</v>
       </c>
@@ -8298,7 +8303,7 @@
       <c r="E190" s="10"/>
       <c r="F190" s="7"/>
     </row>
-    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
         <v>79</v>
       </c>
@@ -8314,7 +8319,7 @@
       <c r="E191" s="10"/>
       <c r="F191" s="7"/>
     </row>
-    <row r="192" spans="1:6" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A192" s="7" t="s">
         <v>79</v>
       </c>
@@ -8332,7 +8337,7 @@
       </c>
       <c r="F192" s="7"/>
     </row>
-    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
         <v>79</v>
       </c>
@@ -8348,7 +8353,7 @@
       <c r="E193" s="10"/>
       <c r="F193" s="7"/>
     </row>
-    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="7" t="s">
         <v>79</v>
       </c>
@@ -8364,7 +8369,7 @@
       <c r="E194" s="10"/>
       <c r="F194" s="7"/>
     </row>
-    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
         <v>79</v>
       </c>
@@ -8380,7 +8385,7 @@
       <c r="E195" s="10"/>
       <c r="F195" s="7"/>
     </row>
-    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="7" t="s">
         <v>79</v>
       </c>
@@ -8396,7 +8401,7 @@
       <c r="E196" s="10"/>
       <c r="F196" s="7"/>
     </row>
-    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
         <v>79</v>
       </c>
@@ -8412,7 +8417,7 @@
       <c r="E197" s="10"/>
       <c r="F197" s="7"/>
     </row>
-    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
         <v>79</v>
       </c>
@@ -8428,7 +8433,7 @@
       <c r="E198" s="10"/>
       <c r="F198" s="7"/>
     </row>
-    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
         <v>79</v>
       </c>
@@ -8444,7 +8449,7 @@
       <c r="E199" s="10"/>
       <c r="F199" s="7"/>
     </row>
-    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
         <v>79</v>
       </c>
@@ -8460,7 +8465,7 @@
       <c r="E200" s="10"/>
       <c r="F200" s="7"/>
     </row>
-    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
         <v>79</v>
       </c>
@@ -8476,7 +8481,7 @@
       <c r="E201" s="10"/>
       <c r="F201" s="7"/>
     </row>
-    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
         <v>79</v>
       </c>
@@ -8492,7 +8497,7 @@
       <c r="E202" s="10"/>
       <c r="F202" s="7"/>
     </row>
-    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
         <v>79</v>
       </c>
@@ -8508,7 +8513,7 @@
       <c r="E203" s="10"/>
       <c r="F203" s="7"/>
     </row>
-    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
         <v>79</v>
       </c>
@@ -8524,7 +8529,7 @@
       <c r="E204" s="10"/>
       <c r="F204" s="7"/>
     </row>
-    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
         <v>79</v>
       </c>
@@ -8540,7 +8545,7 @@
       <c r="E205" s="10"/>
       <c r="F205" s="7"/>
     </row>
-    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="7" t="s">
         <v>79</v>
       </c>
@@ -8556,7 +8561,7 @@
       <c r="E206" s="10"/>
       <c r="F206" s="7"/>
     </row>
-    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
         <v>79</v>
       </c>
@@ -8572,7 +8577,7 @@
       <c r="E207" s="10"/>
       <c r="F207" s="7"/>
     </row>
-    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="7" t="s">
         <v>79</v>
       </c>
@@ -8588,7 +8593,7 @@
       <c r="E208" s="10"/>
       <c r="F208" s="7"/>
     </row>
-    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
         <v>79</v>
       </c>
@@ -8604,7 +8609,7 @@
       <c r="E209" s="10"/>
       <c r="F209" s="7"/>
     </row>
-    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="7" t="s">
         <v>39</v>
       </c>
@@ -8622,7 +8627,7 @@
       </c>
       <c r="F210" s="7"/>
     </row>
-    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
         <v>39</v>
       </c>
@@ -8638,7 +8643,7 @@
       <c r="E211" s="10"/>
       <c r="F211" s="7"/>
     </row>
-    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="7" t="s">
         <v>39</v>
       </c>
@@ -8654,7 +8659,7 @@
       <c r="E212" s="10"/>
       <c r="F212" s="7"/>
     </row>
-    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
         <v>39</v>
       </c>
@@ -8670,7 +8675,7 @@
       <c r="E213" s="10"/>
       <c r="F213" s="7"/>
     </row>
-    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="7" t="s">
         <v>39</v>
       </c>
@@ -8686,7 +8691,7 @@
       <c r="E214" s="10"/>
       <c r="F214" s="7"/>
     </row>
-    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="7" t="s">
         <v>39</v>
       </c>
@@ -8702,7 +8707,7 @@
       <c r="E215" s="10"/>
       <c r="F215" s="7"/>
     </row>
-    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="7" t="s">
         <v>39</v>
       </c>
@@ -8718,7 +8723,7 @@
       <c r="E216" s="10"/>
       <c r="F216" s="7"/>
     </row>
-    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="7" t="s">
         <v>39</v>
       </c>
@@ -8734,7 +8739,7 @@
       <c r="E217" s="10"/>
       <c r="F217" s="7"/>
     </row>
-    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="7" t="s">
         <v>39</v>
       </c>
@@ -8750,7 +8755,7 @@
       <c r="E218" s="10"/>
       <c r="F218" s="7"/>
     </row>
-    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="7" t="s">
         <v>39</v>
       </c>
@@ -8766,7 +8771,7 @@
       <c r="E219" s="10"/>
       <c r="F219" s="7"/>
     </row>
-    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="7" t="s">
         <v>39</v>
       </c>
@@ -8782,7 +8787,7 @@
       <c r="E220" s="10"/>
       <c r="F220" s="7"/>
     </row>
-    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
         <v>39</v>
       </c>
@@ -8798,7 +8803,7 @@
       <c r="E221" s="10"/>
       <c r="F221" s="7"/>
     </row>
-    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="7" t="s">
         <v>39</v>
       </c>
@@ -8814,7 +8819,7 @@
       <c r="E222" s="10"/>
       <c r="F222" s="7"/>
     </row>
-    <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="7" t="s">
         <v>39</v>
       </c>
@@ -8830,7 +8835,7 @@
       <c r="E223" s="10"/>
       <c r="F223" s="7"/>
     </row>
-    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="7" t="s">
         <v>39</v>
       </c>
@@ -8846,7 +8851,7 @@
       <c r="E224" s="10"/>
       <c r="F224" s="7"/>
     </row>
-    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
         <v>39</v>
       </c>
@@ -8862,7 +8867,7 @@
       <c r="E225" s="10"/>
       <c r="F225" s="7"/>
     </row>
-    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="7" t="s">
         <v>39</v>
       </c>
@@ -8878,7 +8883,7 @@
       <c r="E226" s="10"/>
       <c r="F226" s="7"/>
     </row>
-    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
         <v>39</v>
       </c>
@@ -8894,7 +8899,7 @@
       <c r="E227" s="10"/>
       <c r="F227" s="7"/>
     </row>
-    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="7" t="s">
         <v>39</v>
       </c>
@@ -8910,7 +8915,7 @@
       <c r="E228" s="10"/>
       <c r="F228" s="7"/>
     </row>
-    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
         <v>39</v>
       </c>
@@ -8926,9 +8931,9 @@
       <c r="E229" s="10"/>
       <c r="F229" s="7"/>
     </row>
-    <row r="230" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A230" s="7" t="s">
-        <v>36</v>
+        <v>270</v>
       </c>
       <c r="B230" s="7" t="s">
         <v>135</v>
@@ -8940,13 +8945,13 @@
         <v>228</v>
       </c>
       <c r="E230" s="8" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F230" s="7"/>
     </row>
-    <row r="231" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
-        <v>36</v>
+        <v>271</v>
       </c>
       <c r="B231" s="7" t="s">
         <v>74</v>
@@ -8955,16 +8960,16 @@
         <v>58</v>
       </c>
       <c r="D231" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E231" s="8" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F231" s="7"/>
     </row>
-    <row r="232" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="7" t="s">
-        <v>36</v>
+        <v>271</v>
       </c>
       <c r="B232" s="7" t="s">
         <v>130</v>
@@ -8973,14 +8978,14 @@
         <v>24</v>
       </c>
       <c r="D232" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E232" s="10"/>
       <c r="F232" s="7"/>
     </row>
-    <row r="233" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="7" t="s">
-        <v>36</v>
+        <v>271</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>137</v>
@@ -8989,14 +8994,14 @@
         <v>19</v>
       </c>
       <c r="D233" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E233" s="10"/>
       <c r="F233" s="7"/>
     </row>
-    <row r="234" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="7" t="s">
-        <v>36</v>
+        <v>271</v>
       </c>
       <c r="B234" s="7" t="s">
         <v>50</v>
@@ -9005,14 +9010,14 @@
         <v>17</v>
       </c>
       <c r="D234" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E234" s="10"/>
       <c r="F234" s="7"/>
     </row>
-    <row r="235" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="7" t="s">
-        <v>36</v>
+        <v>271</v>
       </c>
       <c r="B235" s="7" t="s">
         <v>141</v>
@@ -9021,14 +9026,14 @@
         <v>10</v>
       </c>
       <c r="D235" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E235" s="10"/>
       <c r="F235" s="7"/>
     </row>
-    <row r="236" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="7" t="s">
-        <v>36</v>
+        <v>271</v>
       </c>
       <c r="B236" s="7" t="s">
         <v>118</v>
@@ -9037,14 +9042,14 @@
         <v>7</v>
       </c>
       <c r="D236" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E236" s="10"/>
       <c r="F236" s="7"/>
     </row>
-    <row r="237" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="7" t="s">
-        <v>36</v>
+        <v>271</v>
       </c>
       <c r="B237" s="7" t="s">
         <v>51</v>
@@ -9053,14 +9058,14 @@
         <v>4</v>
       </c>
       <c r="D237" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E237" s="10"/>
       <c r="F237" s="7"/>
     </row>
-    <row r="238" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="7" t="s">
-        <v>36</v>
+        <v>271</v>
       </c>
       <c r="B238" s="7" t="s">
         <v>72</v>
@@ -9069,14 +9074,14 @@
         <v>1</v>
       </c>
       <c r="D238" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E238" s="10"/>
       <c r="F238" s="7"/>
     </row>
-    <row r="239" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="7" t="s">
-        <v>36</v>
+        <v>271</v>
       </c>
       <c r="B239" s="7" t="s">
         <v>71</v>
@@ -9085,12 +9090,12 @@
         <v>1</v>
       </c>
       <c r="D239" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E239" s="10"/>
       <c r="F239" s="7"/>
     </row>
-    <row r="240" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A240" s="7" t="s">
         <v>38</v>
       </c>
@@ -9108,7 +9113,7 @@
       </c>
       <c r="F240" s="7"/>
     </row>
-    <row r="241" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="7" t="s">
         <v>38</v>
       </c>
@@ -9124,7 +9129,7 @@
       <c r="E241" s="10"/>
       <c r="F241" s="7"/>
     </row>
-    <row r="242" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="7" t="s">
         <v>38</v>
       </c>
@@ -9140,7 +9145,7 @@
       <c r="E242" s="10"/>
       <c r="F242" s="7"/>
     </row>
-    <row r="243" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="7" t="s">
         <v>38</v>
       </c>
@@ -9156,7 +9161,7 @@
       <c r="E243" s="10"/>
       <c r="F243" s="7"/>
     </row>
-    <row r="244" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="7" t="s">
         <v>38</v>
       </c>
@@ -9172,7 +9177,7 @@
       <c r="E244" s="10"/>
       <c r="F244" s="7"/>
     </row>
-    <row r="245" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="7" t="s">
         <v>38</v>
       </c>
@@ -9188,7 +9193,7 @@
       <c r="E245" s="10"/>
       <c r="F245" s="7"/>
     </row>
-    <row r="246" spans="1:6" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A246" s="7" t="s">
         <v>38</v>
       </c>
@@ -9206,7 +9211,7 @@
       </c>
       <c r="F246" s="7"/>
     </row>
-    <row r="247" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="7" t="s">
         <v>38</v>
       </c>
@@ -9222,7 +9227,7 @@
       <c r="E247" s="10"/>
       <c r="F247" s="7"/>
     </row>
-    <row r="248" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="7" t="s">
         <v>38</v>
       </c>
@@ -9238,7 +9243,7 @@
       <c r="E248" s="10"/>
       <c r="F248" s="7"/>
     </row>
-    <row r="249" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
         <v>38</v>
       </c>
@@ -9254,7 +9259,7 @@
       <c r="E249" s="10"/>
       <c r="F249" s="7"/>
     </row>
-    <row r="250" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="7" t="s">
         <v>38</v>
       </c>
@@ -9270,7 +9275,7 @@
       <c r="E250" s="10"/>
       <c r="F250" s="7"/>
     </row>
-    <row r="251" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="7" t="s">
         <v>38</v>
       </c>
@@ -9286,7 +9291,7 @@
       <c r="E251" s="10"/>
       <c r="F251" s="7"/>
     </row>
-    <row r="252" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="7" t="s">
         <v>38</v>
       </c>
@@ -9302,7 +9307,7 @@
       <c r="E252" s="10"/>
       <c r="F252" s="7"/>
     </row>
-    <row r="253" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
         <v>38</v>
       </c>
@@ -9318,7 +9323,7 @@
       <c r="E253" s="10"/>
       <c r="F253" s="7"/>
     </row>
-    <row r="254" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="7" t="s">
         <v>38</v>
       </c>
@@ -9334,7 +9339,7 @@
       <c r="E254" s="10"/>
       <c r="F254" s="7"/>
     </row>
-    <row r="255" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
         <v>38</v>
       </c>
@@ -9350,7 +9355,7 @@
       <c r="E255" s="10"/>
       <c r="F255" s="7"/>
     </row>
-    <row r="256" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="7" t="s">
         <v>38</v>
       </c>
@@ -9366,7 +9371,7 @@
       <c r="E256" s="10"/>
       <c r="F256" s="7"/>
     </row>
-    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
         <v>38</v>
       </c>
@@ -9382,7 +9387,7 @@
       <c r="E257" s="10"/>
       <c r="F257" s="7"/>
     </row>
-    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="7" t="s">
         <v>38</v>
       </c>
@@ -9398,7 +9403,7 @@
       <c r="E258" s="10"/>
       <c r="F258" s="7"/>
     </row>
-    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
         <v>38</v>
       </c>
@@ -9414,7 +9419,7 @@
       <c r="E259" s="10"/>
       <c r="F259" s="7"/>
     </row>
-    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="7" t="s">
         <v>38</v>
       </c>
@@ -9430,7 +9435,7 @@
       <c r="E260" s="10"/>
       <c r="F260" s="7"/>
     </row>
-    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
         <v>38</v>
       </c>
@@ -9446,7 +9451,7 @@
       <c r="E261" s="10"/>
       <c r="F261" s="7"/>
     </row>
-    <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="7" t="s">
         <v>38</v>
       </c>
@@ -9462,7 +9467,7 @@
       <c r="E262" s="10"/>
       <c r="F262" s="7"/>
     </row>
-    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
         <v>38</v>
       </c>
@@ -9478,7 +9483,7 @@
       <c r="E263" s="10"/>
       <c r="F263" s="7"/>
     </row>
-    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="7" t="s">
         <v>38</v>
       </c>
@@ -9494,7 +9499,7 @@
       <c r="E264" s="10"/>
       <c r="F264" s="7"/>
     </row>
-    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
         <v>38</v>
       </c>
@@ -9510,7 +9515,7 @@
       <c r="E265" s="10"/>
       <c r="F265" s="7"/>
     </row>
-    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="7" t="s">
         <v>38</v>
       </c>
@@ -9526,7 +9531,7 @@
       <c r="E266" s="10"/>
       <c r="F266" s="7"/>
     </row>
-    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
         <v>38</v>
       </c>
@@ -9542,7 +9547,7 @@
       <c r="E267" s="10"/>
       <c r="F267" s="7"/>
     </row>
-    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="7" t="s">
         <v>38</v>
       </c>
@@ -9558,7 +9563,7 @@
       <c r="E268" s="10"/>
       <c r="F268" s="7"/>
     </row>
-    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
         <v>38</v>
       </c>
@@ -9574,7 +9579,7 @@
       <c r="E269" s="10"/>
       <c r="F269" s="7"/>
     </row>
-    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="7" t="s">
         <v>38</v>
       </c>
@@ -9590,7 +9595,7 @@
       <c r="E270" s="10"/>
       <c r="F270" s="7"/>
     </row>
-    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
         <v>38</v>
       </c>
@@ -9606,7 +9611,7 @@
       <c r="E271" s="10"/>
       <c r="F271" s="7"/>
     </row>
-    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="7" t="s">
         <v>38</v>
       </c>
@@ -9622,7 +9627,7 @@
       <c r="E272" s="10"/>
       <c r="F272" s="7"/>
     </row>
-    <row r="273" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
         <v>38</v>
       </c>
@@ -9638,7 +9643,7 @@
       <c r="E273" s="10"/>
       <c r="F273" s="7"/>
     </row>
-    <row r="274" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="7" t="s">
         <v>38</v>
       </c>
@@ -9654,7 +9659,7 @@
       <c r="E274" s="10"/>
       <c r="F274" s="7"/>
     </row>
-    <row r="275" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="7" t="s">
         <v>38</v>
       </c>
@@ -9670,7 +9675,7 @@
       <c r="E275" s="10"/>
       <c r="F275" s="7"/>
     </row>
-    <row r="276" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="7" t="s">
         <v>38</v>
       </c>
@@ -9686,7 +9691,7 @@
       <c r="E276" s="10"/>
       <c r="F276" s="7"/>
     </row>
-    <row r="277" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="7" t="s">
         <v>38</v>
       </c>
@@ -9702,7 +9707,7 @@
       <c r="E277" s="10"/>
       <c r="F277" s="7"/>
     </row>
-    <row r="278" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="7" t="s">
         <v>38</v>
       </c>
@@ -9718,7 +9723,7 @@
       <c r="E278" s="10"/>
       <c r="F278" s="7"/>
     </row>
-    <row r="279" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
         <v>38</v>
       </c>
@@ -9736,7 +9741,7 @@
       </c>
       <c r="F279" s="7"/>
     </row>
-    <row r="280" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="7" t="s">
         <v>38</v>
       </c>
@@ -9752,7 +9757,7 @@
       <c r="E280" s="10"/>
       <c r="F280" s="7"/>
     </row>
-    <row r="281" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="7" t="s">
         <v>38</v>
       </c>
@@ -9768,7 +9773,7 @@
       <c r="E281" s="10"/>
       <c r="F281" s="7"/>
     </row>
-    <row r="282" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="7" t="s">
         <v>38</v>
       </c>
@@ -9784,7 +9789,7 @@
       <c r="E282" s="10"/>
       <c r="F282" s="7"/>
     </row>
-    <row r="283" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="7" t="s">
         <v>38</v>
       </c>
@@ -9800,7 +9805,7 @@
       <c r="E283" s="10"/>
       <c r="F283" s="7"/>
     </row>
-    <row r="284" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="7" t="s">
         <v>38</v>
       </c>
@@ -9816,7 +9821,7 @@
       <c r="E284" s="10"/>
       <c r="F284" s="7"/>
     </row>
-    <row r="285" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="7" t="s">
         <v>38</v>
       </c>
@@ -9832,7 +9837,7 @@
       <c r="E285" s="10"/>
       <c r="F285" s="7"/>
     </row>
-    <row r="286" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="7" t="s">
         <v>38</v>
       </c>
@@ -9848,7 +9853,7 @@
       <c r="E286" s="10"/>
       <c r="F286" s="7"/>
     </row>
-    <row r="287" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="7" t="s">
         <v>38</v>
       </c>
@@ -9864,7 +9869,7 @@
       <c r="E287" s="10"/>
       <c r="F287" s="7"/>
     </row>
-    <row r="288" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="7" t="s">
         <v>38</v>
       </c>
@@ -9880,7 +9885,7 @@
       <c r="E288" s="10"/>
       <c r="F288" s="7"/>
     </row>
-    <row r="289" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="7" t="s">
         <v>38</v>
       </c>
@@ -9896,7 +9901,7 @@
       <c r="E289" s="10"/>
       <c r="F289" s="7"/>
     </row>
-    <row r="290" spans="1:6" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A290" s="7" t="s">
         <v>38</v>
       </c>
@@ -9914,7 +9919,7 @@
       </c>
       <c r="F290" s="7"/>
     </row>
-    <row r="291" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="7" t="s">
         <v>38</v>
       </c>
@@ -9930,7 +9935,7 @@
       <c r="E291" s="10"/>
       <c r="F291" s="7"/>
     </row>
-    <row r="292" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="7" t="s">
         <v>38</v>
       </c>
@@ -9946,7 +9951,7 @@
       <c r="E292" s="10"/>
       <c r="F292" s="7"/>
     </row>
-    <row r="293" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="7" t="s">
         <v>38</v>
       </c>
@@ -9962,7 +9967,7 @@
       <c r="E293" s="10"/>
       <c r="F293" s="7"/>
     </row>
-    <row r="294" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="7" t="s">
         <v>38</v>
       </c>
@@ -9978,7 +9983,7 @@
       <c r="E294" s="10"/>
       <c r="F294" s="7"/>
     </row>
-    <row r="295" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="7" t="s">
         <v>38</v>
       </c>
@@ -9994,7 +9999,7 @@
       <c r="E295" s="10"/>
       <c r="F295" s="7"/>
     </row>
-    <row r="296" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="7" t="s">
         <v>38</v>
       </c>
@@ -10010,7 +10015,7 @@
       <c r="E296" s="10"/>
       <c r="F296" s="7"/>
     </row>
-    <row r="297" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="7" t="s">
         <v>38</v>
       </c>
@@ -10026,7 +10031,7 @@
       <c r="E297" s="10"/>
       <c r="F297" s="7"/>
     </row>
-    <row r="298" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="7" t="s">
         <v>38</v>
       </c>
@@ -10042,7 +10047,7 @@
       <c r="E298" s="10"/>
       <c r="F298" s="7"/>
     </row>
-    <row r="299" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="7" t="s">
         <v>38</v>
       </c>
@@ -10058,7 +10063,7 @@
       <c r="E299" s="10"/>
       <c r="F299" s="7"/>
     </row>
-    <row r="300" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="7" t="s">
         <v>38</v>
       </c>
@@ -10076,11 +10081,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F300" xr:uid="{38A162FC-7907-44C7-A909-E8E1323EC5F6}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="nile_tilapia"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A240:F300">
       <sortCondition ref="D1:D300"/>
     </sortState>
@@ -10664,7 +10664,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B13" s="49" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C13" s="20">
         <f>COUNTA(C2:C7)/6*C12</f>
@@ -10802,7 +10802,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B15" s="49" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C15" s="18">
         <f>SUM(C13:R13)</f>
